--- a/data/חכמים_ללא_מחקר.xlsx
+++ b/data/חכמים_ללא_מחקר.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חכמים ללא מחקר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$N$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,9 @@
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -511,334 +514,463 @@
           <t>קישור ספוטיפיי</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>מסמך בתיקייה?</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>שם הקובץ המועמד</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>שורת הפתיחה של המסמך</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>בת שבע</t>
+          <t>הרא"ם ממיץ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>המלכים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>תקופת דוד ושלמה</t>
+          <t>המאה ה־12</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; ממלכת ישראל</t>
+          <t>צרפת ואשכנז</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>מלכות, הנהגה וחכמה</t>
+          <t>הלכה, מצוות ומוסר</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, שלמה המלך, נתן הנביא, אם המלך, אשת חיל, משלי, משפט צדק, נשים</t>
+          <t>ספר יראים, רבנו תם, יראת שמים, מצוות</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>אשת דוד ואמו של שלמה, שבספר מלכים מתגלה כדמות מדינית נחושה: היא פועלת עם נתן הנביא להבטחת המלכת שלמה, ולאחר מכן זוכה למעמד ״אם המלך״. במסורת חז״ל היא מזוהה עם אמו של למואל המוכיחה את בנה על אחריות המלכות.</t>
+          <t>מגדולי הראשונים בצרפת ואשכנז, תלמידם של רבנו תם והרשב"ם. בספרו 'ספר יראים' הציג את המצוות לא רק כמערכת דינים אלא כדרך לעיצוב האדם.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>הכתר אינו זכות בלבד אלא אחריות מוסרית; בת שבע מייצגת את הכוח להציב גבולות למלך ולדרוש ממנו צדק, משמעת עצמית ודאגה לחלשים.</t>
+          <t>סידור המצוות כמבנה רוחני־מוסרי כולל, שבו ההלכה נועדה לעצב את נפש האדם ולא רק להכריע בדין.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, שלמה המלך, נתן הנביא, אדוניהו בן חגית</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>רבנו תם; הרשב"ם; רבי חיים כהן מפריז; רבי אלעזר מגרמייזא; האור זרוע</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/6J1axbvjzcVZFeEI2lU1IV?si=wAeaI5T6TDSElvMR_MhZ1w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>עמוד ההוראה והחסידות_ משנתו התורנית ופועלו ההלכתי של רבי אליעזר ממיץ (הרא_ם).docx</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>עמוד ההוראה והחסידות: משנתו התורנית ופועלו ההלכתי של רבי אליעזר ממיץ (הרא"ם)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>צרויה</t>
+          <t>הרא״ה (רבי אהרן הלוי)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>המלכים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>תקופת דוד המלך</t>
+          <t>1231–1303</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>בית לחם; ממלכת דוד</t>
+          <t>ספרד</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>בית דוד, משפחה ומלוכה</t>
+          <t>הלכה ותלמוד</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, יואב, אבישי, עשהאל, בני צרויה, הנהגה, גבורה, מלכות, נשים</t>
+          <t>בדק הבית</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>אחותו של דוד המלך ובתו של ישי, ששמה נשמר במקרא בעיקר דרך שלושת בניה - יואב, אבישי ועשהאל. הייחוס החוזר של הבנים דווקא לאמם הפך את צרויה לסמל משפחתי המזוהה עם כוח, גבורה ונאמנות לבית דוד.</t>
+          <t>מתלמידי הרמב״ן ומגדולי חכמי קטלוניה, מבקרו ההלכתי המרכזי של הרשב״א.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>המתח בין דוד לבין בני צרויה ממחיש את הצורך והסכנה שבחיבור בין חסד לכוח: המלכות זקוקה לעוצמה צבאית, אך גם לריסון מוסרי ולהנהגה רוחנית.</t>
+          <t>נאמנות למסורת יחד עם ביקורת הלכתית עצמאית.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, ישי, יואב בן צרויה, אבישי בן צרויה, עשהאל בן צרויה</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>הרמב״ן, הריטב״א</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/1VCc2NTp4Fx2MnomLuC2YQ</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>משנתו, פועלו ומורשתו התורנית של רבי אהרן הלוי (הרא_ה)_ ניתוח היסטורי, הלכתי ופרשני של עמוד התווך בחכמי ברצלונה.docx</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>משנתו, פועלו ומורשתו התורנית של רבי אהרן הלוי (הרא"ה): ניתוח היסטורי, הלכתי ופרשני של עמוד התווך בחכמי ברצלונה</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>בן סירא</t>
+          <t>הרי״ד הזקן – רבי ישעיה די טראני</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>בית שני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>סביב 190 לפנה״ס</t>
+          <t>המאה ה־13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; מצרים (תרגום/תוספות הנכד)</t>
+          <t>איטליה</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>חכמה ומוסר</t>
+          <t>תלמוד, הלכה</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ספרות בית שני, מוסר ודרך ארץ, גבולות קאנון, השפעה חז"לית</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>תוספות, שיטה למדנית</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>יצר שיטת לימוד חדשה המתמקדת בהבנת כל סוגיה בפני עצמה, גם במחיר השארת סתירות פתוחות.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>“ננס על גבי ענק” – המשכיות יצירתית של המסורת</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>בעלי התוספות; מהר"ם מרוטנבורג; הרא"ש; ריטב"א</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3u5udRWI84FVJ3OsOBBbPF?si=ek7V_WzPS7OadSPOZSU-VA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/1RhrrkBapQNDsL3Nc92rS3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>(הרי_ד הזקן)_ מחקר מקיף על יצירתו, שיטתו והשפעתו לדורות.docx</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>(הרי"ד הזקן): מחקר מקיף על יצירתו, שיטתו והשפעתו לדורות</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>298</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>שמעון כיפא – מרטיר נוצרי או צדיק נסתר ששלחו חכמי ישראל?</t>
+          <t>יחיאל בן יקותיאל</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>בית שני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>המאות הראשונות לספירה</t>
+          <t>המאה ה־13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ארץ ישראל; רומא; ראשית הנצרות</t>
+          <t>רומא, איטליה</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>מסורת ופולמוס</t>
+          <t>מוסר, הלכה, רפואה ועריכת טקסטים</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>יהדות–נצרות, מסורות אזוטריות, זהות, פולמוס, ליטורגיה, ט' בטבת</t>
+          <t>מעלות המידות, תניא רבתי, ירושלמי, רומא</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>הפרק מציג את הפער בין המסורת הנוצרית על פטרוס לבין מסורות יהודיות המציירות את שמעון כיפא כשליח נסתר שנועד ליצור הפרדה בין יהדות לנצרות כדי למנוע שפיכות דמים והתבוללות. לפי הסיפור, הוא עיצב מנהגים ותיאולוגיה שמרחיקים מן היהדות ובמקביל למד תורה בסתר. מוצגים גם ייחוסים ליטורגיים ומסורות סביב צום ט' בטבת.</t>
+          <t>חכם איטלקי ששילב תורה, רפואה, פילוסופיה ודקדוק טקסטואלי. מיוחסת לו תרומה מכרעת לשימור מסורת הירושלמי ולבניית ספרות מוסר שיטתית.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>מסורות כמנגנון זהות: סיפור 'שליח נסתר' שמפרש פילוג דתי כצעד הגנתי של הקהילה.</t>
+          <t>חיבור הלכה, מוסר ודיוק מדעי לתפיסה אחת של תיקון האדם כולו — גוף, נפש ושכל.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ספר חסידים; אוצר המדרשים; תולדות ישו</t>
+          <t>הרמב״ם; חסידי אשכנז; מסורת איטליה; כתב יד ליידן של הירושלמי</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4tu43oeL4qVdXGKzX2025J?si=G3-56Xu3TxKoDiSCHX9gEA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/1tRAsJRFk47EvwWKBYsRZc?si=wIR3RR1RT0qdwsZfGHbvvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>רבי יחיאל בן יקותיאל ענו_ מחקר היסטורי והלכתי מקיף.docx</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>רבי יחיאל בן יקותיאל ענו: מחקר היסטורי והלכתי מקיף</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ילתא</t>
+          <t>ספר הזוהר – מי כתב? רבי שמעון בר יוחאי או חיבור מאוחר? המחלוקת סביב מחבר הזוהר</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>אמוראים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־3–4 לספירה</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>בבל</t>
+          <t>ארץ ישראל/ספרד; עולם הקבלה</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה ומעמד נשים</t>
+          <t>קבלה</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>רב נחמן, עולא, רבה בר בר חנה, היתר ואיסור, כוס של ברכה, 400 חביות יין, נשים</t>
+          <t>מסורת וביקורת; סמכות טקסטואלית; היסטוריה של הזוהר</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>בת למשפחת ראש הגולה ורעייתו של רב נחמן, מן הדמויות הנשיות הבולטות בתלמוד. היא מביעה רעיונות הלכתיים מקוריים, עומדת על דעתה מול חכמים, פונה לבירור הלכתי נוסף בעת הצורך ואף מייעצת לבעלה בענייני הנהגה.</t>
+          <t>מחלוקת הייחוס של הזוהר לרשב"י מול טענות למחבר מאוחר, והשלכות השאלה על סמכות הקבלה ועל קריאת הטקסט.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>עולם ההלכה כולל לא רק איסורים אלא גם מרחב של היתר, עונג וקדושה; ילתא מגלמת עצמאות אינטלקטואלית, מעמד ציבורי ונוכחות נשית פעילה בעולם האמוראי.</t>
+          <t>מעבר ל'מי כתב': איך טקסט נעשה קנוני ומהי אחריות הפרשנות כשמסורת והיסטוריה מצטלבות.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>רב נחמן, עולא, רבה בר בר חנה, רב יצחק בריה דרב יהודה</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>רשב"י; ר' משה די ליאון; גרשם שלום; מחקר הקבלה</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://spotifycreators-web.app.link/e/HxZF2iS4yQb</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>התנא רבי שמעון בר יוחאי.docx</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>התנא רבי שמעון בר יוחאי</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>רבי חייא הגדול</t>
+          <t>רבי יהודה בן ברכיה</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>אמוראים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־2–3 לספירה</t>
+          <t>המאות ה־12–13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>בבל, טבריה</t>
+          <t>פרובאנס</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>תורה שבעל פה, חינוך</t>
+          <t>הלכה, תלמוד ופירוש הרי״ף</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>שכחת התורה, תוספתא, מסירות</t>
+          <t>שיטת ריב״ב, הרי״ף, גאונים, רמב״ם</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>הציל את התורה משכחה בפעולה מעשית כוללת. שילב עמל גשמי ורוחני כדי להעביר מסורת.</t>
+          <t>מחכמי פרובאנס שיצר פירוש רחב על הלכות הרי״ף. שיטתו שילבה פשט, ביקורת על הרי״ף, מסורת גאונים והשוואה לפסקי הרמב״ם.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>תורה נשמרת במעשה. אחריות אישית להעברה דורית.</t>
+          <t>הפיכת פרובאנס לגשר חי בין מסורת הגאונים, הרי״ף, הרמב״ם ובעלי התוספות.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הנשיא, רבי אושעיה</t>
+          <t>הרי״ף; בעל המאור; רב האי גאון; ר״י אבן גיאת; הרמב״ם; הרמב״ן; הרשב״א</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4MI4LUL2FI4WeVtEdPZS5F</t>
+          <t>https://open.spotify.com/episode/647NStP3Z8X3LRqObcCXUZ?si=KByF2c3MQAKtqw4L_2KQFg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>משנתו ההלכתית ופועלו התורני של רבי יהודה בן ברכיה (ריב_ב)_ מחקר מקיף על צומת מסורות פרובנס.docx</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>משנתו ההלכתית ופועלו התורני של רבי יהודה בן ברכיה (ריב"ב): מחקר מקיף על צומת מסורות פרובנס</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>אברהם בר חייא</t>
+          <t>רבי משה די ליאון</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -848,54 +980,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>המאה ה-12</t>
+          <t>1240–1305</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ברצלונה</t>
+          <t>קסטיליה, ספרד</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>מדע, פילוסופיה</t>
+          <t>קבלה</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>בר חייא, פילוסופיה, מדע יהודי, מתמטיקה</t>
+          <t>ספר הזוהר, קבלת קסטיליה, גירונה, ספרות הסוד</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>היהודי הראשון שכתב מדע בעברית והשפיע על תרגום חכמת המזרח לאירופה.</t>
+          <t>מגדולי המקובלים בקסטיליה במאה ה-13, שבידיו נתגלה (או נערך) ספר הזוהר. חיבר גם ספרי קבלה בעברית כ"שקל הקודש", ועמד במוקד המחלוקת ההיסטורית על קדמות הזוהר.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>שילוב בין תורה, מדע ופילוסופיה; תרגום חכמה כללית לעברית.</t>
+          <t>העמדת ספר הזוהר במרכז ארון הספרים היהודי — הטקסט המכונן של תורת הסוד.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>פיבונאצ'י, חכמי ספרד</t>
+          <t>רבי שמעון בר יוחאי (ייחוס הזוהר), מקובלי גירונה</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3FAGqYdzyMQbyPbon3KYoC</t>
+          <t>https://open.spotify.com/episode/5hjMOYSZfyk2PpvO1z7y60?si=xvtDucKGTcqSJ5rNgkG76A</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>משה בן שם טוב די ליאון (1240–1305)_ דו_ח מומחה על פועלו ומשנתו התורנית.docx</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>משה בן שם טוב די ליאון (1240–1305): דו"ח מומחה על פועלו ומשנתו התורנית</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>הרא"ם ממיץ</t>
+          <t>רבי צדקיה בן אברהם העניו</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -905,54 +1052,69 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־12</t>
+          <t>המאה ה־13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>צרפת ואשכנז</t>
+          <t>איטליה</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>הלכה, מצוות ומוסר</t>
+          <t>הלכה ורפואה</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>ספר יראים, רבנו תם, יראת שמים, מצוות</t>
+          <t>שיבולי הלקט</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>מגדולי הראשונים בצרפת ואשכנז, תלמידם של רבנו תם והרשב"ם. בספרו 'ספר יראים' הציג את המצוות לא רק כמערכת דינים אלא כדרך לעיצוב האדם.</t>
+          <t>מגדולי חכמי איטליה, מחבר שיבולי הלקט ומגשר בין מסורות אשכנז ואיטליה.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>סידור המצוות כמבנה רוחני־מוסרי כולל, שבו ההלכה נועדה לעצב את נפש האדם ולא רק להכריע בדין.</t>
+          <t>סידור ושימור המסורת ההלכתית מתוך ענווה ואחריות.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>רבנו תם; הרשב"ם; רבי חיים כהן מפריז; רבי אלעזר מגרמייזא; האור זרוע</t>
+          <t>בעלי התוספות, בעל הטורים</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6J1axbvjzcVZFeEI2lU1IV?si=wAeaI5T6TDSElvMR_MhZ1w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/0zmmVvmiG4Wzj6H3D3wwK7</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>הקודיפיקציה האיטלקית ושורשיה בירושלים_ משנתו התורנית ופועלו של רבי צדקיה בן אברהם הרופא.docx</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>הקודיפיקציה האיטלקית ושורשיה בירושלים: משנתו התורנית ופועלו של רבי צדקיה בן אברהם הרופא</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>הראב"ן</t>
+          <t>רבנו יצחק בן יהודה ממגנצא</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -962,1186 +1124,1493 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1090–1170 בקירוב</t>
+          <t>המאה ה־11</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>מגנצא</t>
+          <t>גרמניה</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>הלכה והיסטוריה</t>
+          <t>הלכה ותלמוד</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>גזרות תתנ"ו</t>
+          <t>מגנצא, רש"י</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>החכם שתיעד את החורבן ובנה מחדש את יהדות אשכנז.</t>
+          <t>ראש ישיבת מגנצא ומורו המרכזי של רש"י, ממעצבי שיטת הלימוד האשכנזית.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>הפיכת זיכרון החורבן ליסוד של בנייה רוחנית.</t>
+          <t>שילוב בין דיוק טקסטואלי, מנהג ופסיקה.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>רבנו תם; הרשב"ם; הרא"ש</t>
+          <t>רבנו גרשום, רש"י</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5QGbbhxhb2hremjTS5I9E8?si=wQyrfYb9SgeVnHb998KX6w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/4tFSo5qQFWExTxQDDj1a8Q</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>רבי יצחק בן יהודה על התהוות המסורת האשכנזית.docx</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>רבי יצחק בן יהודה על התהוות המסורת האשכנזית</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>הרא״ה (רבי אהרן הלוי)</t>
+          <t>רבי חיים בן עטר (בעל אור החיים)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1231–1303</t>
+          <t>1696–1743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ספרד</t>
+          <t>סאלי, מרוקו; ליבורנו; ירושלים</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>הלכה ותלמוד</t>
+          <t>פרשנות התורה, הלכה וקבלה</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>בדק הבית</t>
+          <t>אור החיים, מדרש כנסת ישראל, כבה נר המערבי, גאולת אחישנה ובעתה</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>מתלמידי הרמב״ן ומגדולי חכמי קטלוניה, מבקרו ההלכתי המרכזי של הרשב״א.</t>
+          <t>מגדולי חכמי מרוקו במאה ה־18, פרשן, פוסק ומקובל. חיבר את "אור החיים" המשלב פשט, רמז, דרש וסוד, והקים בירושלים את ישיבת "כנסת ישראל". הבעל שם טוב ספד לו במות: "כבה נר המערבי".</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>נאמנות למסורת יחד עם ביקורת הלכתית עצמאית.</t>
+          <t>שילוב שיטתי של ארבעת רבדי הפרשנות (פרד"ס) בפירוש אחד, לצד תפיסת גאולה המבחינה בין "אחישנה" מהירה ל"בעתה" הדרגתית.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ן, הריטב״א</t>
+          <t>הבעל שם טוב, ועד כנסת ישראל בליבורנו</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1VCc2NTp4Fx2MnomLuC2YQ</t>
+          <t>https://open.spotify.com/episode/3HwpG5NALcGOQmbs1wwR4N?si=2otS_OCBTYaCbDWu2xZarQ</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>משנתו, פועלו ומורשתו של רבי חיים בן עטר_ אור החיים הקדוש בפרספקטיבה היסטורית ותאולוגית.docx</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>משנתו, פועלו ומורשתו של רבי חיים בן עטר: אור החיים הקדוש בפרספקטיבה היסטורית ותאולוגית</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>הרב אפרים מקלעת־חמאד</t>
+          <t>רבי ישראל יהושע טרונק (ישועות מלכו)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>בערך 1050–1150</t>
+          <t>1820–1893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>קלעת בן חמאד, צפון אפריקה</t>
+          <t>פולין</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>הלכה, נוסח ודקדוק</t>
+          <t>הלכה, ציונות דתית</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>הרי"ף, דקדוק עברי, ביקורת נוסח, קירואן</t>
+          <t>היתר מכירה, יישוב הארץ</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>מן הדמויות העמוקות שבין תקופת הגאונים לראשוני ספרד ופרובנס, 'תלמיד חבר' של הרי"ף. הגהותיו נטמעו בספר ההלכות, והוא שילב רגישות פילולוגית ודקדוקית בתוך הפסיקה.</t>
+          <t>פוסק גדול שתמך בהתיישבות וב"היתר מכירה" מתוך ראיית הגאולה המעשית.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>החדרת דיוק לשוני וביקורת נוסח ככלים הלכתיים מהותיים, מתוך נאמנות למסורת ואומץ אינטלקטואלי.</t>
+          <t>עבודת הארץ כחלק מהמצווה והגאולה</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>הרי"ף; רבי שלמה אבן פרחון; הראב"ד; בעל המאור; הרמב"ן</t>
+          <t>קלישר; רבני ארץ ישראל; פוסקי הדור</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5teJp1U9ghLdy4CXNAusRN?si=uqTLoA-PT_yqmv9eyGRw6g&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=88</t>
+          <t>https://open.spotify.com/episode/5CjFGW61SRKSx3ScmazcV1</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, פסיקה ותפיסה לאומית_ דמותו ופועלו של רבי ישראל יהושע טרונק מקוטנא (ה_ישועות מלכו_).docx</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, פסיקה ותפיסה לאומית: דמותו ופועלו של רבי ישראל יהושע טרונק מקוטנא (ה"ישועות מלכו")</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>הרד״ק</t>
+          <t>האדמו״ר מקאליב (רבי מנחם מנדל טאוב)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1160–1235</t>
+          <t>1923–2019</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>פרובאנס</t>
+          <t>הונגריה וישראל</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>מקרא ודקדוק</t>
+          <t>חסידות, זיכרון השואה והלכה</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>ספר השורשים, ספר המכלול</t>
+          <t>קול מנחם, שמע ישראל</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>מגדולי פרשני המקרא והמדקדקים, ממעצבי דרך הפשט בלימוד התנ״ך.</t>
+          <t>ניצול שואה ומנהיג חסידי שהקדיש את חייו להנצחת הנספים ולהפצת תורה ואמונה.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>הבנת לשון הקודש כמפתח להבנת התורה.</t>
+          <t>הפיכת הזיכרון והכאב לכוח של בניין רוחני.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>רבי יוסף קמחי, הרמב״ם</t>
+          <t>חסידות קאליב</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7t7Mwzw5zr9XQ4uPrDcKcz</t>
+          <t>https://open.spotify.com/episode/2RfVxXD6TIynHVoCEcKPJn</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של האדמו_ר מקאליב, רבי מנחם מנדל טאוב_ מנהיגות, הנצחה ויצירה תורנית בצל החורבן.docx</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של האדמו"ר מקאליב, רבי מנחם מנדל טאוב: מנהיגות, הנצחה ויצירה תורנית בצל החורבן</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>הריצב״א</t>
+          <t>הרב אברהם יהושע השל – הגות ומעורבות מוסרית</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־12–13</t>
+          <t>1907–1972</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>צרפת</t>
+          <t>פולין / ארה"ב</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, תוספות וסוד</t>
+          <t>הגות יהודית ואתיקה ציבורית</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ר״י הבחור, רבנו תם, ר״י הזקן, מעשה מרכבה</t>
+          <t>השבת ארמון בזמן, נבואה, פליאה, זכויות אזרח, דיאלוג יהודי-נוצרי</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>מן הדמויות המרכזיות בדור שלאחר רבנו תם בעולם התוספות. שילב עצמאות למדנית ושימוש רחב בירושלמי עם מוניטין של איש חזיונות וסודות הבריאה.</t>
+          <t>הוגה שחיבר חסידות ופילוסופיה עם אתיקה ציבורית. כתב 'השבת' ו'הנביאים', פעל בזכויות האזרח, וצעד לצד מרטין לותר קינג – 'תפילה עם הרגליים'.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>חיבור נדיר בין חריפות דיאלקטית תלמודית לבין עומק מיסטי, כגשר בין אשכנז, ספרד ועולמות הסוד.</t>
+          <t>קדושת הזמן והפליאה כמנוע אמונה; אחריות מוסרית כחלק בלתי נפרד מעבודת ה'.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>רבנו תם; ר״י הזקן; הרמב״ם; רבי יהודה בר יקר; רבי יחיאל מפאריס</t>
+          <t>מרטין לותר קינג; JTS; דיאלוג יהודי-נוצרי (נוסטרה אטאטה)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0fIS5dc7OCTq1C6amM82LT?si=tqcgKwdFQPuRVDKuMbTmkQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/63Q7RdapehdnH3FCLVMrBy?si=DujHYLYPTUmSckrnlOofCQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>אברהם יהושע השל_ פנומנולוגיה של קדושה וצדק.docx</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>אברהם יהושע השל: פנומנולוגיה של קדושה וצדק</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>הרי״ד הזקן – רבי ישעיה די טראני</t>
+          <t>הרב אברהם יצחק הכהן קוק – החזון שאיחד קודש וחול</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>1865–1935</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>איטליה</t>
+          <t>ארץ ישראל</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, הלכה</t>
+          <t>הגות ציונית-דתית והלכה</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>תוספות, שיטה למדנית</t>
+          <t>קודש וחול, תשובה היסטורית, ציונות, היתר מכירה, מרכז הרב</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>יצר שיטת לימוד חדשה המתמקדת בהבנת כל סוגיה בפני עצמה, גם במחיר השארת סתירות פתוחות.</t>
+          <t>הראי"ה קוק ראה במודרנה תהליך אלוהי ובציונות החילונית תנועת תשובה עמוקה. חיפש אחדות בין ניגודים, דיבר על התפתחות, והנהיג הלכתית-לאומית מתוך אחריות ליישוב.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>“ננס על גבי ענק” – המשכיות יצירתית של המסורת</t>
+          <t>האמת מתגלה במתח בין ניגודים: “הישן יתחדש והחדש יתקדש” – איחוד כוחות במקום מחיקה.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>בעלי התוספות; מהר"ם מרוטנבורג; הרא"ש; ריטב"א</t>
+          <t>חלוצים; ישיבת 'מרכז הרב'; פולמוס ההיתר בשמיטה</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1RhrrkBapQNDsL3Nc92rS3</t>
+          <t>https://open.spotify.com/episode/19vVkCaNfYWm6AlvbjbkRe?si=Y2-7mNX9QnCXzxz32MKpgA</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>רב אברהם יצחק הכהן קוק.docx</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>הם יצחק הכהן קוק: אנליזה מקיפה של מהפכת הקודש בתקופת התחייה</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>הרמב"ן (רבי משה בן נחמן)</t>
+          <t>הרב חיים דרוקמן – מנהיג ציונות דתית בדורנו</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1194–1270</t>
+          <t>1932–2022</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ספרד, ארץ ישראל</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>פרשנות, הלכה, קבלה</t>
+          <t>מנהיגות וחינוך</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>ויכוח ברצלונה, פרשנות לתורה, תורת הסוד, עלייה לארץ</t>
+          <t>בני עקיבא, ישיבות הסדר, גיור, הנהגה ציבורית, אחדות</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>פוסק, פרשן ומקובל ששילב את כל רבדי התורה, חידש את יישוב ירושלים ועמד באומץ מול הכנסייה.</t>
+          <t>ניצול שואה שהפך למנהיג מרכזי בציונות הדתית: ראש מוסדות אור עציון, מנהיג בני עקיבא ונשיא ישיבות ההסדר. נשא באחריות למערך הגיור הממלכתי מתוך אהבת ישראל.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>שילוב פשט, דרש, סוד ופרשנות קבלית – ראיית הטבע כסדרה של ניסים נסתרים.</t>
+          <t>הנהגה אחראית שמחזיקה תורה-צבא-מדינה יחד, עם דגש על אחדות ואהבת אדם.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם, בעלי התוספות, הר"ן</t>
+          <t>הרב צבי יהודה קוק; מוסדות אור עציון; מערך הגיור</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3ZjAqfQEp21lw1GXKibFGq</t>
+          <t>https://open.spotify.com/episode/1j4SgDhb3vWdY3gvTjv3oq?si=67O0wVDkTsa2b7zRpBFQmQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=128</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>הרב חיים מאיר דרוקמן.docx</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>הרב חיים מאיר דרוקמן</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>הרמ״ה</t>
+          <t>הרב יהודה אלקלעי – תשובה שהופכת לתוכנית לאומית</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1170–1244</t>
+          <t>1798–1878</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ספרד</t>
+          <t>הבלקן</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, מסורה והלכה</t>
+          <t>הגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>רבי מאיר הלוי אבולעפיה, יד רמה</t>
+          <t>תשובה כללית, שיבה לארץ, דיפלומטיה, שפה עברית, אחדות</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי ספרד, פוסק, ראש ישיבה ובעל מסורת סייג לתורה.</t>
+          <t>הוגה ציוני-דתי מוקדם שמפרש 'תשובה' כתהליך לאומי: שיבה לארץ היא עצמה הגאולה. מציע תכנית פעולה: חברות כלכליות, יוזמות מדיניות ואחידות לאומית סביב עברית וזהות אחת.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>דיוק במסורת לצד הנהגה הלכתית עצמאית.</t>
+          <t>תשובה כללית = שיבה: אחריות היסטורית עוברת מן השמיים לאדם ולציבור.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ם, הרמב״ן</t>
+          <t>קשר רעיוני למשפחת הרצל (כפי שנרמז בטקסט); מבשרי חיבת ציון</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3DlGOty8LZ8KGhLiLcyqjs</t>
+          <t>https://open.spotify.com/episode/6GD0RxzoBaG17nmaGA9pe9?si=qeIXN4iwRIWsOjztQ5cWoQ</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>הרב יהודה בן שלמה חי אלקלעי.docx</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>הרב יהודה בן שלמה חי אלקלעי</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>חכמי פרובנס – בין נרבון, בית דוד והמיסטיקה הראשונה: המרכז היהודי ששבר את המפה הרוחנית של ימי הביניים</t>
+          <t>הרב יהודה אריה מודנה – דיוקן של גאונות שנאבקה על עצמה</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>המאות ה־11–13</t>
+          <t>1571–1648</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>פרובנס; נרבון; דרום צרפת</t>
+          <t>ונציה; איטליה</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>היסטוריה ותולדות</t>
+          <t>מוסר והגות</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>הלכה ותלמוד, מפגש ספרד–אשכנז, נשיאות נרבון, קבלה מוקדמת, חסידות אשכנז, מוסדות</t>
+          <t>אוטוביוגרפיה, הימורים, התמכרות, פולמוס קבלה, יהודים–נוצרים, הומניזם, ספרות</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>פרובנס מתוארת כמרחב מפגש בין הלכה ספרדית שיטתית לדיאלקטיקה אשכנזית-צרפתית, וכמוקד מדיני-תורני סביב נרבון והמסורת הנשיאותית. מתוך המתח הזה נולדת קבלה מוקדמת בסינתזה עם חסידות אשכנז. הפרק מציג כיצד מרכז אזורי קטן שינה את המפה הרוחנית של ימי הביניים והכין קרקע להתפתחויות מאוחרות.</t>
+          <t>רבי יהודה אריה מודנה היה רב, דרשן ופולמוסן בגטו ונציה, בעל גאונות לשונית וכתיבה עשירה. לצד מפעל רוחני רחב הוא תיעד בכנות את התמכרותו להימורים ואת נפילותיו באוטוביוגרפיה "חיי יהודה". כתביו נעים בין הגנה על המסורת לבין ביקורת חריפה על הקבלה ושיח עם העולם הנוצרי.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>מפגש מסורות כמנוע יצירה: סינתזה בין ספרד–אשכנז שמולידה מרכז הלכתי ומיסטי חדש.</t>
+          <t>יושר רוחני כמודל הנהגה: גאונות לצד חשיפה כנה של חולשה ומאבק פנימי.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>הראב"ד; הרז"ה; האחים הכהן; יצחק סגי נהור</t>
+          <t>קהילת ונציה; פולמוס מול מקובלים; הומניזם נוצרי</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/28wg8VCd8QFBLQiEa8y15f?si=ai8T1gHuSUulzXa6z02hwA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/7dCBE5OnROaK58y5cK5tiO?si=4Cr1F3_iTIu6UQbPYdZuyg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>בין סמכות הלכתית, רציונליזם ומודרנה_ פועלו, יצירתו ומשנתו התורנית של רבי יהודה אריה ממודנה (הריא_ם).docx</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>בין סמכות הלכתית, רציונליזם ומודרנה: פועלו, יצירתו ומשנתו התורנית של רבי יהודה אריה ממודנה (הריא"ם)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>יחיאל בן יקותיאל</t>
+          <t>הרב יחזקאל לנדא – “הנודע ביהודה”</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>1713–1793</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>רומא, איטליה</t>
+          <t>פראג (בוהמיה)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>מוסר, הלכה, רפואה ועריכת טקסטים</t>
+          <t>פסיקה והנהגה קהילתית</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>מעלות המידות, תניא רבתי, ירושלמי, רומא</t>
+          <t>שו"ת, שבתאות, חסידות, השכלה, קבלה (זהירות), הנהגה</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>חכם איטלקי ששילב תורה, רפואה, פילוסופיה ודקדוק טקסטואלי. מיוחסת לו תרומה מכרעת לשימור מסורת הירושלמי ולבניית ספרות מוסר שיטתית.</t>
+          <t>גדול פוסקי פראג שניצב מול שבתאות, השכלה וחסידות. הכריע באומץ בסוגיות עקרוניות, הנהיג בקור רוח בזמן משברים, ושילב מאבק בכפירה עם אחריות ציבורית.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>חיבור הלכה, מוסר ודיוק מדעי לתפיסה אחת של תיקון האדם כולו — גוף, נפש ושכל.</t>
+          <t>מנהיגות הלכתית אסטרטגית: לדעת מתי להילחם בגלוי ומתי לרסן כדי לשמור על אחדות הקהילה.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ם; חסידי אשכנז; מסורת איטליה; כתב יד ליידן של הירושלמי</t>
+          <t>מריה תרזה; יוזף השני; הערכה גם בחוגים חסידיים</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1tRAsJRFk47EvwWKBYsRZc?si=wIR3RR1RT0qdwsZfGHbvvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/4EJ2FNYaB1FdSuKMRkfonR?si=123rhSTsT6Wga_7NA8Xp_A&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>רבי יחזקאל לנדא, _הנודע ביהודה_.docx</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>רבי יחזקאל לנדא, "הנודע ביהודה"</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>מהפכת הרמב"ם, תגובת ספרד ומורשת הרמ"א – הקרב על נשמתה של התורה</t>
+          <t>הרב יצחק נסים – הראשון לציון שניהל 'מדיניות חוץ' עצמאית</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ימי הביניים–המאה ה־16</t>
+          <t>1895–1981</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ספרד; אשכנז; קרקוב</t>
+          <t>בגדד / ישראל</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>מוסר והגות</t>
+          <t>הלכה, הנהגה ציבורית</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>פילוסופיה, סדרי לימוד, הלכה, מטאפיזיקה, קבלה, עולם הישיבות, סמכות</t>
+          <t>ראשון לציון, רבנות ראשית, ממלכתיות, גיור, יחסי דת ומדינה</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>דרמה אינטלקטואלית על מטרת לימוד התורה: הרמב"ם מציב את ההשגה המטאפיזית כפסגה, וחכמי ספרד מדגישים את מרכזיות הגמרא ולעיתים את הקבלה. הרמ"א מעצב מודל שבו לימוד הלכה ותלמוד הם עצמם התכלית ובכך מניח יסודות לעולם הישיבות. הפרק מצביע על השלכות לשאלת סמכות תורה שבעל-פה.</t>
+          <t>ראשון לציון והרב הראשי לישראל; הנהיג קו ממלכתי־עצמאי, פעל לקרב רחוקים וקבע עמדות ציבוריות תקיפות.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>הוויכוח על תכלית התורה: הלכה כתכלית מול פילוסופיה/קבלה כפסגה – ועיצוב עולם הישיבות.</t>
+          <t>רבנות ממלכתית גאה ועצמאית – שילוב הנהגה, פסיקה ואחריות לאומית.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם; הרשב"א; הריטב"א; הרמ"א; רש"י ורשב"ם</t>
+          <t>חכמי בבל; הרבנות הראשית; הרב מרדכי אליהו (תלמיד/השפעה)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4NKKrtI7AcK5wwQ0ejB7h1?si=jKMxNYqPRq6LQQm_5UMAbw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/6M7GqxrkmSgbLaowvUoIbM?si=YsGIvc_wSLu215jfLClMtg</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה וממלכתיות_ פועלו ומשנתו התורנית של הראשון לציון הרב יצחק נסים.docx</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה וממלכתיות: פועלו ומשנתו התורנית של הראשון לציון הרב יצחק נסים</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>מחזור ויטרי</t>
+          <t>הרב מאיר דוד כהנא</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1105 בקירוב</t>
+          <t>1932–1990</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>צרפת</t>
+          <t>ארה"ב → ישראל</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>ליטורגיה והלכה</t>
+          <t>אידיאולוגיה/פוליטיקה</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>מחזור ויטרי, רבנו שמחה מוויטרי</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>אנציקלופדיה הלכתית וליטורגית מבית מדרשו של רש״י, המשמרת את נוסח צרפת ומסורות אשכנז הקדומות.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>חיבור בין תפילה, הלכה, אגדה וחיי קהילה.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>רש״י, בעלי התוספות</t>
-        </is>
-      </c>
+          <t>זהות יהודית ומדינה, דמוקרטיה והלכה, ביטחון, גבולות שיח</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6xiWssuJyV4GypDbnlCpl0</t>
+          <t>https://open.spotify.com/episode/7aTrR9GQVvo3kwZrfhAuIj?si=_hnfvF-wT06Aqi3ZB0hU9w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>דוח מומחה_ הכל על פועלו ומשנתו התורנית של הרב מאיר כהנא – ניתוח רב-שכבתי של אידיאולוגיה ואקטיביזם.docx</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>דוח מומחה: הכל על פועלו ומשנתו התורנית של הרב מאיר כהנא – ניתוח רב-שכבתי של אידיאולוגיה ואקטיביזם</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>מימון בן יוסף (אב הרמב״ם)</t>
+          <t>הרב צבי הירש חיות (מהר"ץ חיות)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1110 בקירוב–1165/1170</t>
+          <t>1805–1855</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>קורדובה, מרוקו, ארץ ישראל ומצרים</t>
+          <t>גליציה</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה, מדע וחינוך</t>
+          <t>תורה שבעל פה, הגנה על המסורת, מתודולוגיה</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>רב מימון הדיין, איגרת הנחמה, רמב״ם, אנוסים</t>
+          <t>מנחת קנאות, תורת נביאים, אמנציפציה, גשר מסורת-מחקר</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>דיין ומנהיג שהיה החוליה המקשרת בין תור הזהב של ספרד לבין מהפכת הרמב״ם. הנהיג קהילות נרדפות, חיזק אנוסים ויצר בביתו הרמוניה בין תורה, מדע ושכל.</t>
+          <t>גדול תורה בגליציה שניסה לגשר בין מחקר זהיר לבין נאמנות מוחלטת לתורה שבעל פה, ובנה שפה של הגנה אינטלקטואלית על המסורת.</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>הנחת היסודות האנושיים, ההלכתיים והרעיוניים שמהם צמחה שיטת הרמב״ם.</t>
+          <t>גשר נאמן: פתיחות דעת המשרתת אמונה – לא מחליפה אותה.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>הר״י מיגאש; הרי״ף; הרמב״ם; רבי אברהם בן הרמב״ם; משה הדרעי</t>
+          <t>חת"ם סופר; שלמה קלוגר; נחמן קרוכמל (רנ"ק)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0N9JxxpJynDDTur8c5c0fd?si=H3uqUkfiSRSw3pYMwoKbnA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/7qsdQhzQdtrX80wVbwkfmZ</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית_ משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר.docx</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית: משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ספר הזוהר – מי כתב? רבי שמעון בר יוחאי או חיבור מאוחר? המחלוקת סביב מחבר הזוהר</t>
+          <t>הרב צבי הירש קלישר – ציונות דתית לפני הרצל</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1795–1874</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ארץ ישראל/ספרד; עולם הקבלה</t>
+          <t>פרוסיה / ארץ ישראל (חזון)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
+          <t>הגות ציונית-דתית והלכה</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>מסורת וביקורת; סמכות טקסטואלית; היסטוריה של הזוהר</t>
+          <t>גאולה בדרך הטבע, יישוב הארץ, חקלאות, קורבנות בלי בית, מדיניות</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>מחלוקת הייחוס של הזוהר לרשב"י מול טענות למחבר מאוחר, והשלכות השאלה על סמכות הקבלה ועל קריאת הטקסט.</t>
+          <t>פוסק שמרן שניסח תוכנית מעשית לגאולה: עלייה, חקלאות ובניין הארץ “מעט מעט”. הציע מהלכים הלכתיים נועזים (כגון דיון בחידוש קורבנות) ופעל מול נדבנים ומעצמות.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>מעבר ל'מי כתב': איך טקסט נעשה קנוני ומהי אחריות הפרשנות כשמסורת והיסטוריה מצטלבות.</t>
+          <t>גאולה קמעא קמעא: אחריות אנושית כמצווה – יוזמה לאומית ללא ניתוק מן ההלכה.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>רשב"י; ר' משה די ליאון; גרשם שלום; מחקר הקבלה</t>
+          <t>מונטיפיורי; רוטשילד; נפוליאון השלישי; 'דרישת ציון'</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>https://spotifycreators-web.app.link/e/HxZF2iS4yQb</t>
+          <t>https://open.spotify.com/episode/7CWcx0r0X5jRyzuRCBPBDh?si=gf7x1W04SsWqd3iA4wjpMQ</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית_ משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר.docx</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית: משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ספר הכוזרי</t>
+          <t>הרב צבי יהודה הכהן קוק</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1891–1982</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ספרד / אל־אנדלוס</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>הגות ואמונה</t>
+          <t>הגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הלוי, אמונה, סיני, ארץ ישראל</t>
+          <t>מרכז הרב, אתחלתא דגאולה, התיישבות</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>אחד מחיבורי היסוד של המחשבה היהודית, שנכתב בידי רבי יהודה הלוי בערבית יהודית. מציג הגנה מקורית על היהדות דרך ההיסטוריה, ההתגלות הלאומית והקשר בין עם, מצוות וארץ.</t>
+          <t>ממשיך דרכו של הראי"ה קוק ומנהיג דור התחייה של הציונות הדתית.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>ביסוס האמונה היהודית על זיכרון היסטורי לאומי והתגלות ציבורית, ולא רק על הוכחה פילוסופית מופשטת.</t>
+          <t>חיבור בין מדינת ישראל, לימוד תורה וגאולה.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הלוי; הרמב"ם; הרב קוק; ביאליק</t>
+          <t>הראי"ה קוק; הרב חנן פורת; הרב משה לוינגר</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0E55prQ6VaFsIXKSiCpDe3?si=XrQKU-Z0TgKEvgDDjH-MFQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/33CjfygeixWek05uscU4qM?si=zHwL0eT7QtWwuw1PHxvNJg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>רב אברהם יצחק הכהן קוק.docx</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>הם יצחק הכהן קוק: אנליזה מקיפה של מהפכת הקודש בתקופת התחייה</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>רבי אביגדור כ״ץ</t>
+          <t>הרב צדוק הכהן מלובלין – המיסטיקן האינטלקטואלי</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>1823–1900</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>איטליה, גרמניה ואוסטריה</t>
+          <t>ליטא / לובלין</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>הלכה והנהגה</t>
+          <t>חסידות והגות</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>חידושי תוספות</t>
+          <t>ספק כתנאי לתורה, תשובה, חטא וזכות, תורה שבעל פה, איזביצא</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>ממנהיגי יהדות אוסטריה ומחבר בין מסורות איטליה, אשכנז וצרפת.</t>
+          <t>עילוי ליטאי שנהפך לחסיד בעקבות מפגש עם ר׳ מרדכי יוסף מאיז׳ביצא. מציע תיאולוגיה שבה תורה שבעל‑פה היא התגלות מתמשכת דרך מאבק אנושי, וספק הוא תנאי לגילוי עמוק.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>בניית רצף מסורת באמצעות תלמידים וקהילות.</t>
+          <t>הנפילה כחלק מהמהלך: חטא ותשובה נקראים לאחור כחלק מרצון ה׳; הסכנה האמיתית היא ייאוש.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>המהר״ם מרוטנבורג</t>
+          <t>ר׳ מרדכי יוסף מאיז׳ביצא; הרב דסלר; הרב הוטנר</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0Gbt6DvaXHHA3NQUKn6gAe</t>
+          <t>https://open.spotify.com/episode/6DLhfveOXBJupYoYqgceWx?si=zrPEwB1LQjua2OW_BkVXPw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>הארת התודעה וסוד הצמצום האנושי_ פועלו, ביוגרפיית העומק ומשנתו התורנית של רבי צדוק הכהן מלובלין.docx</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>הארת התודעה וסוד הצמצום האנושי: פועלו, ביוגרפיית העומק ומשנתו התורנית של רבי צדוק הכהן מלובלין</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>רבי יהודה בן ברכיה</t>
+          <t>הרב קלמן שם טוב גפן</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>המאות ה־12–13</t>
+          <t>1856–1927</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>פרובאנס</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>הלכה, תלמוד ופירוש הרי״ף</t>
+          <t>קבלה, פילוסופיה ומדע</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>שיטת ריב״ב, הרי״ף, גאונים, רמב״ם</t>
+          <t>תורת הממדים</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>מחכמי פרובאנס שיצר פירוש רחב על הלכות הרי״ף. שיטתו שילבה פשט, ביקורת על הרי״ף, מסורת גאונים והשוואה לפסקי הרמב״ם.</t>
+          <t>הוגה שניסה ליצור סינתזה בין קבלה, מדע מודרני ופילוסופיה.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>הפיכת פרובאנס לגשר חי בין מסורת הגאונים, הרי״ף, הרמב״ם ובעלי התוספות.</t>
+          <t>המדע והתורה מתארים רבדים שונים של אותה מציאות.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>הרי״ף; בעל המאור; רב האי גאון; ר״י אבן גיאת; הרמב״ם; הרמב״ן; הרשב״א</t>
+          <t>הראי״ה קוק, הרצי״ה קוק</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/647NStP3Z8X3LRqObcCXUZ?si=KByF2c3MQAKtqw4L_2KQFg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/12f9H8UgJMaWzeIBegbaMu</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>משנתו התורנית, הגותו הפילוסופית ופועלו המדעי של הרב שם טוב גפן_ ניתוח אנליטי מקיף של איש אשכולות בפרשת הדרכים של המודרנה.docx</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>משנתו התורנית, הגותו הפילוסופית ופועלו המדעי של הרב שם טוב גפן: ניתוח אנליטי מקיף של איש אשכולות בפרשת הדרכים של המודרנה</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>רבי יוסף חיון (רי״ח)</t>
+          <t>הרב שמואל מוהליבר – מנהיג דתי ומבשר הציונות</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>מאה 15</t>
+          <t>1824–1898</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ליסבון, פורטוגל</t>
+          <t>מזרח אירופה / ארץ ישראל (מפעל היישוב)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>פרשנות מקרא/תיאולוגיה</t>
+          <t>מנהיגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>תורה מן השמים, דיוק לשוני, ספר דברים, פרשנות סמנטית</t>
+          <t>חיבת ציון, אחדות דתיים-חילונים, היתר מכירה, התיישבות</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>מנהיג קהילת ליסבון ומורו של האברבנאל. פיתח פתרון לשאלת 'דברים מפי עצמו' ועיקרון שאין כפל עניין בתנ״ך.</t>
+          <t>מנהיג חיבת ציון שהבין שהשיבה לארץ היא משימה מעשית. יצר גשר בין דתיים לחילונים, פעל עם רוטשילד להקמת מושבות, ותמך בהיתר מכירה בפולמוס השמיטה כדי להציל את ההתיישבות.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>משה ניסח נאומים, אך ה׳ הכתיב לו מילה במילה בעת כתיבת התורה; כל מילה במקרא ייחודית ואין 'נרדפות' סתמית.</t>
+          <t>ברית ציבורית רחבה כצורך גאולי: אחדות בין כוחות שונים בעם כדי לבנות מציאות.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>דון יצחק אברבנאל; קנפנטון; המלבי״ם (הקדמה רעיונית)</t>
+          <t>הרצל (כינויו בטקסט); הרב קוק (הספד); רוטשילד; מזכרת בתיה</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
+          <t>https://open.spotify.com/episode/5T2FtQnfoEkvsFnCYyFBcQ?si=B9g6mdr7TtqbzlQnC1gTMA</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>הרב שמואל מוהליבר.docx</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>הרב שמואל מוהליבר</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>רבי יצחק קנפנטון</t>
+          <t>חנה סנש</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1360–1463</t>
+          <t>1921–1944</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>קסטיליה; ספרד</t>
+          <t>בודפשט, הונגריה; נהלל; שדות ים; יוגוסלביה</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>למדנות תלמודית</t>
+          <t>ציונות, שליחות ושירה</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>דרכי התלמוד, גאון מקסטיליה</t>
+          <t>צנחני היישוב, ציונות, תפילה, הליכה לקיסריה, אלי אלי, שליחות, השואה, גבורה, נשים</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/2xytN0uGuTq03wNYWvusDO?si=GjQi6caQRZGdjDrWc8cX7w</t>
+          <t>משוררת, צנחנית וגיבורת היישוב שעלתה מהונגריה לארץ ישראל והצטרפה למשימת צניחה מעבר לקווי האויב באירופה. ביומניה ובשיריה חיברה בין זהות יהודית, תפילה, אחריות מוסרית ושליחות לאומית.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>רוחניות אמיתית אינה מסתגרת מן המציאות אלא מחייבת פעולה; תפילה, אחריות לעם ונכונות למעשה יכולות להשתלב בשליחות מוסרית אחת.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>קטרינה סנש, גיורא סנש, צנחני היישוב, קיבוץ שדות ים</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>פועלה, הגותה ומשנתה הרוחנית-תורנית של חנה סנש- ניתוח היסטורי, ספרותי ותיאולוגי.docx</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>פועלה, הגותה ומשנתה הרוחנית-תורנית של חנה סנש: ניתוח היסטורי, ספרותי ותיאולוגי</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>רבי משה די ליאון</t>
+          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1240–1305</t>
+          <t>1886–1929</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>קסטיליה, ספרד</t>
+          <t>גרמניה</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
+          <t>פילוסופיה יהודית מודרנית</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>ספר הזוהר, קבלת קסטיליה, גירונה, ספרות הסוד</t>
+          <t>כוכב הגאולה, התגלות, דיאלוג, יהדות ונצרות, תרגום תנ"ך, ALS</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>מגדולי המקובלים בקסטיליה במאה ה-13, שבידיו נתגלה (או נערך) ספר הזוהר. חיבר גם ספרי קבלה בעברית כ"שקל הקודש", ועמד במוקד המחלוקת ההיסטורית על קדמות הזוהר.</t>
+          <t>ב'כוכב הגאולה' מפרק את ה'כוליות' ומציע מבנה של אלוהים-אדם-עולם דרך בריאה/התגלות/גאולה. הקים Lehrhaus בפרנקפורט ותרגם תנ"ך עם בובר, תוך התמודדות עם ALS.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>העמדת ספר הזוהר במרכז ארון הספרים היהודי — הטקסט המכונן של תורת הסוד.</t>
+          <t>התגלות כדיבור ואהבה שמולידים אחריות; אמת נוצרת במפגש ולא במערכת מופשטת.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>רבי שמעון בר יוחאי (ייחוס הזוהר), מקובלי גירונה</t>
+          <t>מרטין בובר; Lehrhaus; עמנואל לוינס (השפעה מאוחרת)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5hjMOYSZfyk2PpvO1z7y60?si=xvtDucKGTcqSJ5rNgkG76A</t>
+          <t>https://open.spotify.com/episode/7EpaIjYgIJVmSWDAsXDI7g?si=u6IC097XQ-KpBRfRRIGqcg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>פרנץ רוזנצווייג.docx</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>פרנץ רוזנצווייג</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>רבי משה הדרשן מנרבונה</t>
+          <t>רבי משה חגיז – הקנאי הירושלמי שניסה להציל את היהדות מן הקריסה הפנימית</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>המאה ה-11</t>
+          <t>1671–1750</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>נרבונה</t>
+          <t>ירושלים; איטליה; אמסטרדם; אירופה</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>מדרש</t>
+          <t>פסיקה והנהגה קהילתית</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>ספר יסוד, בראשית רבתי</t>
+          <t>אחר שבתאות, פולמוס, סמכות חכמים, גבולות קבלה, השכלה, לקט הקמח</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>החכם שעיצב את עולם המדרש באירופה והשפיע עמוקות על רש"י.</t>
+          <t>חגיז פעל לאחר טראומת השבתאות כקנאי-אחראי להצבת גבולות מול מה שראה כהתפוררות המסורת. משבר אישי הוביל אותו להתמסר לכתיבה ולפולמוס, ולעימותים שהדהדו בקהילות אירופה. ב"לקט הקמח" ביקש לשרטט סדר מחודש ולהחזיר סמכות הלכתית מרכזית, גם במחיר של קיטוב ומחלוקת.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>שימור ועיבוד אוצרות מדרש קדומים בתוך פרשנות אירופית.</t>
+          <t>קנאות כאחריות: שרטוט גבולות כדי למנוע קריסה רוחנית אחרי שבתאות – במחיר גבוה.</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>רש"י; רבי נתן מרומי</t>
+          <t>נחמיה חיון; החכם צבי; הרמח"ל; ר' יונתן אייבשיץ</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1PpzvwnJnR9ssTIwkuP4Lj?si=6Muo4ngpS_yzlOrCWj4iKw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/2kCpBIWS1B2NtObhJemSdG?si=CHbvRGp1RkW_Lj5w4HGnsQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבי משה חגיז_ שומר חומות המסורת בעידן התמורות.docx</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבי משה חגיז: שומר חומות המסורת בעידן התמורות</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>262</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>רבי צדקיה בן אברהם העניו</t>
+          <t>הרב אפרים מקלעת־חמאד</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2151,54 +2620,69 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>בערך 1050–1150</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>איטליה</t>
+          <t>קלעת בן חמאד, צפון אפריקה</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>הלכה ורפואה</t>
+          <t>הלכה, נוסח ודקדוק</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>שיבולי הלקט</t>
+          <t>הרי"ף, דקדוק עברי, ביקורת נוסח, קירואן</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי איטליה, מחבר שיבולי הלקט ומגשר בין מסורות אשכנז ואיטליה.</t>
+          <t>מן הדמויות העמוקות שבין תקופת הגאונים לראשוני ספרד ופרובנס, 'תלמיד חבר' של הרי"ף. הגהותיו נטמעו בספר ההלכות, והוא שילב רגישות פילולוגית ודקדוקית בתוך הפסיקה.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>סידור ושימור המסורת ההלכתית מתוך ענווה ואחריות.</t>
+          <t>החדרת דיוק לשוני וביקורת נוסח ככלים הלכתיים מהותיים, מתוך נאמנות למסורת ואומץ אינטלקטואלי.</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>בעלי התוספות, בעל הטורים</t>
+          <t>הרי"ף; רבי שלמה אבן פרחון; הראב"ד; בעל המאור; הרמב"ן</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0zmmVvmiG4Wzj6H3D3wwK7</t>
+          <t>https://open.spotify.com/episode/5teJp1U9ghLdy4CXNAusRN?si=uqTLoA-PT_yqmv9eyGRw6g&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=88</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבי אפרים מקלעת חמאד_ מחקר היסטורי והלכתי מקיף.docx</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבי אפרים מקלעת חמאד: מחקר היסטורי והלכתי מקיף</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>רבנו חננאל בן חושיאל</t>
+          <t>הרמב"ן (רבי משה בן נחמן)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2208,54 +2692,69 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>מאה 11</t>
+          <t>1194–1270</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>קירואן (צפון אפריקה)</t>
+          <t>ספרד, ארץ ישראל</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>פירוש תלמוד/פסיקה</t>
+          <t>פרשנות, הלכה, קבלה</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
+          <t>ויכוח ברצלונה, פרשנות לתורה, תורת הסוד, עלייה לארץ</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
+          <t>פוסק, פרשן ומקובל ששילב את כל רבדי התורה, חידש את יישוב ירושלים ועמד באומץ מול הכנסייה.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
+          <t>שילוב פשט, דרש, סוד ופרשנות קבלית – ראיית הטבע כסדרה של ניסים נסתרים.</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
+          <t>הרמב"ם, בעלי התוספות, הר"ן</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
+          <t>https://open.spotify.com/episode/3ZjAqfQEp21lw1GXKibFGq</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>הרמב_ן_ ניתוח רב-ממדי של הגות, הלכה ומנהיגות במאה ה-13.docx</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>הרמב"ן: ניתוח רב-ממדי של הגות, הלכה ומנהיגות במאה ה-13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>רבנו יצחק בן יהודה ממגנצא</t>
+          <t>חכמי פרובנס – בין נרבון, בית דוד והמיסטיקה הראשונה: המרכז היהודי ששבר את המפה הרוחנית של ימי הביניים</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2265,54 +2764,69 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־11</t>
+          <t>המאות ה־11–13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>גרמניה</t>
+          <t>פרובנס; נרבון; דרום צרפת</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>הלכה ותלמוד</t>
+          <t>היסטוריה ותולדות</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>מגנצא, רש"י</t>
+          <t>הלכה ותלמוד, מפגש ספרד–אשכנז, נשיאות נרבון, קבלה מוקדמת, חסידות אשכנז, מוסדות</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>ראש ישיבת מגנצא ומורו המרכזי של רש"י, ממעצבי שיטת הלימוד האשכנזית.</t>
+          <t>פרובנס מתוארת כמרחב מפגש בין הלכה ספרדית שיטתית לדיאלקטיקה אשכנזית-צרפתית, וכמוקד מדיני-תורני סביב נרבון והמסורת הנשיאותית. מתוך המתח הזה נולדת קבלה מוקדמת בסינתזה עם חסידות אשכנז. הפרק מציג כיצד מרכז אזורי קטן שינה את המפה הרוחנית של ימי הביניים והכין קרקע להתפתחויות מאוחרות.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>שילוב בין דיוק טקסטואלי, מנהג ופסיקה.</t>
+          <t>מפגש מסורות כמנוע יצירה: סינתזה בין ספרד–אשכנז שמולידה מרכז הלכתי ומיסטי חדש.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>רבנו גרשום, רש"י</t>
+          <t>הראב"ד; הרז"ה; האחים הכהן; יצחק סגי נהור</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4tFSo5qQFWExTxQDDj1a8Q</t>
+          <t>https://open.spotify.com/episode/28wg8VCd8QFBLQiEa8y15f?si=ai8T1gHuSUulzXa6z02hwA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>אור הגנוז במדבר_ משנתו הקבלית והנהגתו הרוחנית של המקובל רבי ברוך שפירא זצ_ל.docx</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>אור הגנוז במדבר: משנתו הקבלית והנהגתו הרוחנית של המקובל רבי ברוך שפירא זצ"ל</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
+          <t>מהפכת הרמב"ם, תגובת ספרד ומורשת הרמ"א – הקרב על נשמתה של התורה</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2322,54 +2836,69 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1100–1171</t>
+          <t>ימי הביניים–המאה ה־16</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>צרפת (אשכנז)</t>
+          <t>ספרד; אשכנז; קרקוב</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>תלמוד ושיטה למדנית</t>
+          <t>מוסר והגות</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>תוספות, שתי שקיעות, תפילין, תקנות, מסעות הצלב</t>
+          <t>פילוסופיה, סדרי לימוד, הלכה, מטאפיזיקה, קבלה, עולם הישיבות, סמכות</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>נכדו של רש״י שבנה את שיטת בעלי התוספות: לא מוותרים על סתירות – מחברים סוגיות וגשרים. במקביל היה מנהיג קהילה בתקופת מסעי הצלב ותקן תקנות חברתיות.</t>
+          <t>דרמה אינטלקטואלית על מטרת לימוד התורה: הרמב"ם מציב את ההשגה המטאפיזית כפסגה, וחכמי ספרד מדגישים את מרכזיות הגמרא ולעיתים את הקבלה. הרמ"א מעצב מודל שבו לימוד הלכה ותלמוד הם עצמם התכלית ובכך מניח יסודות לעולם הישיבות. הפרק מצביע על השלכות לשאלת סמכות תורה שבעל-פה.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>נאמנות קשוחה לנוסח הגמרא (“בספרים אל ימחק”) שמכריחה עומק, דיוק וחילוקים – ומייצרת לימוד יוצר.</t>
+          <t>הוויכוח על תכלית התורה: הלכה כתכלית מול פילוסופיה/קבלה כפסגה – ועיצוב עולם הישיבות.</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>בעלי התוספות; רש״י; מנהג זמן רבנו תם</t>
+          <t>הרמב"ם; הרשב"א; הריטב"א; הרמ"א; רש"י ורשב"ם</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ?si=o5kksAmaQNiRkBHxN8CVpQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/4NKKrtI7AcK5wwQ0ejB7h1?si=jKMxNYqPRq6LQQm_5UMAbw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה ומסורה_ פועלו ומשנתו התורנית של רבי מאיר הלוי אבולעפיה (הרמ_ה) בתקופת המעבר של יהדות ספרד.docx</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה ומסורה: פועלו ומשנתו התורנית של רבי מאיר הלוי אבולעפיה (הרמ"ה) בתקופת המעבר של יהדות ספרד</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>292</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>שמואל בן יצחק</t>
+          <t>מימון בן יוסף (אב הרמב״ם)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2379,168 +2908,213 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1190–1256</t>
+          <t>1110 בקירוב–1165/1170</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ברצלונה, ספרד</t>
+          <t>קורדובה, מרוקו, ארץ ישראל ומצרים</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>הלכה ודיני ממונות</t>
+          <t>הלכה, הנהגה, מדע וחינוך</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>רבנו שמואל הסרדי, ספר התרומות, ממונות, משפט עברי</t>
+          <t>רב מימון הדיין, איגרת הנחמה, רמב״ם, אנוסים</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי ספרד במאה ה־13 ואחד ממעצבי המשפט העברי. חיבורו 'ספר התרומות' סידר לראשונה באופן שיטתי תחום שלם של דיני ממונות.</t>
+          <t>דיין ומנהיג שהיה החוליה המקשרת בין תור הזהב של ספרד לבין מהפכת הרמב״ם. הנהיג קהילות נרדפות, חיזק אנוסים ויצר בביתו הרמוניה בין תורה, מדע ושכל.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>הפיכת ההלכה המשפטית לשפה חיה, נגישה ושיטתית עבור דיין, סוחר וקהילה כלכלית ממשית.</t>
+          <t>הנחת היסודות האנושיים, ההלכתיים והרעיוניים שמהם צמחה שיטת הרמב״ם.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ן; רבי נתן בן מאיר מטרינקטיי; הטור; שולחן ערוך</t>
+          <t>הר״י מיגאש; הרי״ף; הרמב״ם; רבי אברהם בן הרמב״ם; משה הדרעי</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5Cdc9RvxyriLFWPFMRfciK?si=P9JIX4Q4TCCtqmGdnswLcA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/0N9JxxpJynDDTur8c5c0fd?si=H3uqUkfiSRSw3pYMwoKbnA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>משנתו התורנית, פועלו הציבורי ומורשתו של רב מימון הדיין_ חוליה מקשרת בין דורות.docx</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>משנתו התורנית, פועלו הציבורי ומורשתו של רב מימון הדיין: חוליה מקשרת בין דורות</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>המהר"י מינץ</t>
+          <t>רבי משה הדרשן מנרבונה</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1405–1508</t>
+          <t>המאה ה-11</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>גרמניה ואיטליה / פדובה</t>
+          <t>נרבונה</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>הלכה והנהגה קהילתית</t>
+          <t>מדרש</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>פדובה, רנסנס, פסיקה אשכנזית, פורים</t>
+          <t>ספר יסוד, בראשית רבתי</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>רב, פוסק וזקן הדור שהעביר את מרכז התורה האשכנזי אל איטליה של הרנסנס. הנהיג את יהדות פדובה ושילב נאמנות למסורת עם התמודדות הלכתית יצירתית.</t>
+          <t>החכם שעיצב את עולם המדרש באירופה והשפיע עמוקות על רש"י.</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>עיצוב הנהגה הלכתית השומרת על סמכות המסורת בתוך מציאות רנסנסית פתוחה ומשתנה, תוך איזון בין תקיפות לגמישות.</t>
+          <t>שימור ועיבוד אוצרות מדרש קדומים בתוך פרשנות אירופית.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>מהר"ם פאדובה; הרמ"א; אליהו דלמדיגו; דון יצחק אברבנאל</t>
+          <t>רש"י; רבי נתן מרומי</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2UFLK856gB3r5MDYUiO2mV?si=GMJjiZMzQjK1asCeXsrPzg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/1PpzvwnJnR9ssTIwkuP4Lj?si=6Muo4ngpS_yzlOrCWj4iKw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבינו מנוח מנרבונה_ פרשנות, קודיפיקציה ומסורת פרובאנסאלית.docx</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבינו מנוח מנרבונה: פרשנות, קודיפיקציה ומסורת פרובאנסאלית</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>291</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>המהרי״ק (רבי יוסף קולון)</t>
+          <t>שמואל בן יצחק</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1420–1480 בקירוב</t>
+          <t>1190–1256</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>צרפת ואיטליה</t>
+          <t>ברצלונה, ספרד</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>הלכה ומנהג</t>
+          <t>הלכה ודיני ממונות</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>שו״ת מהרי״ק</t>
+          <t>רבנו שמואל הסרדי, ספר התרומות, ממונות, משפט עברי</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>מגדולי הפוסקים שהעניקו למנהג הקהילתי מעמד מרכזי בפסיקה.</t>
+          <t>מגדולי חכמי ספרד במאה ה־13 ואחד ממעצבי המשפט העברי. חיבורו 'ספר התרומות' סידר לראשונה באופן שיטתי תחום שלם של דיני ממונות.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>המנהג הוא חלק מהתורה החיה של עם ישראל.</t>
+          <t>הפיכת ההלכה המשפטית לשפה חיה, נגישה ושיטתית עבור דיין, סוחר וקהילה כלכלית ממשית.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>הרמ״א, תרומת הדשן</t>
+          <t>הרמב״ן; רבי נתן בן מאיר מטרינקטיי; הטור; שולחן ערוך</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5V8efc6gWfwrgHLR6E1AQZ</t>
+          <t>https://open.spotify.com/episode/5Cdc9RvxyriLFWPFMRfciK?si=P9JIX4Q4TCCtqmGdnswLcA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>דמותו, מעמדו ומשנתו ההלכתית-מדעית של רבי יצחק חזקיה למפרונטי בעיני חכמי ישראל.docx</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>דמותו, מעמדו ומשנתו ההלכתית-מדעית של רבי יצחק חזקיה למפרונטי בעיני חכמי ישראל</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
+          <t>המהר"י מינץ</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2550,1846 +3124,2045 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1858–1936</t>
+          <t>1405–1508</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>רוגצ'וב/דווינסק</t>
+          <t>גרמניה ואיטליה / פדובה</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
+          <t>הלכה והנהגה קהילתית</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
+          <t>פדובה, רנסנס, פסיקה אשכנזית, פורים</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
+          <t>רב, פוסק וזקן הדור שהעביר את מרכז התורה האשכנזי אל איטליה של הרנסנס. הנהיג את יהדות פדובה ושילב נאמנות למסורת עם התמודדות הלכתית יצירתית.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
+          <t>עיצוב הנהגה הלכתית השומרת על סמכות המסורת בתוך מציאות רנסנסית פתוחה ומשתנה, תוך איזון בין תקיפות לגמישות.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
+          <t>מהר"ם פאדובה; הרמ"א; אליהו דלמדיגו; דון יצחק אברבנאל</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
+          <t>https://open.spotify.com/episode/2UFLK856gB3r5MDYUiO2mV?si=GMJjiZMzQjK1asCeXsrPzg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>רבי יהודה הלוי מינץ (מהר_י מינץ).docx</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>רבי יהודה הלוי מינץ (מהר"י מינץ)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>הרב יעקב ששפורטש</t>
+          <t>אליאן עמדו לוי־ולנסי</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1610–1698</t>
+          <t>1919–2006</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>צפון אפריקה, אירופה המערבית (אמסטרדם, לונדון, המבורג, ליבורנו)</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>פולמוס/הנהגה</t>
+          <t>מחשבת ישראל, מקרא, פסיכואנליזה</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+          <t>אסכולת פריז, אברהם, הנני, פרשנות קיומית, נשים</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>הוגה עמוקה שחיברה בין מקרא, פילוסופיה ופסיכואנליזה. ראתה באברהם דמות קיומית של אחריות והיסטוריה.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>הישות האברהמית – האדם כנוכחות מוסרית היוצרת היסטוריה דרך אמירה 'הנני'.</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>לוינס, מניטו, נהר</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/09JfLsbxRNjLhC969SxOPd?si=zTKhNkZ7T8qiI1akCdsAvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/7DJX0cnVGFtntXiLnNdbpj</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>אליענה אמדו לוי-ולנסי_ ניתוח רב-תחומי של דיאלוג, זהות וקיום יהודי.docx</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>אליענה אמדו לוי-ולנסי: ניתוח רב-תחומי של דיאלוג, זהות וקיום יהודי</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>רבי דוד פארדו</t>
+          <t>האדמו"ר מפיאסצ'נה (1889–1942) – קודש בתוך החורבן: תורה פסיכולוגית, אמונה ועמידה בגטו ורשה</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1719–1792</t>
+          <t>1889–1942</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ונציה, הבלקן, ירושלים</t>
+          <t>פולין; גטו ורשה</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, משנה ותוספתא</t>
+          <t>חסידות; חינוך</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>חסדי דוד, תוספתא</t>
+          <t>אמונה בשבר; פסיכולוגיה רוחנית; חינוך; גטו ורשה</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>מגדולי פרשני התוספתא, שהחזיר את לימודה למרכז בית המדרש באמצעות פירושו 'חסדי דוד'.</t>
+          <t>דיוקן של הרבי מפיאסצ'נה כמחנך והוגה: עומק חסידי, הבנת נפש, ואומץ להמשיך ללמד ולכתוב בתוך גטו ורשה.</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>דיוק טקסטואלי לצד מחויבות עמוקה למסורת.</t>
+          <t>קדושה שמסרבת לברוח: עבודת ה' נבנית מתוך אמת פנימית גם כשהמציאות קורסת.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>פרופ' שאול ליברמן</t>
+          <t>חסידות פולין; כתבי דרשות מן השואה; תנועת המוסר</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0gNG3pg6tSS0rP12co2dsU</t>
+          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>דו_ח מומחה_ פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ_נה.docx</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>דו"ח מומחה: פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ'נה</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>רבי חיים בן עטר (בעל אור החיים)</t>
+          <t>הרבי מפיאסצ'נה</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1696–1743</t>
+          <t>1889–1943</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>סאלי, מרוקו; ליבורנו; ירושלים</t>
+          <t>פולין</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>פרשנות התורה, הלכה וקבלה</t>
+          <t>חסידות וחינוך</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>אור החיים, מדרש כנסת ישראל, כבה נר המערבי, גאולת אחישנה ובעתה</t>
+          <t>אש קודש, חובת התלמידים</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי מרוקו במאה ה־18, פרשן, פוסק ומקובל. חיבר את "אור החיים" המשלב פשט, רמז, דרש וסוד, והקים בירושלים את ישיבת "כנסת ישראל". הבעל שם טוב ספד לו במות: "כבה נר המערבי".</t>
+          <t>אדמו"ר שחשף את עומק הנשמה גם בתוך אימי השואה.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>שילוב שיטתי של ארבעת רבדי הפרשנות (פרד"ס) בפירוש אחד, לצד תפיסת גאולה המבחינה בין "אחישנה" מהירה ל"בעתה" הדרגתית.</t>
+          <t>הפיכת המשבר וההסתר למקום של עבודת ה' פנימית.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>הבעל שם טוב, ועד כנסת ישראל בליבורנו</t>
+          <t>גטו ורשה; בני מחשבה טובה</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3HwpG5NALcGOQmbs1wwR4N?si=2otS_OCBTYaCbDWu2xZarQ</t>
+          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>דו_ח מומחה_ פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ_נה.docx</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>דו"ח מומחה: פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ'נה</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>רבי ישראל יהושע טרונק (ישועות מלכו)</t>
+          <t>הרבנית בת שבע אסתר קניבסקי</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1820–1893</t>
+          <t>1932–2011</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>פולין</t>
+          <t>ירושלים; בני ברק</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>הלכה, ציונות דתית</t>
+          <t>חסד, תפילה והנהגה רוחנית לנשים</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>היתר מכירה, יישוב הארץ</t>
+          <t>בית רשב״ם, חסד, תפילה, תהילים, עצה וברכה, צניעות, נשים</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>פוסק גדול שתמך בהתיישבות וב"היתר מכירה" מתוך ראיית הגאולה המעשית.</t>
+          <t>בתו של הרב יוסף שלום אלישיב, נכדת רבי אריה לוין ורעיית הרב חיים קניבסקי. ביתה בבני ברק הפך לכתובת לאלפי נשים שביקשו עצה, תפילה וחיזוק, ולמוקד של צדקה, סיוע למשפחות וליווי חולים.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>עבודת הארץ כחלק מהמצווה והגאולה</t>
+          <t>השפעה רוחנית אינה תלויה בתפקיד רשמי: הקשבה אישית, חסד ואמונה פשוטה יכולות להפוך בית פרטי למרכז של תקווה ואהבת ישראל.</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>קלישר; רבני ארץ ישראל; פוסקי הדור</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5CjFGW61SRKSx3ScmazcV1</t>
+          <t>הרב יוסף שלום אלישיב (אביה), רבי אריה לוין (סבה), הרב חיים קניבסקי (בעלה), הרבנית לאה קולדצקי (בתה)</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>מורשת הרבנית קנייבסקי_ כוח התפילה, התהילים והפרשת החלה.docx</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>מורשת הרבנית קנייבסקי: כוח התפילה, התהילים והפרשת החלה</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>רבי משה דוד ואלי (הרמ״ד ואלי)</t>
+          <t>שד"ל – הלוחם האחרון של היהדות הרגשית מול כיבוש השכל היווני</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1697–1777</t>
+          <t>1800–1865</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>פדובה, איטליה</t>
+          <t>פאדובה; איטליה</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>קבלה/פרשנות מקרא</t>
+          <t>פרשנות מקרא ולשון</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>פשוטו מכוון אל סודו, רמח״ל, כתבים גנוזים</t>
+          <t>חכמת ישראל, פרשנות מקרא, פילולוגיה, רציונליזם, אמונה, חמלה, ביקורת יוון</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>רופא מוסמך וחבר קרוב של הרמח״ל. פיתח שיטת פרשנות: הפשט עצמו רומז לסוד בכל שינוי דקדוקי/לשוני.</t>
+          <t>שד"ל טען שהיהדות האותנטית היא דת של חמלה ואמונה ולא של שכל קר, ובנה מפעל מדעי (לשון, מקרא, ביקורת טקסט) כדי להגן על חיות המסורת. הוא נאבק בחוגי חכמת ישראל שנראו לו כמי שהופכים יהדות לארכיאולוגיה, ותקף את הכנסת "חכמת יוון" ליהדות. כאב חייו חיזק אצלו את עליונות האמונה והמעשה הטוב.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>מיפוי לשון המקרא למבנה הספירות; דחיית חכמות חיצוניות כתחליף; מפעל פירושים עצום שנחשף רק בדורות האחרונים.</t>
+          <t>הגנה על יהדות של חמלה ואמונה מול רציונליזם קר – באמצעות מחקר מקרא ולשון.</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>הרמח״ל; חוג פדובה; הדפסת כתבים בדורנו</t>
+          <t>חכמת ישראל; רמב"ם; ראב"ע; שפינוזה</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6Sc3CiYpTfV68Ke8SueReD</t>
+          <t>https://open.spotify.com/episode/03tAgaC9jfaMhMJ2rvW4uF?si=cgIj0F37SiKtDyDT85ZqKA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי_ עיצוב היהדות בעידן המשבר והשיקום(1).docx</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי: עיצוב היהדות בעידן המשבר והשיקום</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>רבי רפאל עמנואל חי ריקי</t>
+          <t>שושלת אבוחצירא</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1687–1743</t>
+          <t>המאה ה־19–20</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>איטליה וירושלים</t>
+          <t>מרוקו, ארץ ישראל</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>קבלה ופרשנות</t>
+          <t>קבלה, הנהגה, פיוט</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>משנת חסידים, יושר לבב, קבלת האר"י</t>
+          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>מקובל, פייטן ופרשן משנה, מן הדמויות הבולטות בקבלת איטליה.</t>
+          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>שילוב קבלת האר"י עם הוראה שיטתית וספרות הלכתית-קבלית.</t>
+          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>האר"י; הרש"ש; האור החיים</t>
+          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3Foy6VcyWU352VPpw1z1cp?si=jaoMkKODSduL9jAf58zdww</t>
+          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>רבי יעקב אבוחצירא_ האביר יעקב בראי הדורות.docx</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>רבי יעקב אבוחצירא: האביר יעקב בראי הדורות</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>רבי שבתאי הכהן (הש"ך)</t>
+          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1622–1663</t>
+          <t>המאה ה־19 (פרסום 1843)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>פולין</t>
+          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>הלכה, חושן משפט, ביקורת מקורות</t>
+          <t>מחשבת ישראל (קבלה)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>שפתי כהן, יורה דעה, תקפו כהן, מחלוקת</t>
+          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>פוסק גאון שדרש פתיחה מחודשת של ההלכה, עימת את המקובל, חידש בעיון, וספריו הפכו יסוד ללימוד ולפסיקה עד היום.</t>
+          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>הלכה כעיון פתוח ולא כקובץ סגור; עקרונות חדשניים בדיני ממונות וספקות.</t>
+          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>הט"ז, מגיני שלמה, מגלה עמוקות</t>
+          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0zeTxQVV4ZhQFYYST2sO12</t>
+          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE?si=N2J3HnklTRW2Gm-BmT4SFA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>אדולף פרנק בספרו _הקבלה_.docx</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>אדולף פרנק בספרו "הקבלה"</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>אליאן עמדו לוי־ולנסי</t>
+          <t>בת שבע</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>המלכים</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1919–2006</t>
+          <t>תקופת דוד ושלמה</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>צרפת</t>
+          <t>ירושלים; ממלכת ישראל</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל, מקרא, פסיכואנליזה</t>
+          <t>מלכות, הנהגה וחכמה</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>אסכולת פריז, אברהם, הנני, פרשנות קיומית, נשים</t>
+          <t>דוד המלך, שלמה המלך, נתן הנביא, אם המלך, אשת חיל, משלי, משפט צדק, נשים</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>הוגה עמוקה שחיברה בין מקרא, פילוסופיה ופסיכואנליזה. ראתה באברהם דמות קיומית של אחריות והיסטוריה.</t>
+          <t>אשת דוד ואמו של שלמה, שבספר מלכים מתגלה כדמות מדינית נחושה: היא פועלת עם נתן הנביא להבטחת המלכת שלמה, ולאחר מכן זוכה למעמד ״אם המלך״. במסורת חז״ל היא מזוהה עם אמו של למואל המוכיחה את בנה על אחריות המלכות.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>הישות האברהמית – האדם כנוכחות מוסרית היוצרת היסטוריה דרך אמירה 'הנני'.</t>
+          <t>הכתר אינו זכות בלבד אלא אחריות מוסרית; בת שבע מייצגת את הכוח להציב גבולות למלך ולדרוש ממנו צדק, משמעת עצמית ודאגה לחלשים.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>לוינס, מניטו, נהר</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7DJX0cnVGFtntXiLnNdbpj</t>
-        </is>
-      </c>
+          <t>דוד המלך, שלמה המלך, נתן הנביא, אדוניהו בן חגית</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>האדמו"ר מפיאסצ'נה (1889–1942) – קודש בתוך החורבן: תורה פסיכולוגית, אמונה ועמידה בגטו ורשה</t>
+          <t>צרויה</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>המלכים</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1889–1942</t>
+          <t>תקופת דוד המלך</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>פולין; גטו ורשה</t>
+          <t>בית לחם; ממלכת דוד</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>חסידות; חינוך</t>
+          <t>בית דוד, משפחה ומלוכה</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>אמונה בשבר; פסיכולוגיה רוחנית; חינוך; גטו ורשה</t>
+          <t>דוד המלך, יואב, אבישי, עשהאל, בני צרויה, הנהגה, גבורה, מלכות, נשים</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>דיוקן של הרבי מפיאסצ'נה כמחנך והוגה: עומק חסידי, הבנת נפש, ואומץ להמשיך ללמד ולכתוב בתוך גטו ורשה.</t>
+          <t>אחותו של דוד המלך ובתו של ישי, ששמה נשמר במקרא בעיקר דרך שלושת בניה - יואב, אבישי ועשהאל. הייחוס החוזר של הבנים דווקא לאמם הפך את צרויה לסמל משפחתי המזוהה עם כוח, גבורה ונאמנות לבית דוד.</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>קדושה שמסרבת לברוח: עבודת ה' נבנית מתוך אמת פנימית גם כשהמציאות קורסת.</t>
+          <t>המתח בין דוד לבין בני צרויה ממחיש את הצורך והסכנה שבחיבור בין חסד לכוח: המלכות זקוקה לעוצמה צבאית, אך גם לריסון מוסרי ולהנהגה רוחנית.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>חסידות פולין; כתבי דרשות מן השואה; תנועת המוסר</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ</t>
-        </is>
-      </c>
+          <t>דוד המלך, ישי, יואב בן צרויה, אבישי בן צרויה, עשהאל בן צרויה</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>האדמו״ר מקאליב (רבי מנחם מנדל טאוב)</t>
+          <t>בן סירא</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>בית שני</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1923–2019</t>
+          <t>סביב 190 לפנה״ס</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>הונגריה וישראל</t>
+          <t>ירושלים; מצרים (תרגום/תוספות הנכד)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>חסידות, זיכרון השואה והלכה</t>
+          <t>חכמה ומוסר</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>קול מנחם, שמע ישראל</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>ניצול שואה ומנהיג חסידי שהקדיש את חייו להנצחת הנספים ולהפצת תורה ואמונה.</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>הפיכת הזיכרון והכאב לכוח של בניין רוחני.</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>חסידות קאליב</t>
-        </is>
-      </c>
+          <t>ספרות בית שני, מוסר ודרך ארץ, גבולות קאנון, השפעה חז"לית</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2RfVxXD6TIynHVoCEcKPJn</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/3u5udRWI84FVJ3OsOBBbPF?si=ek7V_WzPS7OadSPOZSU-VA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>האדר״ת (רבי אליהו דוד רבינוביץ'-תאומים)</t>
+          <t>שמעון כיפא – מרטיר נוצרי או צדיק נסתר ששלחו חכמי ישראל?</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>בית שני</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1843–1905</t>
+          <t>המאות הראשונות לספירה</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ליטא וירושלים</t>
+          <t>ארץ ישראל; רומא; ראשית הנצרות</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>הלכה, מוסר והנהגה ציבורית</t>
+          <t>מסורת ופולמוס</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>סדר אליהו, נפש דוד</t>
+          <t>יהדות–נצרות, מסורות אזוטריות, זהות, פולמוס, ליטורגיה, ט' בטבת</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>רבה של פוניבז', מיר וירושלים, ומחותנו של הראי״ה קוק.</t>
+          <t>הפרק מציג את הפער בין המסורת הנוצרית על פטרוס לבין מסורות יהודיות המציירות את שמעון כיפא כשליח נסתר שנועד ליצור הפרדה בין יהדות לנצרות כדי למנוע שפיכות דמים והתבוללות. לפי הסיפור, הוא עיצב מנהגים ותיאולוגיה שמרחיקים מן היהדות ובמקביל למד תורה בסתר. מוצגים גם ייחוסים ליטורגיים ומסורות סביב צום ט' בטבת.</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>גדלות בתורה מחייבת אחריות ציבורית ודוגמה אישית.</t>
+          <t>מסורות כמנגנון זהות: סיפור 'שליח נסתר' שמפרש פילוג דתי כצעד הגנתי של הקהילה.</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>הראי״ה קוק, רבי שמואל סלנט</t>
+          <t>ספר חסידים; אוצר המדרשים; תולדות ישו</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7zHC1A3dQMNYpbYXahsYQd</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/4tu43oeL4qVdXGKzX2025J?si=G3-56Xu3TxKoDiSCHX9gEA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>הלל צייטלין (1871–1942) – פילוסוף יהודי בין ניטשה לחסידות, שנרצח בשואה</t>
+          <t>ילתא</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אמוראים</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1871–1942</t>
+          <t>המאה ה־3–4 לספירה</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>פולין; מזרח אירופה</t>
+          <t>בבל</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>מחשבה</t>
+          <t>הלכה, הנהגה ומעמד נשים</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>מודרנה יהודית; אקזיסטנציאליזם; חסידות; משבר אמונה</t>
+          <t>רב נחמן, עולא, רבה בר בר חנה, היתר ואיסור, כוס של ברכה, 400 חביות יין, נשים</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>הלל צייטלין: פילוסוף יהודי בין ניטשה לחסידות, מבקר תרבות שחוזר לעומק רוחני; נרצח בשואה.</t>
+          <t>בת למשפחת ראש הגולה ורעייתו של רב נחמן, מן הדמויות הנשיות הבולטות בתלמוד. היא מביעה רעיונות הלכתיים מקוריים, עומדת על דעתה מול חכמים, פונה לבירור הלכתי נוסף בעת הצורך ואף מייעצת לבעלה בענייני הנהגה.</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>החיפוש עצמו הוא עבודת ה': להפוך ספק ומודרניות למנוע של תשובה וחידוש רוחני.</t>
+          <t>עולם ההלכה כולל לא רק איסורים אלא גם מרחב של היתר, עונג וקדושה; ילתא מגלמת עצמאות אינטלקטואלית, מעמד ציבורי ונוכחות נשית פעילה בעולם האמוראי.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>ניטשה; בובר; ברנר; חסידות חב"ד; ספרות יהודית מודרנית</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>https://spotifycreators-web.app.link/e/VKh6sMX4yQb</t>
-        </is>
-      </c>
+          <t>רב נחמן, עולא, רבה בר בר חנה, רב יצחק בריה דרב יהודה</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>הרב אברהם יהושע השל – הגות ומעורבות מוסרית</t>
+          <t>רבי חייא הגדול</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אמוראים</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1907–1972</t>
+          <t>המאה ה־2–3 לספירה</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>פולין / ארה"ב</t>
+          <t>בבל, טבריה</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>הגות יהודית ואתיקה ציבורית</t>
+          <t>תורה שבעל פה, חינוך</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>השבת ארמון בזמן, נבואה, פליאה, זכויות אזרח, דיאלוג יהודי-נוצרי</t>
+          <t>שכחת התורה, תוספתא, מסירות</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>הוגה שחיבר חסידות ופילוסופיה עם אתיקה ציבורית. כתב 'השבת' ו'הנביאים', פעל בזכויות האזרח, וצעד לצד מרטין לותר קינג – 'תפילה עם הרגליים'.</t>
+          <t>הציל את התורה משכחה בפעולה מעשית כוללת. שילב עמל גשמי ורוחני כדי להעביר מסורת.</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>קדושת הזמן והפליאה כמנוע אמונה; אחריות מוסרית כחלק בלתי נפרד מעבודת ה'.</t>
+          <t>תורה נשמרת במעשה. אחריות אישית להעברה דורית.</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>מרטין לותר קינג; JTS; דיאלוג יהודי-נוצרי (נוסטרה אטאטה)</t>
+          <t>רבי יהודה הנשיא, רבי אושעיה</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/63Q7RdapehdnH3FCLVMrBy?si=DujHYLYPTUmSckrnlOofCQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/4MI4LUL2FI4WeVtEdPZS5F</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>הרב אברהם יצחק הכהן קוק – החזון שאיחד קודש וחול</t>
+          <t>אברהם בר חייא</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1865–1935</t>
+          <t>המאה ה-12</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ארץ ישראל</t>
+          <t>ברצלונה</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית והלכה</t>
+          <t>מדע, פילוסופיה</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>קודש וחול, תשובה היסטורית, ציונות, היתר מכירה, מרכז הרב</t>
+          <t>בר חייא, פילוסופיה, מדע יהודי, מתמטיקה</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>הראי"ה קוק ראה במודרנה תהליך אלוהי ובציונות החילונית תנועת תשובה עמוקה. חיפש אחדות בין ניגודים, דיבר על התפתחות, והנהיג הלכתית-לאומית מתוך אחריות ליישוב.</t>
+          <t>היהודי הראשון שכתב מדע בעברית והשפיע על תרגום חכמת המזרח לאירופה.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>האמת מתגלה במתח בין ניגודים: “הישן יתחדש והחדש יתקדש” – איחוד כוחות במקום מחיקה.</t>
+          <t>שילוב בין תורה, מדע ופילוסופיה; תרגום חכמה כללית לעברית.</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>חלוצים; ישיבת 'מרכז הרב'; פולמוס ההיתר בשמיטה</t>
+          <t>פיבונאצ'י, חכמי ספרד</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/19vVkCaNfYWm6AlvbjbkRe?si=Y2-7mNX9QnCXzxz32MKpgA</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/3FAGqYdzyMQbyPbon3KYoC</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>הרב חיים דרוקמן – מנהיג ציונות דתית בדורנו</t>
+          <t>הראב"ן</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1932–2022</t>
+          <t>1090–1170 בקירוב</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>מגנצא</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות וחינוך</t>
+          <t>הלכה והיסטוריה</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>בני עקיבא, ישיבות הסדר, גיור, הנהגה ציבורית, אחדות</t>
+          <t>גזרות תתנ"ו</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>ניצול שואה שהפך למנהיג מרכזי בציונות הדתית: ראש מוסדות אור עציון, מנהיג בני עקיבא ונשיא ישיבות ההסדר. נשא באחריות למערך הגיור הממלכתי מתוך אהבת ישראל.</t>
+          <t>החכם שתיעד את החורבן ובנה מחדש את יהדות אשכנז.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>הנהגה אחראית שמחזיקה תורה-צבא-מדינה יחד, עם דגש על אחדות ואהבת אדם.</t>
+          <t>הפיכת זיכרון החורבן ליסוד של בנייה רוחנית.</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>הרב צבי יהודה קוק; מוסדות אור עציון; מערך הגיור</t>
+          <t>רבנו תם; הרשב"ם; הרא"ש</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1j4SgDhb3vWdY3gvTjv3oq?si=67O0wVDkTsa2b7zRpBFQmQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=128</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/5QGbbhxhb2hremjTS5I9E8?si=wQyrfYb9SgeVnHb998KX6w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודא ליאון אשכנזי (מניטו)</t>
+          <t>הרד״ק</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1922–1996</t>
+          <t>1160–1235</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>אלג'יריה → צרפת → ישראל</t>
+          <t>פרובאנס</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל, קבלה, זהות לאומית</t>
+          <t>מקרא ודקדוק</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>אסכולת פריז, לוינס, שושני, עברי/יהודי, צמצום כמוסר, תחייה</t>
+          <t>ספר השורשים, ספר המכלול</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>הוגה וקבליסט שחיבר בין מסורת צפון אפריקה, שיח אינטלקטואלי צרפתי ותורת ארץ ישראל; ניסח תורת זהויות והעמיד שפה חדשה של תחייה.</t>
+          <t>מגדולי פרשני המקרא והמדקדקים, ממעצבי דרך הפשט בלימוד התנ״ך.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>זהות 'עברי' כשלב תודעתי-לאומי שמאחד קודש וחול, משפחה ועם, מוסר והיסטוריה.</t>
+          <t>הבנת לשון הקודש כמפתח להבנת התורה.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>עמנואל לוינס; אנדרה נהר; יעקב גורדין; מר שושני; הרב צבי יהודה קוק; הרב אורי שרקי</t>
+          <t>רבי יוסף קמחי, הרמב״ם</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6vCbxdldNDpdncGxSjvAyD</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/7t7Mwzw5zr9XQ4uPrDcKcz</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודה אלקלעי – תשובה שהופכת לתוכנית לאומית</t>
+          <t>הריצב״א</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1798–1878</t>
+          <t>המאה ה־12–13</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>הבלקן</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית</t>
+          <t>תלמוד, תוספות וסוד</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>תשובה כללית, שיבה לארץ, דיפלומטיה, שפה עברית, אחדות</t>
+          <t>ר״י הבחור, רבנו תם, ר״י הזקן, מעשה מרכבה</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>הוגה ציוני-דתי מוקדם שמפרש 'תשובה' כתהליך לאומי: שיבה לארץ היא עצמה הגאולה. מציע תכנית פעולה: חברות כלכליות, יוזמות מדיניות ואחידות לאומית סביב עברית וזהות אחת.</t>
+          <t>מן הדמויות המרכזיות בדור שלאחר רבנו תם בעולם התוספות. שילב עצמאות למדנית ושימוש רחב בירושלמי עם מוניטין של איש חזיונות וסודות הבריאה.</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>תשובה כללית = שיבה: אחריות היסטורית עוברת מן השמיים לאדם ולציבור.</t>
+          <t>חיבור נדיר בין חריפות דיאלקטית תלמודית לבין עומק מיסטי, כגשר בין אשכנז, ספרד ועולמות הסוד.</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>קשר רעיוני למשפחת הרצל (כפי שנרמז בטקסט); מבשרי חיבת ציון</t>
+          <t>רבנו תם; ר״י הזקן; הרמב״ם; רבי יהודה בר יקר; רבי יחיאל מפאריס</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6GD0RxzoBaG17nmaGA9pe9?si=qeIXN4iwRIWsOjztQ5cWoQ</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/0fIS5dc7OCTq1C6amM82LT?si=tqcgKwdFQPuRVDKuMbTmkQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודה אריה מודנה – דיוקן של גאונות שנאבקה על עצמה</t>
+          <t>הרמ״ה</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1571–1648</t>
+          <t>1170–1244</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ונציה; איטליה</t>
+          <t>ספרד</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>מוסר והגות</t>
+          <t>תלמוד, מסורה והלכה</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>אוטוביוגרפיה, הימורים, התמכרות, פולמוס קבלה, יהודים–נוצרים, הומניזם, ספרות</t>
+          <t>רבי מאיר הלוי אבולעפיה, יד רמה</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה אריה מודנה היה רב, דרשן ופולמוסן בגטו ונציה, בעל גאונות לשונית וכתיבה עשירה. לצד מפעל רוחני רחב הוא תיעד בכנות את התמכרותו להימורים ואת נפילותיו באוטוביוגרפיה "חיי יהודה". כתביו נעים בין הגנה על המסורת לבין ביקורת חריפה על הקבלה ושיח עם העולם הנוצרי.</t>
+          <t>מגדולי חכמי ספרד, פוסק, ראש ישיבה ובעל מסורת סייג לתורה.</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>יושר רוחני כמודל הנהגה: גאונות לצד חשיפה כנה של חולשה ומאבק פנימי.</t>
+          <t>דיוק במסורת לצד הנהגה הלכתית עצמאית.</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>קהילת ונציה; פולמוס מול מקובלים; הומניזם נוצרי</t>
+          <t>הרמב״ם, הרמב״ן</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7dCBE5OnROaK58y5cK5tiO?si=4Cr1F3_iTIu6UQbPYdZuyg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/3DlGOty8LZ8KGhLiLcyqjs</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף משאש</t>
+          <t>מחזור ויטרי</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1892–1974</t>
+          <t>1105 בקירוב</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>מקנס (מרוקו) → חיפה</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>הלכה, היסטוריה, הנהגה</t>
+          <t>ליטורגיה והלכה</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>פסיקה ריאלית, רציונליזם, אחדות ישראל, יהדות המגרב, אתחלתא דגאולה</t>
+          <t>מחזור ויטרי, רבנו שמחה מוויטרי</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>איש אשכולות שראה במציאות כלי להבנת ההלכה, פסק באומץ מתוך חמלה ורוח הזמן, וחיזק את אחדות ישראל בין גולה לתקומה.</t>
+          <t>אנציקלופדיה הלכתית וליטורגית מבית מדרשו של רש״י, המשמרת את נוסח צרפת ומסורות אשכנז הקדומות.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>הלכה נצחית שפוגשת זמן: ריאליזם הלכתי כמפתח לשמירת המסורת בחברה משתנה.</t>
+          <t>חיבור בין תפילה, הלכה, אגדה וחיי קהילה.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>קהילות המגרב; רבנות חיפה; שיח ציוני-דתי</t>
+          <t>רש״י, בעלי התוספות</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2bY5WI2sxqsa1csNcbHXoG</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/6xiWssuJyV4GypDbnlCpl0</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>הרב יחזקאל לנדא – “הנודע ביהודה”</t>
+          <t>ספר הכוזרי</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1713–1793</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>פראג (בוהמיה)</t>
+          <t>ספרד / אל־אנדלוס</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>פסיקה והנהגה קהילתית</t>
+          <t>הגות ואמונה</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>שו"ת, שבתאות, חסידות, השכלה, קבלה (זהירות), הנהגה</t>
+          <t>רבי יהודה הלוי, אמונה, סיני, ארץ ישראל</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>גדול פוסקי פראג שניצב מול שבתאות, השכלה וחסידות. הכריע באומץ בסוגיות עקרוניות, הנהיג בקור רוח בזמן משברים, ושילב מאבק בכפירה עם אחריות ציבורית.</t>
+          <t>אחד מחיבורי היסוד של המחשבה היהודית, שנכתב בידי רבי יהודה הלוי בערבית יהודית. מציג הגנה מקורית על היהדות דרך ההיסטוריה, ההתגלות הלאומית והקשר בין עם, מצוות וארץ.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות הלכתית אסטרטגית: לדעת מתי להילחם בגלוי ומתי לרסן כדי לשמור על אחדות הקהילה.</t>
+          <t>ביסוס האמונה היהודית על זיכרון היסטורי לאומי והתגלות ציבורית, ולא רק על הוכחה פילוסופית מופשטת.</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>מריה תרזה; יוזף השני; הערכה גם בחוגים חסידיים</t>
+          <t>רבי יהודה הלוי; הרמב"ם; הרב קוק; ביאליק</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4EJ2FNYaB1FdSuKMRkfonR?si=123rhSTsT6Wga_7NA8Xp_A&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/0E55prQ6VaFsIXKSiCpDe3?si=XrQKU-Z0TgKEvgDDjH-MFQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>הרב יצחק נסים – הראשון לציון שניהל 'מדיניות חוץ' עצמאית</t>
+          <t>רבי אביגדור כ״ץ</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1895–1981</t>
+          <t>המאה ה־13</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>בגדד / ישראל</t>
+          <t>איטליה, גרמניה ואוסטריה</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה ציבורית</t>
+          <t>הלכה והנהגה</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>ראשון לציון, רבנות ראשית, ממלכתיות, גיור, יחסי דת ומדינה</t>
+          <t>חידושי תוספות</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>ראשון לציון והרב הראשי לישראל; הנהיג קו ממלכתי־עצמאי, פעל לקרב רחוקים וקבע עמדות ציבוריות תקיפות.</t>
+          <t>ממנהיגי יהדות אוסטריה ומחבר בין מסורות איטליה, אשכנז וצרפת.</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>רבנות ממלכתית גאה ועצמאית – שילוב הנהגה, פסיקה ואחריות לאומית.</t>
+          <t>בניית רצף מסורת באמצעות תלמידים וקהילות.</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>חכמי בבל; הרבנות הראשית; הרב מרדכי אליהו (תלמיד/השפעה)</t>
+          <t>המהר״ם מרוטנבורג</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6M7GqxrkmSgbLaowvUoIbM?si=YsGIvc_wSLu215jfLClMtg</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/0Gbt6DvaXHHA3NQUKn6gAe</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>הרב מאיר דוד כהנא</t>
+          <t>רבי יוסף חיון (רי״ח)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1932–1990</t>
+          <t>מאה 15</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ארה"ב → ישראל</t>
+          <t>ליסבון, פורטוגל</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>אידיאולוגיה/פוליטיקה</t>
+          <t>פרשנות מקרא/תיאולוגיה</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>זהות יהודית ומדינה, דמוקרטיה והלכה, ביטחון, גבולות שיח</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr"/>
+          <t>תורה מן השמים, דיוק לשוני, ספר דברים, פרשנות סמנטית</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>מנהיג קהילת ליסבון ומורו של האברבנאל. פיתח פתרון לשאלת 'דברים מפי עצמו' ועיקרון שאין כפל עניין בתנ״ך.</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>משה ניסח נאומים, אך ה׳ הכתיב לו מילה במילה בעת כתיבת התורה; כל מילה במקרא ייחודית ואין 'נרדפות' סתמית.</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>דון יצחק אברבנאל; קנפנטון; המלבי״ם (הקדמה רעיונית)</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7aTrR9GQVvo3kwZrfhAuIj?si=_hnfvF-wT06Aqi3ZB0hU9w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>הרב מאיר זייני</t>
+          <t>רבי יצחק קנפנטון</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1921–2012</t>
+          <t>1360–1463</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>אלג׳יריה → פריז → ירושלים</t>
+          <t>קסטיליה; ספרד</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות קהילה/ציונות/מסורת צפון אפריקה</t>
+          <t>למדנות תלמודית</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>יהדות אלג׳יריה, עוז חיים, תורה וגבורה, עלייה בגיל 85</t>
+          <t>דרכי התלמוד, גאון מקסטיליה</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>רב קהילות באלג׳יריה, רב צבאי, ובצרפת החיה בית כנסת והנחיל זהות ליוורנואית-ציונית. עלה לישראל בגיל 85.</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>מנהיגות 'גדול גיבור' המחברת תורה ומעשה; גאולה מתוך מפגש תפילה-עשייה ושימור ניגון מסורת.</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>מגורשי ספרד; הרב שרקי (תיאור תלמידים)</t>
-        </is>
-      </c>
+          <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0hEDzOsuXWV4gBqUTv3KqW</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/2xytN0uGuTq03wNYWvusDO?si=GjQi6caQRZGdjDrWc8cX7w</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי הירש חיות (מהר"ץ חיות)</t>
+          <t>רבנו חננאל בן חושיאל</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1805–1855</t>
+          <t>מאה 11</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>גליציה</t>
+          <t>קירואן (צפון אפריקה)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>תורה שבעל פה, הגנה על המסורת, מתודולוגיה</t>
+          <t>פירוש תלמוד/פסיקה</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>מנחת קנאות, תורת נביאים, אמנציפציה, גשר מסורת-מחקר</t>
+          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>גדול תורה בגליציה שניסה לגשר בין מחקר זהיר לבין נאמנות מוחלטת לתורה שבעל פה, ובנה שפה של הגנה אינטלקטואלית על המסורת.</t>
+          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>גשר נאמן: פתיחות דעת המשרתת אמונה – לא מחליפה אותה.</t>
+          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>חת"ם סופר; שלמה קלוגר; נחמן קרוכמל (רנ"ק)</t>
+          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7qsdQhzQdtrX80wVbwkfmZ</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי הירש קלישר – ציונות דתית לפני הרצל</t>
+          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1795–1874</t>
+          <t>1100–1171</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>פרוסיה / ארץ ישראל (חזון)</t>
+          <t>צרפת (אשכנז)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית והלכה</t>
+          <t>תלמוד ושיטה למדנית</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>גאולה בדרך הטבע, יישוב הארץ, חקלאות, קורבנות בלי בית, מדיניות</t>
+          <t>תוספות, שתי שקיעות, תפילין, תקנות, מסעות הצלב</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>פוסק שמרן שניסח תוכנית מעשית לגאולה: עלייה, חקלאות ובניין הארץ “מעט מעט”. הציע מהלכים הלכתיים נועזים (כגון דיון בחידוש קורבנות) ופעל מול נדבנים ומעצמות.</t>
+          <t>נכדו של רש״י שבנה את שיטת בעלי התוספות: לא מוותרים על סתירות – מחברים סוגיות וגשרים. במקביל היה מנהיג קהילה בתקופת מסעי הצלב ותקן תקנות חברתיות.</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>גאולה קמעא קמעא: אחריות אנושית כמצווה – יוזמה לאומית ללא ניתוק מן ההלכה.</t>
+          <t>נאמנות קשוחה לנוסח הגמרא (“בספרים אל ימחק”) שמכריחה עומק, דיוק וחילוקים – ומייצרת לימוד יוצר.</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>מונטיפיורי; רוטשילד; נפוליאון השלישי; 'דרישת ציון'</t>
+          <t>בעלי התוספות; רש״י; מנהג זמן רבנו תם</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7CWcx0r0X5jRyzuRCBPBDh?si=gf7x1W04SsWqd3iA4wjpMQ</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ?si=o5kksAmaQNiRkBHxN8CVpQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי יהודה הכהן קוק</t>
+          <t>המהרי״ק (רבי יוסף קולון)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1891–1982</t>
+          <t>1420–1480 בקירוב</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>צרפת ואיטליה</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית</t>
+          <t>הלכה ומנהג</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>מרכז הרב, אתחלתא דגאולה, התיישבות</t>
+          <t>שו״ת מהרי״ק</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>ממשיך דרכו של הראי"ה קוק ומנהיג דור התחייה של הציונות הדתית.</t>
+          <t>מגדולי הפוסקים שהעניקו למנהג הקהילתי מעמד מרכזי בפסיקה.</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>חיבור בין מדינת ישראל, לימוד תורה וגאולה.</t>
+          <t>המנהג הוא חלק מהתורה החיה של עם ישראל.</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>הראי"ה קוק; הרב חנן פורת; הרב משה לוינגר</t>
+          <t>הרמ״א, תרומת הדשן</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/33CjfygeixWek05uscU4qM?si=zHwL0eT7QtWwuw1PHxvNJg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/5V8efc6gWfwrgHLR6E1AQZ</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>הרב צדוק הכהן מלובלין – המיסטיקן האינטלקטואלי</t>
+          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1823–1900</t>
+          <t>1858–1936</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ליטא / לובלין</t>
+          <t>רוגצ'וב/דווינסק</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>חסידות והגות</t>
+          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>ספק כתנאי לתורה, תשובה, חטא וזכות, תורה שבעל פה, איזביצא</t>
+          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>עילוי ליטאי שנהפך לחסיד בעקבות מפגש עם ר׳ מרדכי יוסף מאיז׳ביצא. מציע תיאולוגיה שבה תורה שבעל‑פה היא התגלות מתמשכת דרך מאבק אנושי, וספק הוא תנאי לגילוי עמוק.</t>
+          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>הנפילה כחלק מהמהלך: חטא ותשובה נקראים לאחור כחלק מרצון ה׳; הסכנה האמיתית היא ייאוש.</t>
+          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>ר׳ מרדכי יוסף מאיז׳ביצא; הרב דסלר; הרב הוטנר</t>
+          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6DLhfveOXBJupYoYqgceWx?si=zrPEwB1LQjua2OW_BkVXPw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>הרב קלמן שם טוב גפן</t>
+          <t>הרב יעקב ששפורטש</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1856–1927</t>
+          <t>1610–1698</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>צפון אפריקה, אירופה המערבית (אמסטרדם, לונדון, המבורג, ליבורנו)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>קבלה, פילוסופיה ומדע</t>
+          <t>פולמוס/הנהגה</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>תורת הממדים</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>הוגה שניסה ליצור סינתזה בין קבלה, מדע מודרני ופילוסופיה.</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>המדע והתורה מתארים רבדים שונים של אותה מציאות.</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>הראי״ה קוק, הרצי״ה קוק</t>
-        </is>
-      </c>
+          <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/12f9H8UgJMaWzeIBegbaMu</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/09JfLsbxRNjLhC969SxOPd?si=zTKhNkZ7T8qiI1akCdsAvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>הרב רפאל יהודה מנחם לוי – רבי יהודה מרגוזה</t>
+          <t>רבי דוד פארדו</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1783–1879</t>
+          <t>1719–1792</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>סרייבו; ירושלים; קושטא; יפו</t>
+          <t>ונציה, הבלקן, ירושלים</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>רבנות, התיישבות וחקלאות</t>
+          <t>תלמוד, משנה ותוספתא</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>יפו, הפרדס היהודי הראשון, מקוה ישראל, פתח תקווה, ועד העיר, עבודת האדמה</t>
+          <t>חסדי דוד, תוספתא</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>רבה הראשון של יפו החדשה, שאיחד קהילות, קלט עולים והקים מוסדות ציבור. נטע ב־1842 את הפרדס היהודי הראשון בעת החדשה, תמך במקוה ישראל ועודד עבודה, חקלאות והתיישבות בארץ.</t>
+          <t>מגדולי פרשני התוספתא, שהחזיר את לימודה למרכז בית המדרש באמצעות פירושו 'חסדי דוד'.</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>תורה ועבודת האדמה אינן סותרות זו את זו; בניין הארץ, עצמאות כלכלית ויוזמה ציבורית הם חלק מתהליך הגאולה.</t>
+          <t>דיוק טקסטואלי לצד מחויבות עמוקה למסורת.</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>הרב יהודה ביבאס, משה מונטיפיורי, קרל נטר, מייסדי פתח תקווה</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
+          <t>פרופ' שאול ליברמן</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0gNG3pg6tSS0rP12co2dsU</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>הרב שמואל מוהליבר – מנהיג דתי ומבשר הציונות</t>
+          <t>רבי משה דוד ואלי (הרמ״ד ואלי)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1824–1898</t>
+          <t>1697–1777</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>מזרח אירופה / ארץ ישראל (מפעל היישוב)</t>
+          <t>פדובה, איטליה</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות ציונית-דתית</t>
+          <t>קבלה/פרשנות מקרא</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>חיבת ציון, אחדות דתיים-חילונים, היתר מכירה, התיישבות</t>
+          <t>פשוטו מכוון אל סודו, רמח״ל, כתבים גנוזים</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>מנהיג חיבת ציון שהבין שהשיבה לארץ היא משימה מעשית. יצר גשר בין דתיים לחילונים, פעל עם רוטשילד להקמת מושבות, ותמך בהיתר מכירה בפולמוס השמיטה כדי להציל את ההתיישבות.</t>
+          <t>רופא מוסמך וחבר קרוב של הרמח״ל. פיתח שיטת פרשנות: הפשט עצמו רומז לסוד בכל שינוי דקדוקי/לשוני.</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>ברית ציבורית רחבה כצורך גאולי: אחדות בין כוחות שונים בעם כדי לבנות מציאות.</t>
+          <t>מיפוי לשון המקרא למבנה הספירות; דחיית חכמות חיצוניות כתחליף; מפעל פירושים עצום שנחשף רק בדורות האחרונים.</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>הרצל (כינויו בטקסט); הרב קוק (הספד); רוטשילד; מזכרת בתיה</t>
+          <t>הרמח״ל; חוג פדובה; הדפסת כתבים בדורנו</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5T2FtQnfoEkvsFnCYyFBcQ?si=B9g6mdr7TtqbzlQnC1gTMA</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/6Sc3CiYpTfV68Ke8SueReD</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>הרבי מפיאסצ'נה</t>
+          <t>רבי רפאל עמנואל חי ריקי</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>1889–1943</t>
+          <t>1687–1743</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>פולין</t>
+          <t>איטליה וירושלים</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>חסידות וחינוך</t>
+          <t>קבלה ופרשנות</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>אש קודש, חובת התלמידים</t>
+          <t>משנת חסידים, יושר לבב, קבלת האר"י</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>אדמו"ר שחשף את עומק הנשמה גם בתוך אימי השואה.</t>
+          <t>מקובל, פייטן ופרשן משנה, מן הדמויות הבולטות בקבלת איטליה.</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>הפיכת המשבר וההסתר למקום של עבודת ה' פנימית.</t>
+          <t>שילוב קבלת האר"י עם הוראה שיטתית וספרות הלכתית-קבלית.</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>גטו ורשה; בני מחשבה טובה</t>
+          <t>האר"י; הרש"ש; האור החיים</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/3Foy6VcyWU352VPpw1z1cp?si=jaoMkKODSduL9jAf58zdww</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>הרבנית בת שבע אסתר קניבסקי</t>
+          <t>רבי שבתאי הכהן (הש"ך)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1932–2011</t>
+          <t>1622–1663</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; בני ברק</t>
+          <t>פולין</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>חסד, תפילה והנהגה רוחנית לנשים</t>
+          <t>הלכה, חושן משפט, ביקורת מקורות</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>בית רשב״ם, חסד, תפילה, תהילים, עצה וברכה, צניעות, נשים</t>
+          <t>שפתי כהן, יורה דעה, תקפו כהן, מחלוקת</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>בתו של הרב יוסף שלום אלישיב, נכדת רבי אריה לוין ורעיית הרב חיים קניבסקי. ביתה בבני ברק הפך לכתובת לאלפי נשים שביקשו עצה, תפילה וחיזוק, ולמוקד של צדקה, סיוע למשפחות וליווי חולים.</t>
+          <t>פוסק גאון שדרש פתיחה מחודשת של ההלכה, עימת את המקובל, חידש בעיון, וספריו הפכו יסוד ללימוד ולפסיקה עד היום.</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>השפעה רוחנית אינה תלויה בתפקיד רשמי: הקשבה אישית, חסד ואמונה פשוטה יכולות להפוך בית פרטי למרכז של תקווה ואהבת ישראל.</t>
+          <t>הלכה כעיון פתוח ולא כקובץ סגור; עקרונות חדשניים בדיני ממונות וספקות.</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>הרב יוסף שלום אלישיב (אביה), רבי אריה לוין (סבה), הרב חיים קניבסקי (בעלה), הרבנית לאה קולדצקי (בתה)</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+          <t>הט"ז, מגיני שלמה, מגלה עמוקות</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0zeTxQVV4ZhQFYYST2sO12</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>חכם ציון חביב ברכה</t>
+          <t>האדר״ת (רבי אליהו דוד רבינוביץ'-תאומים)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4399,42 +5172,57 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
+          <t>1843–1905</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ירושלים (נחלאות)</t>
+          <t>ליטא וירושלים</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
+          <t>הלכה, מוסר והנהגה ציבורית</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+          <t>סדר אליהו, נפש דוד</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>רבה של פוניבז', מיר וירושלים, ומחותנו של הראי״ה קוק.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>גדלות בתורה מחייבת אחריות ציבורית ודוגמה אישית.</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>הראי״ה קוק, רבי שמואל סלנט</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/7zHC1A3dQMNYpbYXahsYQd</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>חנה סנש</t>
+          <t>הלל צייטלין (1871–1942) – פילוסוף יהודי בין ניטשה לחסידות, שנרצח בשואה</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4444,50 +5232,57 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1921–1944</t>
+          <t>1871–1942</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>בודפשט, הונגריה; נהלל; שדות ים; יוגוסלביה</t>
+          <t>פולין; מזרח אירופה</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>ציונות, שליחות ושירה</t>
+          <t>מחשבה</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>צנחני היישוב, ציונות, תפילה, הליכה לקיסריה, אלי אלי, שליחות, השואה, גבורה, נשים</t>
+          <t>מודרנה יהודית; אקזיסטנציאליזם; חסידות; משבר אמונה</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>משוררת, צנחנית וגיבורת היישוב שעלתה מהונגריה לארץ ישראל והצטרפה למשימת צניחה מעבר לקווי האויב באירופה. ביומניה ובשיריה חיברה בין זהות יהודית, תפילה, אחריות מוסרית ושליחות לאומית.</t>
+          <t>הלל צייטלין: פילוסוף יהודי בין ניטשה לחסידות, מבקר תרבות שחוזר לעומק רוחני; נרצח בשואה.</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>רוחניות אמיתית אינה מסתגרת מן המציאות אלא מחייבת פעולה; תפילה, אחריות לעם ונכונות למעשה יכולות להשתלב בשליחות מוסרית אחת.</t>
+          <t>החיפוש עצמו הוא עבודת ה': להפוך ספק ומודרניות למנוע של תשובה וחידוש רוחני.</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>קטרינה סנש, גיורא סנש, צנחני היישוב, קיבוץ שדות ים</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+          <t>ניטשה; בובר; ברנר; חסידות חב"ד; ספרות יהודית מודרנית</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>https://spotifycreators-web.app.link/e/VKh6sMX4yQb</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>טובה סנהדראי-גולדרייך</t>
+          <t>הרב יהודא ליאון אשכנזי (מניטו)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4497,54 +5292,57 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1906–1993</t>
+          <t>1922–1996</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>גליציה; ארץ ישראל</t>
+          <t>אלג'יריה → צרפת → ישראל</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות ציונית־דתית</t>
+          <t>מחשבת ישראל, קבלה, זהות לאומית</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, המפד"ל, כנסת, שירות לאומי, נשים</t>
+          <t>אסכולת פריז, לוינס, שושני, עברי/יהודי, צמצום כמוסר, תחייה</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>חברת הכנסת הדתית הראשונה, ממנהיגות תנועת "אמונה" ומקימת "רשימת הפועלת והאישה הדתית" ב־1949. כיהנה ארבע קדנציות בכנסת מטעם המפד"ל וקידמה חקיקה חברתית ורווחתית.</t>
+          <t>הוגה וקבליסט שחיבר בין מסורת צפון אפריקה, שיח אינטלקטואלי צרפתי ותורת ארץ ישראל; ניסח תורת זהויות והעמיד שפה חדשה של תחייה.</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>שילוב מחויבות הלכתית עם אחריות ציבורית ופרלמנטרית — הרחבת השתתפות נשים דתיות בבניין המדינה מבלי לוותר על עקרונות.</t>
+          <t>זהות 'עברי' כשלב תודעתי-לאומי שמאחד קודש וחול, משפחה ועם, מוסר והיסטוריה.</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, המפד"ל</t>
+          <t>עמנואל לוינס; אנדרה נהר; יעקב גורדין; מר שושני; הרב צבי יהודה קוק; הרב אורי שרקי</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0RuE8l4DbgcRxBQWjGBUv3?si=rW9fZeAOTueEFDMOKUR5mQ</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/6vCbxdldNDpdncGxSjvAyD</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
+          <t>הרב יוסף משאש</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4554,54 +5352,57 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1886–1929</t>
+          <t>1892–1974</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>גרמניה</t>
+          <t>מקנס (מרוקו) → חיפה</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>פילוסופיה יהודית מודרנית</t>
+          <t>הלכה, היסטוריה, הנהגה</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>כוכב הגאולה, התגלות, דיאלוג, יהדות ונצרות, תרגום תנ"ך, ALS</t>
+          <t>פסיקה ריאלית, רציונליזם, אחדות ישראל, יהדות המגרב, אתחלתא דגאולה</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>ב'כוכב הגאולה' מפרק את ה'כוליות' ומציע מבנה של אלוהים-אדם-עולם דרך בריאה/התגלות/גאולה. הקים Lehrhaus בפרנקפורט ותרגם תנ"ך עם בובר, תוך התמודדות עם ALS.</t>
+          <t>איש אשכולות שראה במציאות כלי להבנת ההלכה, פסק באומץ מתוך חמלה ורוח הזמן, וחיזק את אחדות ישראל בין גולה לתקומה.</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>התגלות כדיבור ואהבה שמולידים אחריות; אמת נוצרת במפגש ולא במערכת מופשטת.</t>
+          <t>הלכה נצחית שפוגשת זמן: ריאליזם הלכתי כמפתח לשמירת המסורת בחברה משתנה.</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>מרטין בובר; Lehrhaus; עמנואל לוינס (השפעה מאוחרת)</t>
+          <t>קהילות המגרב; רבנות חיפה; שיח ציוני-דתי</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7EpaIjYgIJVmSWDAsXDI7g?si=u6IC097XQ-KpBRfRRIGqcg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/2bY5WI2sxqsa1csNcbHXoG</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>רבי מאיר שמחה הכהן מדווינסק</t>
+          <t>הרב מאיר זייני</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4611,54 +5412,57 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1843–1926</t>
+          <t>1921–2012</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>דווינסק (לטביה/ליטא)</t>
+          <t>אלג׳יריה → פריז → ירושלים</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>הלכה/פרשנות תורה/מחשבה ציונית</t>
+          <t>מנהיגות קהילה/ציונות/מסורת צפון אפריקה</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>אור שמח, משך חכמה, גלות וזהות, שבועות</t>
+          <t>יהדות אלג׳יריה, עוז חיים, תורה וגבורה, עלייה בגיל 85</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>מחבר 'אור שמח' ו'משך חכמה'. גשר בין שכל לאמונה ובין גלות לתחייה; ניתוח חריף של היסטוריה יהודית וקדושה.</t>
+          <t>רב קהילות באלג׳יריה, רב צבאי, ובצרפת החיה בית כנסת והנחיל זהות ליוורנואית-ציונית. עלה לישראל בגיל 85.</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>הגלות כמנגנון זהות; קדושה אינה בחומר אלא ברצון ה׳; ציונות וגאולה בדרך הטבע (בלפור/סן-רמו).</t>
+          <t>מנהיגות 'גדול גיבור' המחברת תורה ומעשה; גאולה מתוך מפגש תפילה-עשייה ושימור ניגון מסורת.</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ם; הרב קוק; עידן התחייה</t>
+          <t>מגורשי ספרד; הרב שרקי (תיאור תלמידים)</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5M242GRqncgReaYVplhjBU</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/0hEDzOsuXWV4gBqUTv3KqW</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>רבי משה חגיז – הקנאי הירושלמי שניסה להציל את היהדות מן הקריסה הפנימית</t>
+          <t>הרב רפאל יהודה מנחם לוי – רבי יהודה מרגוזה</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4668,54 +5472,53 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1671–1750</t>
+          <t>1783–1879</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; איטליה; אמסטרדם; אירופה</t>
+          <t>סרייבו; ירושלים; קושטא; יפו</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>פסיקה והנהגה קהילתית</t>
+          <t>רבנות, התיישבות וחקלאות</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>אחר שבתאות, פולמוס, סמכות חכמים, גבולות קבלה, השכלה, לקט הקמח</t>
+          <t>יפו, הפרדס היהודי הראשון, מקוה ישראל, פתח תקווה, ועד העיר, עבודת האדמה</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>חגיז פעל לאחר טראומת השבתאות כקנאי-אחראי להצבת גבולות מול מה שראה כהתפוררות המסורת. משבר אישי הוביל אותו להתמסר לכתיבה ולפולמוס, ולעימותים שהדהדו בקהילות אירופה. ב"לקט הקמח" ביקש לשרטט סדר מחודש ולהחזיר סמכות הלכתית מרכזית, גם במחיר של קיטוב ומחלוקת.</t>
+          <t>רבה הראשון של יפו החדשה, שאיחד קהילות, קלט עולים והקים מוסדות ציבור. נטע ב־1842 את הפרדס היהודי הראשון בעת החדשה, תמך במקוה ישראל ועודד עבודה, חקלאות והתיישבות בארץ.</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>קנאות כאחריות: שרטוט גבולות כדי למנוע קריסה רוחנית אחרי שבתאות – במחיר גבוה.</t>
+          <t>תורה ועבודת האדמה אינן סותרות זו את זו; בניין הארץ, עצמאות כלכלית ויוזמה ציבורית הם חלק מתהליך הגאולה.</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>נחמיה חיון; החכם צבי; הרמח"ל; ר' יונתן אייבשיץ</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/2kCpBIWS1B2NtObhJemSdG?si=CHbvRGp1RkW_Lj5w4HGnsQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>הרב יהודה ביבאס, משה מונטיפיורי, קרל נטר, מייסדי פתח תקווה</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>רבי שמשון רפאל הירש</t>
+          <t>חכם ציון חביב ברכה</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4725,50 +5528,45 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>1808–1888</t>
+          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>המבורג; פרנקפורט, גרמניה</t>
+          <t>ירושלים (נחלאות)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>הגות, חינוך ויחסי תורה ומודרנה</t>
+          <t>קבלה</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>תורה עם דרך ארץ, אורתודוקסיה, השכלה כללית, חינוך, איגרות צפון, חורב, פולמוס הפרישה</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>רב, פרשן והוגה יהודי מגרמניה שניסח את שיטת ״תורה עם דרך ארץ״. הנהיג בפרנקפורט מערכת חינוך ששילבה לימודי קודש עם לימודים כלליים, ונאבק ברפורמה תוך הדגשת מחויבות מלאה להלכה גם בתוך התרבות המודרנית.</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>אפשר להיות מעורב במדע, בתרבות ובחברה המודרנית מבלי שהתורה תאבד את מרכזיותה; הפתיחות לעולם דורשת זהות תורנית ברורה וגבולות הלכתיים מוצקים.</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>רבי יצחק דב במברגר, קהילת פרנקפורט, התנועה הרפורמית, האורתודוקסיה הגרמנית</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
+          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>רס״ן רועי קליין</t>
+          <t>טובה סנהדראי-גולדרייך</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4778,54 +5576,61 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1975–2006</t>
+          <t>1906–1993</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>גליציה; ארץ ישראל</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות וציונות דתית</t>
+          <t>מנהיגות ציונית־דתית</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>מלחמת לבנון השנייה</t>
+          <t>תנועת אמונה, המפד"ל, כנסת, שירות לאומי, נשים</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>קצין צה״ל שעוטר בעיטור העוז לאחר שנפל תוך הצלת חייליו בקרב בבינת ג'בייל.</t>
+          <t>חברת הכנסת הדתית הראשונה, ממנהיגות תנועת "אמונה" ומקימת "רשימת הפועלת והאישה הדתית" ב־1949. כיהנה ארבע קדנציות בכנסת מטעם המפד"ל וקידמה חקיקה חברתית ורווחתית.</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>גבורה צומחת מחיים של אחריות, אמונה ומסירות.</t>
+          <t>שילוב מחויבות הלכתית עם אחריות ציבורית ופרלמנטרית — הרחבת השתתפות נשים דתיות בבניין המדינה מבלי לוותר על עקרונות.</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>צה״ל, הציונות הדתית</t>
+          <t>תנועת אמונה, המפד"ל</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/0RuE8l4DbgcRxBQWjGBUv3?si=rW9fZeAOTueEFDMOKUR5mQ</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>רס״ן רועי קליין הי״ד</t>
+          <t>רבי מאיר שמחה הכהן מדווינסק</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4835,54 +5640,57 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>1975–2006</t>
+          <t>1843–1926</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>דווינסק (לטביה/ליטא)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>מוסר, מנהיגות</t>
+          <t>הלכה/פרשנות תורה/מחשבה ציונית</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>גבורה, צה״ל, אמונה</t>
+          <t>אור שמח, משך חכמה, גלות וזהות, שבועות</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>קצין צה"ל שמסר נפשו להצלת חייליו והפך לסמל של גבורה הנובעת מחיים של ערכים.</t>
+          <t>מחבר 'אור שמח' ו'משך חכמה'. גשר בין שכל לאמונה ובין גלות לתחייה; ניתוח חריף של היסטוריה יהודית וקדושה.</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>גבורה כרצף חיים – לא רגע חד־פעמי</t>
+          <t>הגלות כמנגנון זהות; קדושה אינה בחומר אלא ברצון ה׳; ציונות וגאולה בדרך הטבע (בלפור/סן-רמו).</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>צה״ל; חינוך דתי</t>
+          <t>הרמב״ם; הרב קוק; עידן התחייה</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/5M242GRqncgReaYVplhjBU</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ר׳ אריה־לייב גינצבורג – “שאגת אריה”</t>
+          <t>רבי שמשון רפאל הירש</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4892,54 +5700,53 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>בערך 1695–1785</t>
+          <t>1808–1888</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>מזרח אירופה / מץ (צרפת)</t>
+          <t>המבורג; פרנקפורט, גרמניה</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>פסיקה ועיון תלמודי</t>
+          <t>הגות, חינוך ויחסי תורה ומודרנה</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>אורח חיים, חריפות, פשט, עצמאות, ביקורת מקרא (תורת הבחינות)</t>
+          <t>תורה עם דרך ארץ, אורתודוקסיה, השכלה כללית, חינוך, איגרות צפון, חורב, פולמוס הפרישה</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>גאון תלמודי ופוסק עצמאי שחי בעוני ונדודים, התנגש בממסד ולא פחד לחלוק. ספרו 'שאגת אריה' נעשה אבן יסוד בפסיקת אורח חיים וחיבוריו נלמדים בעומק.</t>
+          <t>רב, פרשן והוגה יהודי מגרמניה שניסח את שיטת ״תורה עם דרך ארץ״. הנהיג בפרנקפורט מערכת חינוך ששילבה לימודי קודש עם לימודים כלליים, ונאבק ברפורמה תוך הדגשת מחויבות מלאה להלכה גם בתוך התרבות המודרנית.</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>אמת הלכתית ללא פשרות: דיוק במקורות הראשונים ועצמאות פסיקה – גם במחיר של בדידות ציבורית.</t>
+          <t>אפשר להיות מעורב במדע, בתרבות ובחברה המודרנית מבלי שהתורה תאבד את מרכזיותה; הפתיחות לעולם דורשת זהות תורנית ברורה וגבולות הלכתיים מוצקים.</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>השפעה מאוחרת על הרב מרדכי ברויאר (תורת הבחינות); הערכה בחב״ד</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4tSyrs2SrcNd1WsVBoHZuh?si=fQD3_QT6TqqaEDMyoYR9bw</t>
-        </is>
-      </c>
+          <t>רבי יצחק דב במברגר, קהילת פרנקפורט, התנועה הרפורמית, האורתודוקסיה הגרמנית</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>שד"ל – הלוחם האחרון של היהדות הרגשית מול כיבוש השכל היווני</t>
+          <t>רס״ן רועי קליין</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4949,54 +5756,57 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>1800–1865</t>
+          <t>1975–2006</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>פאדובה; איטליה</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>פרשנות מקרא ולשון</t>
+          <t>מנהיגות וציונות דתית</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>חכמת ישראל, פרשנות מקרא, פילולוגיה, רציונליזם, אמונה, חמלה, ביקורת יוון</t>
+          <t>מלחמת לבנון השנייה</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>שד"ל טען שהיהדות האותנטית היא דת של חמלה ואמונה ולא של שכל קר, ובנה מפעל מדעי (לשון, מקרא, ביקורת טקסט) כדי להגן על חיות המסורת. הוא נאבק בחוגי חכמת ישראל שנראו לו כמי שהופכים יהדות לארכיאולוגיה, ותקף את הכנסת "חכמת יוון" ליהדות. כאב חייו חיזק אצלו את עליונות האמונה והמעשה הטוב.</t>
+          <t>קצין צה״ל שעוטר בעיטור העוז לאחר שנפל תוך הצלת חייליו בקרב בבינת ג'בייל.</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>הגנה על יהדות של חמלה ואמונה מול רציונליזם קר – באמצעות מחקר מקרא ולשון.</t>
+          <t>גבורה צומחת מחיים של אחריות, אמונה ומסירות.</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>חכמת ישראל; רמב"ם; ראב"ע; שפינוזה</t>
+          <t>צה״ל, הציונות הדתית</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/03tAgaC9jfaMhMJ2rvW4uF?si=cgIj0F37SiKtDyDT85ZqKA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>שושלת אבוחצירא</t>
+          <t>רס״ן רועי קליין הי״ד</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5006,54 +5816,57 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־19–20</t>
+          <t>1975–2006</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>מרוקו, ארץ ישראל</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>קבלה, הנהגה, פיוט</t>
+          <t>מוסר, מנהיגות</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
+          <t>גבורה, צה״ל, אמונה</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
+          <t>קצין צה"ל שמסר נפשו להצלת חייליו והפך לסמל של גבורה הנובעת מחיים של ערכים.</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
+          <t>גבורה כרצף חיים – לא רגע חד־פעמי</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
+          <t>צה״ל; חינוך דתי</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>שלמה מונק</t>
+          <t>ר׳ אריה־לייב גינצבורג – “שאגת אריה”</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5063,54 +5876,57 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>1803–1867</t>
+          <t>בערך 1695–1785</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>גרמניה וצרפת</t>
+          <t>מזרח אירופה / מץ (צרפת)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>מדעי היהדות ופילוסופיה</t>
+          <t>פסיקה ועיון תלמודי</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>מורה נבוכים, אבן גבירול</t>
+          <t>אורח חיים, חריפות, פשט, עצמאות, ביקורת מקרא (תורת הבחינות)</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>מזרחן וחוקר יהדות שהחזיר את אבן גבירול להיסטוריה של הפילוסופיה וערך את מורה נבוכים מן המקור הערבי.</t>
+          <t>גאון תלמודי ופוסק עצמאי שחי בעוני ונדודים, התנגש בממסד ולא פחד לחלוק. ספרו 'שאגת אריה' נעשה אבן יסוד בפסיקת אורח חיים וחיבוריו נלמדים בעומק.</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>שילוב בין מחקר מדעי לנאמנות למסורת.</t>
+          <t>אמת הלכתית ללא פשרות: דיוק במקורות הראשונים ועצמאות פסיקה – גם במחיר של בדידות ציבורית.</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם, אבן גבירול</t>
+          <t>השפעה מאוחרת על הרב מרדכי ברויאר (תורת הבחינות); הערכה בחב״ד</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0fBwsgpkyNbo7MJnjhEgeH</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/4tSyrs2SrcNd1WsVBoHZuh?si=fQD3_QT6TqqaEDMyoYR9bw</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
+          <t>שלמה מונק</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5120,47 +5936,50 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־19 (פרסום 1843)</t>
+          <t>1803–1867</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
+          <t>גרמניה וצרפת</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל (קבלה)</t>
+          <t>מדעי היהדות ופילוסופיה</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
+          <t>מורה נבוכים, אבן גבירול</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
+          <t>מזרחן וחוקר יהדות שהחזיר את אבן גבירול להיסטוריה של הפילוסופיה וערך את מורה נבוכים מן המקור הערבי.</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
+          <t>שילוב בין מחקר מדעי לנאמנות למסורת.</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
+          <t>הרמב"ם, אבן גבירול</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE?si=N2J3HnklTRW2Gm-BmT4SFA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>https://open.spotify.com/episode/0fBwsgpkyNbo7MJnjhEgeH</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K84"/>
+  <autoFilter ref="A1:N84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/חכמים_ללא_מחקר.xlsx
+++ b/data/חכמים_ללא_מחקר.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חכמים ללא מחקר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$N$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$N$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -533,59 +533,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>593</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>הרא"ם ממיץ</t>
+          <t>רבקה אמנו</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>האבות</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־12</t>
+          <t>1677–1556 לפנה״ס</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>צרפת ואשכנז</t>
+          <t>חברון</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>הלכה, מצוות ומוסר</t>
+          <t>אמהות האומה</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>ספר יראים, רבנו תם, יראת שמים, מצוות</t>
+          <t>נשים</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>מגדולי הראשונים בצרפת ואשכנז, תלמידם של רבנו תם והרשב"ם. בספרו 'ספר יראים' הציג את המצוות לא רק כמערכת דינים אלא כדרך לעיצוב האדם.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>סידור המצוות כמבנה רוחני־מוסרי כולל, שבו ההלכה נועדה לעצב את נפש האדם ולא רק להכריע בדין.</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>רבנו תם; הרשב"ם; רבי חיים כהן מפריז; רבי אלעזר מגרמייזא; האור זרוע</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/6J1axbvjzcVZFeEI2lU1IV?si=wAeaI5T6TDSElvMR_MhZ1w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>השנייה שבאמהות. ראתה ברוח קודשה את ייעודם של בניה והכריעה את המשך דרך הברית — 'ורב יעבוד צעיר'.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -593,71 +581,55 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>עמוד ההוראה והחסידות_ משנתו התורנית ופועלו ההלכתי של רבי אליעזר ממיץ (הרא_ם).docx</t>
+          <t>פועלה, משנתה התורנית ומעמדה המנהיגותי של רבקה אמנו_ ניתוח פרשני, תיאולוגי וחינוכי.docx</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>עמוד ההוראה והחסידות: משנתו התורנית ופועלו ההלכתי של רבי אליעזר ממיץ (הרא"ם)</t>
+          <t>פועלה, משנתה התורנית ומעמדה המנהיגותי של רבקה אמנו: ניתוח פרשני, תיאולוגי וחינוכי</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>575</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>הרא״ה (רבי אהרן הלוי)</t>
+          <t>עזרא הסופר</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>בית שני</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1231–1303</t>
+          <t>480–420 לפנה״ס</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ספרד</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>הלכה ותלמוד</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>בדק הבית</t>
-        </is>
-      </c>
+          <t>תורה, הנהגה</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>מתלמידי הרמב״ן ומגדולי חכמי קטלוניה, מבקרו ההלכתי המרכזי של הרשב״א.</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>נאמנות למסורת יחד עם ביקורת הלכתית עצמאית.</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>הרמב״ן, הריטב״א</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/1VCc2NTp4Fx2MnomLuC2YQ</t>
-        </is>
-      </c>
+          <t>מחדש התורה בישראל בראשית ימי הבית השני. העלה את הגולה מבבל, כונן את קריאת התורה ברבים — 'ראוי היה עזרא שתינתן תורה על ידו'.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -665,71 +637,59 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>משנתו, פועלו ומורשתו התורנית של רבי אהרן הלוי (הרא_ה)_ ניתוח היסטורי, הלכתי ופרשני של עמוד התווך בחכמי ברצלונה.docx</t>
+          <t>עזרא הסופר בראשית ימי הבית השני.docx</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>משנתו, פועלו ומורשתו התורנית של רבי אהרן הלוי (הרא"ה): ניתוח היסטורי, הלכתי ופרשני של עמוד התווך בחכמי ברצלונה</t>
+          <t>עזרא הסופר בראשית ימי הבית השני</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>580</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>הרי״ד הזקן – רבי ישעיה די טראני</t>
+          <t>רבי יהודה הנשיא</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>תנאים</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>135–217</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>איטליה</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, הלכה</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>תוספות, שיטה למדנית</t>
-        </is>
-      </c>
+          <t>משנה, הנהגה</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>יצר שיטת לימוד חדשה המתמקדת בהבנת כל סוגיה בפני עצמה, גם במחיר השארת סתירות פתוחות.</t>
+          <t>עורך המשנה וחותם תקופת התנאים. איחד את מסורות התורה שבעל פה לחיבור אחד מוסמך, ושילב גדולה בתורה עם עושר ומנהיגות מול רומא.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>“ננס על גבי ענק” – המשכיות יצירתית של המסורת</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>בעלי התוספות; מהר"ם מרוטנבורג; הרא"ש; ריטב"א</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/1RhrrkBapQNDsL3Nc92rS3</t>
-        </is>
-      </c>
+          <t>עריכת המשנה — חתימת התורה שבעל פה הראשונה</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -737,71 +697,55 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>(הרי_ד הזקן)_ מחקר מקיף על יצירתו, שיטתו והשפעתו לדורות.docx</t>
+          <t>רבי יהודה הנשיא_ ניתוח היסטורי, הלכתי וארכאולוגי.docx</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>(הרי"ד הזקן): מחקר מקיף על יצירתו, שיטתו והשפעתו לדורות</t>
+          <t>רבי יהודה הנשיא: ניתוח היסטורי, הלכתי וארכאולוגי</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>יחיאל בן יקותיאל</t>
+          <t>רבן גמליאל דיבנה</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>תנאים</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>50–118</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>רומא, איטליה</t>
+          <t>יבנה</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>מוסר, הלכה, רפואה ועריכת טקסטים</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>מעלות המידות, תניא רבתי, ירושלמי, רומא</t>
-        </is>
-      </c>
+          <t>הנהגה, הלכה</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>חכם איטלקי ששילב תורה, רפואה, פילוסופיה ודקדוק טקסטואלי. מיוחסת לו תרומה מכרעת לשימור מסורת הירושלמי ולבניית ספרות מוסר שיטתית.</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>חיבור הלכה, מוסר ודיוק מדעי לתפיסה אחת של תיקון האדם כולו — גוף, נפש ושכל.</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>הרמב״ם; חסידי אשכנז; מסורת איטליה; כתב יד ליידן של הירושלמי</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/1tRAsJRFk47EvwWKBYsRZc?si=wIR3RR1RT0qdwsZfGHbvvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>נשיא ישראל אחרי החורבן. ביצר את סמכות הנשיאות ואת אחדות ההלכה בדור השיקום של יבנה.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -809,71 +753,59 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>רבי יחיאל בן יקותיאל ענו_ מחקר היסטורי והלכתי מקיף.docx</t>
+          <t>מנהיגות משקמת בעידן השבר_ פועלו, משנתו התורנית וביצור סמכותו של רבן גמליאל דיבנה.docx</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>רבי יחיאל בן יקותיאל ענו: מחקר היסטורי והלכתי מקיף</t>
+          <t>מנהיגות משקמת בעידן השבר: פועלו, משנתו התורנית וביצור סמכותו של רבן גמליאל דיבנה</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>592</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ספר הזוהר – מי כתב? רבי שמעון בר יוחאי או חיבור מאוחר? המחלוקת סביב מחבר הזוהר</t>
+          <t>רבן יוחנן בן זכאי</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>תנאים</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 לפנה״ס–74</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ארץ ישראל/ספרד; עולם הקבלה</t>
+          <t>יבנה</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>מסורת וביקורת; סמכות טקסטואלית; היסטוריה של הזוהר</t>
-        </is>
-      </c>
+          <t>תורה שבעל פה, הנהגה</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>מחלוקת הייחוס של הזוהר לרשב"י מול טענות למחבר מאוחר, והשלכות השאלה על סמכות הקבלה ועל קריאת הטקסט.</t>
+          <t>מציל התורה בדור החורבן. יצא מירושלים הנצורה וביקש 'תן לי יבנה וחכמיה' — ובכך הבטיח את המשך התורה שבעל פה אחרי חורבן הבית.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>מעבר ל'מי כתב': איך טקסט נעשה קנוני ומהי אחריות הפרשנות כשמסורת והיסטוריה מצטלבות.</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>רשב"י; ר' משה די ליאון; גרשם שלום; מחקר הקבלה</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>https://spotifycreators-web.app.link/e/HxZF2iS4yQb</t>
-        </is>
-      </c>
+          <t>תן לי יבנה וחכמיה</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -881,24 +813,24 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>התנא רבי שמעון בר יוחאי.docx</t>
+          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי_ עיצוב היהדות בעידן המשבר והשיקום(1).docx</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>התנא רבי שמעון בר יוחאי</t>
+          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי: עיצוב היהדות בעידן המשבר והשיקום</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>רבי יהודה בן ברכיה</t>
+          <t>הרא"ם ממיץ</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -908,42 +840,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>המאות ה־12–13</t>
+          <t>המאה ה־12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>פרובאנס</t>
+          <t>צרפת ואשכנז</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>הלכה, תלמוד ופירוש הרי״ף</t>
+          <t>הלכה, מצוות ומוסר</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>שיטת ריב״ב, הרי״ף, גאונים, רמב״ם</t>
+          <t>ספר יראים, רבנו תם, יראת שמים, מצוות</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>מחכמי פרובאנס שיצר פירוש רחב על הלכות הרי״ף. שיטתו שילבה פשט, ביקורת על הרי״ף, מסורת גאונים והשוואה לפסקי הרמב״ם.</t>
+          <t>מגדולי הראשונים בצרפת ואשכנז, תלמידם של רבנו תם והרשב"ם. בספרו 'ספר יראים' הציג את המצוות לא רק כמערכת דינים אלא כדרך לעיצוב האדם.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>הפיכת פרובאנס לגשר חי בין מסורת הגאונים, הרי״ף, הרמב״ם ובעלי התוספות.</t>
+          <t>סידור המצוות כמבנה רוחני־מוסרי כולל, שבו ההלכה נועדה לעצב את נפש האדם ולא רק להכריע בדין.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>הרי״ף; בעל המאור; רב האי גאון; ר״י אבן גיאת; הרמב״ם; הרמב״ן; הרשב״א</t>
+          <t>רבנו תם; הרשב"ם; רבי חיים כהן מפריז; רבי אלעזר מגרמייזא; האור זרוע</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/647NStP3Z8X3LRqObcCXUZ?si=KByF2c3MQAKtqw4L_2KQFg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/6J1axbvjzcVZFeEI2lU1IV?si=wAeaI5T6TDSElvMR_MhZ1w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -953,24 +885,24 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>משנתו ההלכתית ופועלו התורני של רבי יהודה בן ברכיה (ריב_ב)_ מחקר מקיף על צומת מסורות פרובנס.docx</t>
+          <t>עמוד ההוראה והחסידות_ משנתו התורנית ופועלו ההלכתי של רבי אליעזר ממיץ (הרא_ם).docx</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>משנתו ההלכתית ופועלו התורני של רבי יהודה בן ברכיה (ריב"ב): מחקר מקיף על צומת מסורות פרובנס</t>
+          <t>עמוד ההוראה והחסידות: משנתו התורנית ופועלו ההלכתי של רבי אליעזר ממיץ (הרא"ם)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>רבי משה די ליאון</t>
+          <t>הרי״ד הזקן – רבי ישעיה די טראני</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -980,42 +912,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1240–1305</t>
+          <t>המאה ה־13</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>קסטיליה, ספרד</t>
+          <t>איטליה</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
+          <t>תלמוד, הלכה</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>ספר הזוהר, קבלת קסטיליה, גירונה, ספרות הסוד</t>
+          <t>תוספות, שיטה למדנית</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>מגדולי המקובלים בקסטיליה במאה ה-13, שבידיו נתגלה (או נערך) ספר הזוהר. חיבר גם ספרי קבלה בעברית כ"שקל הקודש", ועמד במוקד המחלוקת ההיסטורית על קדמות הזוהר.</t>
+          <t>יצר שיטת לימוד חדשה המתמקדת בהבנת כל סוגיה בפני עצמה, גם במחיר השארת סתירות פתוחות.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>העמדת ספר הזוהר במרכז ארון הספרים היהודי — הטקסט המכונן של תורת הסוד.</t>
+          <t>“ננס על גבי ענק” – המשכיות יצירתית של המסורת</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>רבי שמעון בר יוחאי (ייחוס הזוהר), מקובלי גירונה</t>
+          <t>בעלי התוספות; מהר"ם מרוטנבורג; הרא"ש; ריטב"א</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5hjMOYSZfyk2PpvO1z7y60?si=xvtDucKGTcqSJ5rNgkG76A</t>
+          <t>https://open.spotify.com/episode/1RhrrkBapQNDsL3Nc92rS3</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1025,24 +957,24 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>משה בן שם טוב די ליאון (1240–1305)_ דו_ח מומחה על פועלו ומשנתו התורנית.docx</t>
+          <t>(הרי_ד הזקן)_ מחקר מקיף על יצירתו, שיטתו והשפעתו לדורות.docx</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>משה בן שם טוב די ליאון (1240–1305): דו"ח מומחה על פועלו ומשנתו התורנית</t>
+          <t>(הרי"ד הזקן): מחקר מקיף על יצירתו, שיטתו והשפעתו לדורות</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>298</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>רבי צדקיה בן אברהם העניו</t>
+          <t>יחיאל בן יקותיאל</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1057,37 +989,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>איטליה</t>
+          <t>רומא, איטליה</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>הלכה ורפואה</t>
+          <t>מוסר, הלכה, רפואה ועריכת טקסטים</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>שיבולי הלקט</t>
+          <t>מעלות המידות, תניא רבתי, ירושלמי, רומא</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי איטליה, מחבר שיבולי הלקט ומגשר בין מסורות אשכנז ואיטליה.</t>
+          <t>חכם איטלקי ששילב תורה, רפואה, פילוסופיה ודקדוק טקסטואלי. מיוחסת לו תרומה מכרעת לשימור מסורת הירושלמי ולבניית ספרות מוסר שיטתית.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>סידור ושימור המסורת ההלכתית מתוך ענווה ואחריות.</t>
+          <t>חיבור הלכה, מוסר ודיוק מדעי לתפיסה אחת של תיקון האדם כולו — גוף, נפש ושכל.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>בעלי התוספות, בעל הטורים</t>
+          <t>הרמב״ם; חסידי אשכנז; מסורת איטליה; כתב יד ליידן של הירושלמי</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0zmmVvmiG4Wzj6H3D3wwK7</t>
+          <t>https://open.spotify.com/episode/1tRAsJRFk47EvwWKBYsRZc?si=wIR3RR1RT0qdwsZfGHbvvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1097,24 +1029,24 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>הקודיפיקציה האיטלקית ושורשיה בירושלים_ משנתו התורנית ופועלו של רבי צדקיה בן אברהם הרופא.docx</t>
+          <t>רבי יחיאל בן יקותיאל ענו_ מחקר היסטורי והלכתי מקיף.docx</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>הקודיפיקציה האיטלקית ושורשיה בירושלים: משנתו התורנית ופועלו של רבי צדקיה בן אברהם הרופא</t>
+          <t>רבי יחיאל בן יקותיאל ענו: מחקר היסטורי והלכתי מקיף</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>רבנו יצחק בן יהודה ממגנצא</t>
+          <t>ספר הזוהר – מי כתב? רבי שמעון בר יוחאי או חיבור מאוחר? המחלוקת סביב מחבר הזוהר</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1124,42 +1056,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>גרמניה</t>
+          <t>ארץ ישראל/ספרד; עולם הקבלה</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>הלכה ותלמוד</t>
+          <t>קבלה</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>מגנצא, רש"י</t>
+          <t>מסורת וביקורת; סמכות טקסטואלית; היסטוריה של הזוהר</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>ראש ישיבת מגנצא ומורו המרכזי של רש"י, ממעצבי שיטת הלימוד האשכנזית.</t>
+          <t>מחלוקת הייחוס של הזוהר לרשב"י מול טענות למחבר מאוחר, והשלכות השאלה על סמכות הקבלה ועל קריאת הטקסט.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>שילוב בין דיוק טקסטואלי, מנהג ופסיקה.</t>
+          <t>מעבר ל'מי כתב': איך טקסט נעשה קנוני ומהי אחריות הפרשנות כשמסורת והיסטוריה מצטלבות.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>רבנו גרשום, רש"י</t>
+          <t>רשב"י; ר' משה די ליאון; גרשם שלום; מחקר הקבלה</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4tFSo5qQFWExTxQDDj1a8Q</t>
+          <t>https://spotifycreators-web.app.link/e/HxZF2iS4yQb</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1169,69 +1101,69 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>רבי יצחק בן יהודה על התהוות המסורת האשכנזית.docx</t>
+          <t>התנא רבי שמעון בר יוחאי.docx</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>רבי יצחק בן יהודה על התהוות המסורת האשכנזית</t>
+          <t>התנא רבי שמעון בר יוחאי</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>רבי חיים בן עטר (בעל אור החיים)</t>
+          <t>רבי יהודה בן ברכיה</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1696–1743</t>
+          <t>המאות ה־12–13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>סאלי, מרוקו; ליבורנו; ירושלים</t>
+          <t>פרובאנס</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>פרשנות התורה, הלכה וקבלה</t>
+          <t>הלכה, תלמוד ופירוש הרי״ף</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>אור החיים, מדרש כנסת ישראל, כבה נר המערבי, גאולת אחישנה ובעתה</t>
+          <t>שיטת ריב״ב, הרי״ף, גאונים, רמב״ם</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי מרוקו במאה ה־18, פרשן, פוסק ומקובל. חיבר את "אור החיים" המשלב פשט, רמז, דרש וסוד, והקים בירושלים את ישיבת "כנסת ישראל". הבעל שם טוב ספד לו במות: "כבה נר המערבי".</t>
+          <t>מחכמי פרובאנס שיצר פירוש רחב על הלכות הרי״ף. שיטתו שילבה פשט, ביקורת על הרי״ף, מסורת גאונים והשוואה לפסקי הרמב״ם.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>שילוב שיטתי של ארבעת רבדי הפרשנות (פרד"ס) בפירוש אחד, לצד תפיסת גאולה המבחינה בין "אחישנה" מהירה ל"בעתה" הדרגתית.</t>
+          <t>הפיכת פרובאנס לגשר חי בין מסורת הגאונים, הרי״ף, הרמב״ם ובעלי התוספות.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>הבעל שם טוב, ועד כנסת ישראל בליבורנו</t>
+          <t>הרי״ף; בעל המאור; רב האי גאון; ר״י אבן גיאת; הרמב״ם; הרמב״ן; הרשב״א</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3HwpG5NALcGOQmbs1wwR4N?si=2otS_OCBTYaCbDWu2xZarQ</t>
+          <t>https://open.spotify.com/episode/647NStP3Z8X3LRqObcCXUZ?si=KByF2c3MQAKtqw4L_2KQFg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1241,71 +1173,55 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>משנתו, פועלו ומורשתו של רבי חיים בן עטר_ אור החיים הקדוש בפרספקטיבה היסטורית ותאולוגית.docx</t>
+          <t>משנתו ההלכתית ופועלו התורני של רבי יהודה בן ברכיה (ריב_ב)_ מחקר מקיף על צומת מסורות פרובנס.docx</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>משנתו, פועלו ומורשתו של רבי חיים בן עטר: אור החיים הקדוש בפרספקטיבה היסטורית ותאולוגית</t>
+          <t>משנתו ההלכתית ופועלו התורני של רבי יהודה בן ברכיה (ריב"ב): מחקר מקיף על צומת מסורות פרובנס</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>רבי ישראל יהושע טרונק (ישועות מלכו)</t>
+          <t>רבי יהודה הלוי (ריה"ל)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1820–1893</t>
+          <t>1075–1141</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>פולין</t>
+          <t>טולדו</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>הלכה, ציונות דתית</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>היתר מכירה, יישוב הארץ</t>
-        </is>
-      </c>
+          <t>שירה, הגות</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>פוסק גדול שתמך בהתיישבות וב"היתר מכירה" מתוך ראיית הגאולה המעשית.</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>עבודת הארץ כחלק מהמצווה והגאולה</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>קלישר; רבני ארץ ישראל; פוסקי הדור</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5CjFGW61SRKSx3ScmazcV1</t>
-        </is>
-      </c>
+          <t>מגדולי משוררי ספרד והוגה 'הכוזרי'. שירת געגועיו לציון — 'לבי במזרח ואנוכי בסוף מערב' — מלווה את האומה; בסוף ימיו יצא לארץ ישראל.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1313,71 +1229,55 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות, פסיקה ותפיסה לאומית_ דמותו ופועלו של רבי ישראל יהושע טרונק מקוטנא (ה_ישועות מלכו_).docx</t>
+          <t>רבי יהודה הלוי_ מחקר מקיף על דמותו, הגותו ויצירתו הספרותית.docx</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות, פסיקה ותפיסה לאומית: דמותו ופועלו של רבי ישראל יהושע טרונק מקוטנא (ה"ישועות מלכו")</t>
+          <t>רבי יהודה הלוי: מחקר מקיף על דמותו, הגותו ויצירתו הספרותית</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>581</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>האדמו״ר מקאליב (רבי מנחם מנדל טאוב)</t>
+          <t>רבי יעקב הכהן (המקובל)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1923–2019</t>
+          <t>1200–1270</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>הונגריה וישראל</t>
+          <t>קאסטיליה</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>חסידות, זיכרון השואה והלכה</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>קול מנחם, שמע ישראל</t>
-        </is>
-      </c>
+          <t>קבלה</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>ניצול שואה ומנהיג חסידי שהקדיש את חייו להנצחת הנספים ולהפצת תורה ואמונה.</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>הפיכת הזיכרון והכאב לכוח של בניין רוחני.</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>חסידות קאליב</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/2RfVxXD6TIynHVoCEcKPJn</t>
-        </is>
-      </c>
+          <t>ממקובלי קאסטיליה הראשונים, מאבות 'קבלת האחים הכהנים'. חיבוריו על האותיות והמרכבה קדמו לזוהר והשפיעו עליו.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1385,71 +1285,55 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של האדמו_ר מקאליב, רבי מנחם מנדל טאוב_ מנהיגות, הנצחה ויצירה תורנית בצל החורבן.docx</t>
+          <t>פועלו ומשנתו התורנית של רבי יעקב הכהן_ צומת דרכים בין מיסטיקה חזיונית לקבלה גנוסטית במאה השלוש-עשרה.docx</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של האדמו"ר מקאליב, רבי מנחם מנדל טאוב: מנהיגות, הנצחה ויצירה תורנית בצל החורבן</t>
+          <t>פועלו ומשנתו התורנית של רבי יעקב הכהן: צומת דרכים בין מיסטיקה חזיונית לקבלה גנוסטית במאה השלוש-עשרה</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>582</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>הרב אברהם יהושע השל – הגות ומעורבות מוסרית</t>
+          <t>רבי יצחק אלפסי (הרי"ף)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1907–1972</t>
+          <t>1013–1103</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>פולין / ארה"ב</t>
+          <t>פאס</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>הגות יהודית ואתיקה ציבורית</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>השבת ארמון בזמן, נבואה, פליאה, זכויות אזרח, דיאלוג יהודי-נוצרי</t>
-        </is>
-      </c>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>הוגה שחיבר חסידות ופילוסופיה עם אתיקה ציבורית. כתב 'השבת' ו'הנביאים', פעל בזכויות האזרח, וצעד לצד מרטין לותר קינג – 'תפילה עם הרגליים'.</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>קדושת הזמן והפליאה כמנוע אמונה; אחריות מוסרית כחלק בלתי נפרד מעבודת ה'.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>מרטין לותר קינג; JTS; דיאלוג יהודי-נוצרי (נוסטרה אטאטה)</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/63Q7RdapehdnH3FCLVMrBy?si=DujHYLYPTUmSckrnlOofCQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>גדול פוסקי הדור שבין הגאונים לראשונים. 'הלכות הרי"ף' זיקקו את התלמוד לפסק הלכה ושימשו עמוד יסוד לשולחן ערוך.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1457,71 +1341,55 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>אברהם יהושע השל_ פנומנולוגיה של קדושה וצדק.docx</t>
+          <t>רבי יצחק אלפסי (הרי_ף) בעיצוב עולם ההלכה.docx</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>אברהם יהושע השל: פנומנולוגיה של קדושה וצדק</t>
+          <t>רבי יצחק אלפסי (הרי"ף) בעיצוב עולם ההלכה</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>583</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>הרב אברהם יצחק הכהן קוק – החזון שאיחד קודש וחול</t>
+          <t>רבי יצחק הלוי (סגן לויה)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1865–1935</t>
+          <t>1000–1080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ארץ ישראל</t>
+          <t>וורמייזא</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית והלכה</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>קודש וחול, תשובה היסטורית, ציונות, היתר מכירה, מרכז הרב</t>
-        </is>
-      </c>
+          <t>תלמוד, פרשנות</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>הראי"ה קוק ראה במודרנה תהליך אלוהי ובציונות החילונית תנועת תשובה עמוקה. חיפש אחדות בין ניגודים, דיבר על התפתחות, והנהיג הלכתית-לאומית מתוך אחריות ליישוב.</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>האמת מתגלה במתח בין ניגודים: “הישן יתחדש והחדש יתקדש” – איחוד כוחות במקום מחיקה.</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>חלוצים; ישיבת 'מרכז הרב'; פולמוס ההיתר בשמיטה</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/19vVkCaNfYWm6AlvbjbkRe?si=Y2-7mNX9QnCXzxz32MKpgA</t>
-        </is>
-      </c>
+          <t>מראשי ישיבות לותיר ורבותיו המובהקים של רש"י בוורמייזא. ממעצבי מסורת הלימוד האשכנזית הקדומה.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1529,69 +1397,69 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>רב אברהם יצחק הכהן קוק.docx</t>
+          <t>רבי יצחק סגן לויה.docx</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>הם יצחק הכהן קוק: אנליזה מקיפה של מהפכת הקודש בתקופת התחייה</t>
+          <t>רבי יצחק סגן לויה</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>הרב חיים דרוקמן – מנהיג ציונות דתית בדורנו</t>
+          <t>רבי משה די ליאון</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1932–2022</t>
+          <t>1240–1305</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>קסטיליה, ספרד</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות וחינוך</t>
+          <t>קבלה</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>בני עקיבא, ישיבות הסדר, גיור, הנהגה ציבורית, אחדות</t>
+          <t>ספר הזוהר, קבלת קסטיליה, גירונה, ספרות הסוד</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>ניצול שואה שהפך למנהיג מרכזי בציונות הדתית: ראש מוסדות אור עציון, מנהיג בני עקיבא ונשיא ישיבות ההסדר. נשא באחריות למערך הגיור הממלכתי מתוך אהבת ישראל.</t>
+          <t>מגדולי המקובלים בקסטיליה במאה ה-13, שבידיו נתגלה (או נערך) ספר הזוהר. חיבר גם ספרי קבלה בעברית כ"שקל הקודש", ועמד במוקד המחלוקת ההיסטורית על קדמות הזוהר.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>הנהגה אחראית שמחזיקה תורה-צבא-מדינה יחד, עם דגש על אחדות ואהבת אדם.</t>
+          <t>העמדת ספר הזוהר במרכז ארון הספרים היהודי — הטקסט המכונן של תורת הסוד.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>הרב צבי יהודה קוק; מוסדות אור עציון; מערך הגיור</t>
+          <t>רבי שמעון בר יוחאי (ייחוס הזוהר), מקובלי גירונה</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1j4SgDhb3vWdY3gvTjv3oq?si=67O0wVDkTsa2b7zRpBFQmQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=128</t>
+          <t>https://open.spotify.com/episode/5hjMOYSZfyk2PpvO1z7y60?si=xvtDucKGTcqSJ5rNgkG76A</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1601,69 +1469,69 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>הרב חיים מאיר דרוקמן.docx</t>
+          <t>משה בן שם טוב די ליאון (1240–1305)_ דו_ח מומחה על פועלו ומשנתו התורנית.docx</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>הרב חיים מאיר דרוקמן</t>
+          <t>משה בן שם טוב די ליאון (1240–1305): דו"ח מומחה על פועלו ומשנתו התורנית</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודה אלקלעי – תשובה שהופכת לתוכנית לאומית</t>
+          <t>רבנו יצחק בן יהודה ממגנצא</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1798–1878</t>
+          <t>המאה ה־11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>הבלקן</t>
+          <t>גרמניה</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית</t>
+          <t>הלכה ותלמוד</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>תשובה כללית, שיבה לארץ, דיפלומטיה, שפה עברית, אחדות</t>
+          <t>מגנצא, רש"י</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>הוגה ציוני-דתי מוקדם שמפרש 'תשובה' כתהליך לאומי: שיבה לארץ היא עצמה הגאולה. מציע תכנית פעולה: חברות כלכליות, יוזמות מדיניות ואחידות לאומית סביב עברית וזהות אחת.</t>
+          <t>ראש ישיבת מגנצא ומורו המרכזי של רש"י, ממעצבי שיטת הלימוד האשכנזית.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>תשובה כללית = שיבה: אחריות היסטורית עוברת מן השמיים לאדם ולציבור.</t>
+          <t>שילוב בין דיוק טקסטואלי, מנהג ופסיקה.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>קשר רעיוני למשפחת הרצל (כפי שנרמז בטקסט); מבשרי חיבת ציון</t>
+          <t>רבנו גרשום, רש"י</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6GD0RxzoBaG17nmaGA9pe9?si=qeIXN4iwRIWsOjztQ5cWoQ</t>
+          <t>https://open.spotify.com/episode/4tFSo5qQFWExTxQDDj1a8Q</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1673,71 +1541,55 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>הרב יהודה בן שלמה חי אלקלעי.docx</t>
+          <t>רבי יצחק בן יהודה על התהוות המסורת האשכנזית.docx</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>הרב יהודה בן שלמה חי אלקלעי</t>
+          <t>רבי יצחק בן יהודה על התהוות המסורת האשכנזית</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>597</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודה אריה מודנה – דיוקן של גאונות שנאבקה על עצמה</t>
+          <t>שמואל הנגיד</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1571–1648</t>
+          <t>993–1056</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ונציה; איטליה</t>
+          <t>גרנדה</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>מוסר והגות</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>אוטוביוגרפיה, הימורים, התמכרות, פולמוס קבלה, יהודים–נוצרים, הומניזם, ספרות</t>
-        </is>
-      </c>
+          <t>הלכה, שירה, מדינאות</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה אריה מודנה היה רב, דרשן ופולמוסן בגטו ונציה, בעל גאונות לשונית וכתיבה עשירה. לצד מפעל רוחני רחב הוא תיעד בכנות את התמכרותו להימורים ואת נפילותיו באוטוביוגרפיה "חיי יהודה". כתביו נעים בין הגנה על המסורת לבין ביקורת חריפה על הקבלה ושיח עם העולם הנוצרי.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>יושר רוחני כמודל הנהגה: גאונות לצד חשיפה כנה של חולשה ומאבק פנימי.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>קהילת ונציה; פולמוס מול מקובלים; הומניזם נוצרי</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7dCBE5OnROaK58y5cK5tiO?si=4Cr1F3_iTIu6UQbPYdZuyg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>וזיר גרנדה, מצביא, משורר ופוסק — סמל תור הזהב בספרד. 'מבוא התלמוד' שלו נלמד עד היום.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1745,71 +1597,55 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>בין סמכות הלכתית, רציונליזם ומודרנה_ פועלו, יצירתו ומשנתו התורנית של רבי יהודה אריה ממודנה (הריא_ם).docx</t>
+          <t>מנהיגות, הלכה ומדע הלשון בימי הביניים_ משנתו הרב-ממדית של רבי שמואל הנגיד.docx</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>בין סמכות הלכתית, רציונליזם ומודרנה: פועלו, יצירתו ומשנתו התורנית של רבי יהודה אריה ממודנה (הריא"ם)</t>
+          <t>מנהיגות, הלכה ומדע הלשון בימי הביניים: משנתו הרב-ממדית של רבי שמואל הנגיד</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>573</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>הרב יחזקאל לנדא – “הנודע ביהודה”</t>
+          <t>מהר"י בירב (רבי יעקב בירב)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1713–1793</t>
+          <t>1474–1546</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>פראג (בוהמיה)</t>
+          <t>צפת</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>פסיקה והנהגה קהילתית</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>שו"ת, שבתאות, חסידות, השכלה, קבלה (זהירות), הנהגה</t>
-        </is>
-      </c>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>גדול פוסקי פראג שניצב מול שבתאות, השכלה וחסידות. הכריע באומץ בסוגיות עקרוניות, הנהיג בקור רוח בזמן משברים, ושילב מאבק בכפירה עם אחריות ציבורית.</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>מנהיגות הלכתית אסטרטגית: לדעת מתי להילחם בגלוי ומתי לרסן כדי לשמור על אחדות הקהילה.</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>מריה תרזה; יוזף השני; הערכה גם בחוגים חסידיים</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4EJ2FNYaB1FdSuKMRkfonR?si=123rhSTsT6Wga_7NA8Xp_A&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>גדול חכמי צפת בדורו ויוזם חידוש הסמיכה (1538) כצעד לקירוב הגאולה — מהלך שהצית את הפולמוס הגדול עם חכמי ירושלים.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1817,69 +1653,69 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>רבי יחזקאל לנדא, _הנודע ביהודה_.docx</t>
+          <t>רבי יעקב בירב.docx</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>רבי יחזקאל לנדא, "הנודע ביהודה"</t>
+          <t>רבי יעקב בירב: מהפכת הסמכות וחידוש המרכז הרוחני בארץ ישראל</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>הרב יצחק נסים – הראשון לציון שניהל 'מדיניות חוץ' עצמאית</t>
+          <t>רבי חיים בן עטר (בעל אור החיים)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1895–1981</t>
+          <t>1696–1743</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>בגדד / ישראל</t>
+          <t>סאלי, מרוקו; ליבורנו; ירושלים</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה ציבורית</t>
+          <t>פרשנות התורה, הלכה וקבלה</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>ראשון לציון, רבנות ראשית, ממלכתיות, גיור, יחסי דת ומדינה</t>
+          <t>אור החיים, מדרש כנסת ישראל, כבה נר המערבי, גאולת אחישנה ובעתה</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>ראשון לציון והרב הראשי לישראל; הנהיג קו ממלכתי־עצמאי, פעל לקרב רחוקים וקבע עמדות ציבוריות תקיפות.</t>
+          <t>מגדולי חכמי מרוקו במאה ה־18, פרשן, פוסק ומקובל. חיבר את "אור החיים" המשלב פשט, רמז, דרש וסוד, והקים בירושלים את ישיבת "כנסת ישראל". הבעל שם טוב ספד לו במות: "כבה נר המערבי".</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>רבנות ממלכתית גאה ועצמאית – שילוב הנהגה, פסיקה ואחריות לאומית.</t>
+          <t>שילוב שיטתי של ארבעת רבדי הפרשנות (פרד"ס) בפירוש אחד, לצד תפיסת גאולה המבחינה בין "אחישנה" מהירה ל"בעתה" הדרגתית.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>חכמי בבל; הרבנות הראשית; הרב מרדכי אליהו (תלמיד/השפעה)</t>
+          <t>הבעל שם טוב, ועד כנסת ישראל בליבורנו</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6M7GqxrkmSgbLaowvUoIbM?si=YsGIvc_wSLu215jfLClMtg</t>
+          <t>https://open.spotify.com/episode/3HwpG5NALcGOQmbs1wwR4N?si=2otS_OCBTYaCbDWu2xZarQ</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1889,59 +1725,55 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות, הלכה וממלכתיות_ פועלו ומשנתו התורנית של הראשון לציון הרב יצחק נסים.docx</t>
+          <t>משנתו, פועלו ומורשתו של רבי חיים בן עטר_ אור החיים הקדוש בפרספקטיבה היסטורית ותאולוגית.docx</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות, הלכה וממלכתיות: פועלו ומשנתו התורנית של הראשון לציון הרב יצחק נסים</t>
+          <t>משנתו, פועלו ומורשתו של רבי חיים בן עטר: אור החיים הקדוש בפרספקטיבה היסטורית ותאולוגית</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>הרב מאיר דוד כהנא</t>
+          <t>רבי לוי בן חביב (המהרלב"ח)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1932–1990</t>
+          <t>1483–1545</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ארה"ב → ישראל</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>אידיאולוגיה/פוליטיקה</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>זהות יהודית ומדינה, דמוקרטיה והלכה, ביטחון, גבולות שיח</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>רבה של ירושלים והמתנגד הגדול לחידוש הסמיכה. 'קונטרס הסמיכה' שלו הכריע את הפולמוס ההלכתי הנודע מול חכמי צפת.</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7aTrR9GQVvo3kwZrfhAuIj?si=_hnfvF-wT06Aqi3ZB0hU9w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -1949,71 +1781,55 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>דוח מומחה_ הכל על פועלו ומשנתו התורנית של הרב מאיר כהנא – ניתוח רב-שכבתי של אידיאולוגיה ואקטיביזם.docx</t>
+          <t>רבי לוי בן חביב (המהרלב_ח).docx</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>דוח מומחה: הכל על פועלו ומשנתו התורנית של הרב מאיר כהנא – ניתוח רב-שכבתי של אידיאולוגיה ואקטיביזם</t>
+          <t>רבי לוי בן חביב (המהרלב"ח)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>586</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי הירש חיות (מהר"ץ חיות)</t>
+          <t>רבי משה אלשקר (מהר"ם אלשקר)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1805–1855</t>
+          <t>1466–1542</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>גליציה</t>
+          <t>מצרים</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>תורה שבעל פה, הגנה על המסורת, מתודולוגיה</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>מנחת קנאות, תורת נביאים, אמנציפציה, גשר מסורת-מחקר</t>
-        </is>
-      </c>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>גדול תורה בגליציה שניסה לגשר בין מחקר זהיר לבין נאמנות מוחלטת לתורה שבעל פה, ובנה שפה של הגנה אינטלקטואלית על המסורת.</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>גשר נאמן: פתיחות דעת המשרתת אמונה – לא מחליפה אותה.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>חת"ם סופר; שלמה קלוגר; נחמן קרוכמל (רנ"ק)</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7qsdQhzQdtrX80wVbwkfmZ</t>
-        </is>
-      </c>
+          <t>מגדולי הפוסקים שאחרי גירוש ספרד. ניצל מספינה טובעת, כיהן בדיינות במצרים ועלה בסוף ימיו לירושלים.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -2021,71 +1837,55 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>בין אקטיביזם משיחי לשמרנות הלכתית_ משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר.docx</t>
+          <t>רבי משה אלשקר (מהר_ם אלשקר).docx</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>בין אקטיביזם משיחי לשמרנות הלכתית: משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר</t>
+          <t>רבי משה אלשקר (מהר"ם אלשקר)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>587</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי הירש קלישר – ציונות דתית לפני הרצל</t>
+          <t>רבי משה חיים אפרים מסדילקוב</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1795–1874</t>
+          <t>1748–1800</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>פרוסיה / ארץ ישראל (חזון)</t>
+          <t>אוקראינה</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית והלכה</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>גאולה בדרך הטבע, יישוב הארץ, חקלאות, קורבנות בלי בית, מדיניות</t>
-        </is>
-      </c>
+          <t>חסידות</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>פוסק שמרן שניסח תוכנית מעשית לגאולה: עלייה, חקלאות ובניין הארץ “מעט מעט”. הציע מהלכים הלכתיים נועזים (כגון דיון בחידוש קורבנות) ופעל מול נדבנים ומעצמות.</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>גאולה קמעא קמעא: אחריות אנושית כמצווה – יוזמה לאומית ללא ניתוק מן ההלכה.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>מונטיפיורי; רוטשילד; נפוליאון השלישי; 'דרישת ציון'</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7CWcx0r0X5jRyzuRCBPBDh?si=gf7x1W04SsWqd3iA4wjpMQ</t>
-        </is>
-      </c>
+          <t>נכד הבעל שם טוב ובעל 'דגל מחנה אפרים' — מן המקורות הראשונים והנאמנים לתורת הסבא הגדול.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -2093,24 +1893,24 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>בין אקטיביזם משיחי לשמרנות הלכתית_ משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר.docx</t>
+          <t>משנתו התורנית ופועלו של רבי משה חיים אפרים מסדילקוב_ בעל _דגל מחנה אפרים_.docx</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>בין אקטיביזם משיחי לשמרנות הלכתית: משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר</t>
+          <t>משנתו התורנית ופועלו של רבי משה חיים אפרים מסדילקוב: בעל "דגל מחנה אפרים"</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי יהודה הכהן קוק</t>
+          <t>הרב אברהם יהושע השל – הגות ומעורבות מוסרית</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2120,42 +1920,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1891–1982</t>
+          <t>1907–1972</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>פולין / ארה"ב</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית</t>
+          <t>הגות יהודית ואתיקה ציבורית</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>מרכז הרב, אתחלתא דגאולה, התיישבות</t>
+          <t>השבת ארמון בזמן, נבואה, פליאה, זכויות אזרח, דיאלוג יהודי-נוצרי</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>ממשיך דרכו של הראי"ה קוק ומנהיג דור התחייה של הציונות הדתית.</t>
+          <t>הוגה שחיבר חסידות ופילוסופיה עם אתיקה ציבורית. כתב 'השבת' ו'הנביאים', פעל בזכויות האזרח, וצעד לצד מרטין לותר קינג – 'תפילה עם הרגליים'.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>חיבור בין מדינת ישראל, לימוד תורה וגאולה.</t>
+          <t>קדושת הזמן והפליאה כמנוע אמונה; אחריות מוסרית כחלק בלתי נפרד מעבודת ה'.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>הראי"ה קוק; הרב חנן פורת; הרב משה לוינגר</t>
+          <t>מרטין לותר קינג; JTS; דיאלוג יהודי-נוצרי (נוסטרה אטאטה)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/33CjfygeixWek05uscU4qM?si=zHwL0eT7QtWwuw1PHxvNJg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/63Q7RdapehdnH3FCLVMrBy?si=DujHYLYPTUmSckrnlOofCQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2165,24 +1965,24 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>רב אברהם יצחק הכהן קוק.docx</t>
+          <t>אברהם יהושע השל_ פנומנולוגיה של קדושה וצדק.docx</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>הם יצחק הכהן קוק: אנליזה מקיפה של מהפכת הקודש בתקופת התחייה</t>
+          <t>אברהם יהושע השל: פנומנולוגיה של קדושה וצדק</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>הרב צדוק הכהן מלובלין – המיסטיקן האינטלקטואלי</t>
+          <t>הרב אברהם יצחק הכהן קוק – החזון שאיחד קודש וחול</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2192,42 +1992,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1823–1900</t>
+          <t>1865–1935</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ליטא / לובלין</t>
+          <t>ארץ ישראל</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>חסידות והגות</t>
+          <t>הגות ציונית-דתית והלכה</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>ספק כתנאי לתורה, תשובה, חטא וזכות, תורה שבעל פה, איזביצא</t>
+          <t>קודש וחול, תשובה היסטורית, ציונות, היתר מכירה, מרכז הרב</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>עילוי ליטאי שנהפך לחסיד בעקבות מפגש עם ר׳ מרדכי יוסף מאיז׳ביצא. מציע תיאולוגיה שבה תורה שבעל‑פה היא התגלות מתמשכת דרך מאבק אנושי, וספק הוא תנאי לגילוי עמוק.</t>
+          <t>הראי"ה קוק ראה במודרנה תהליך אלוהי ובציונות החילונית תנועת תשובה עמוקה. חיפש אחדות בין ניגודים, דיבר על התפתחות, והנהיג הלכתית-לאומית מתוך אחריות ליישוב.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>הנפילה כחלק מהמהלך: חטא ותשובה נקראים לאחור כחלק מרצון ה׳; הסכנה האמיתית היא ייאוש.</t>
+          <t>האמת מתגלה במתח בין ניגודים: “הישן יתחדש והחדש יתקדש” – איחוד כוחות במקום מחיקה.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>ר׳ מרדכי יוסף מאיז׳ביצא; הרב דסלר; הרב הוטנר</t>
+          <t>חלוצים; ישיבת 'מרכז הרב'; פולמוס ההיתר בשמיטה</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6DLhfveOXBJupYoYqgceWx?si=zrPEwB1LQjua2OW_BkVXPw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/19vVkCaNfYWm6AlvbjbkRe?si=Y2-7mNX9QnCXzxz32MKpgA</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2237,24 +2037,24 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>הארת התודעה וסוד הצמצום האנושי_ פועלו, ביוגרפיית העומק ומשנתו התורנית של רבי צדוק הכהן מלובלין.docx</t>
+          <t>רב אברהם יצחק הכהן קוק.docx</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>הארת התודעה וסוד הצמצום האנושי: פועלו, ביוגרפיית העומק ומשנתו התורנית של רבי צדוק הכהן מלובלין</t>
+          <t>הם יצחק הכהן קוק: אנליזה מקיפה של מהפכת הקודש בתקופת התחייה</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>הרב קלמן שם טוב גפן</t>
+          <t>הרב חיים דרוקמן – מנהיג ציונות דתית בדורנו</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2264,42 +2064,42 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1856–1927</t>
+          <t>1932–2022</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>קבלה, פילוסופיה ומדע</t>
+          <t>מנהיגות וחינוך</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>תורת הממדים</t>
+          <t>בני עקיבא, ישיבות הסדר, גיור, הנהגה ציבורית, אחדות</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>הוגה שניסה ליצור סינתזה בין קבלה, מדע מודרני ופילוסופיה.</t>
+          <t>ניצול שואה שהפך למנהיג מרכזי בציונות הדתית: ראש מוסדות אור עציון, מנהיג בני עקיבא ונשיא ישיבות ההסדר. נשא באחריות למערך הגיור הממלכתי מתוך אהבת ישראל.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>המדע והתורה מתארים רבדים שונים של אותה מציאות.</t>
+          <t>הנהגה אחראית שמחזיקה תורה-צבא-מדינה יחד, עם דגש על אחדות ואהבת אדם.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>הראי״ה קוק, הרצי״ה קוק</t>
+          <t>הרב צבי יהודה קוק; מוסדות אור עציון; מערך הגיור</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/12f9H8UgJMaWzeIBegbaMu</t>
+          <t>https://open.spotify.com/episode/1j4SgDhb3vWdY3gvTjv3oq?si=67O0wVDkTsa2b7zRpBFQmQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=128</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2309,24 +2109,24 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>משנתו התורנית, הגותו הפילוסופית ופועלו המדעי של הרב שם טוב גפן_ ניתוח אנליטי מקיף של איש אשכולות בפרשת הדרכים של המודרנה.docx</t>
+          <t>הרב חיים מאיר דרוקמן.docx</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>משנתו התורנית, הגותו הפילוסופית ופועלו המדעי של הרב שם טוב גפן: ניתוח אנליטי מקיף של איש אשכולות בפרשת הדרכים של המודרנה</t>
+          <t>הרב חיים מאיר דרוקמן</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>הרב שמואל מוהליבר – מנהיג דתי ומבשר הציונות</t>
+          <t>הרב יהודה אלקלעי – תשובה שהופכת לתוכנית לאומית</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2336,42 +2136,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1824–1898</t>
+          <t>1798–1878</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>מזרח אירופה / ארץ ישראל (מפעל היישוב)</t>
+          <t>הבלקן</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות ציונית-דתית</t>
+          <t>הגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>חיבת ציון, אחדות דתיים-חילונים, היתר מכירה, התיישבות</t>
+          <t>תשובה כללית, שיבה לארץ, דיפלומטיה, שפה עברית, אחדות</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>מנהיג חיבת ציון שהבין שהשיבה לארץ היא משימה מעשית. יצר גשר בין דתיים לחילונים, פעל עם רוטשילד להקמת מושבות, ותמך בהיתר מכירה בפולמוס השמיטה כדי להציל את ההתיישבות.</t>
+          <t>הוגה ציוני-דתי מוקדם שמפרש 'תשובה' כתהליך לאומי: שיבה לארץ היא עצמה הגאולה. מציע תכנית פעולה: חברות כלכליות, יוזמות מדיניות ואחידות לאומית סביב עברית וזהות אחת.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>ברית ציבורית רחבה כצורך גאולי: אחדות בין כוחות שונים בעם כדי לבנות מציאות.</t>
+          <t>תשובה כללית = שיבה: אחריות היסטורית עוברת מן השמיים לאדם ולציבור.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>הרצל (כינויו בטקסט); הרב קוק (הספד); רוטשילד; מזכרת בתיה</t>
+          <t>קשר רעיוני למשפחת הרצל (כפי שנרמז בטקסט); מבשרי חיבת ציון</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5T2FtQnfoEkvsFnCYyFBcQ?si=B9g6mdr7TtqbzlQnC1gTMA</t>
+          <t>https://open.spotify.com/episode/6GD0RxzoBaG17nmaGA9pe9?si=qeIXN4iwRIWsOjztQ5cWoQ</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2381,24 +2181,24 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>הרב שמואל מוהליבר.docx</t>
+          <t>הרב יהודה בן שלמה חי אלקלעי.docx</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>הרב שמואל מוהליבר</t>
+          <t>הרב יהודה בן שלמה חי אלקלעי</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>חנה סנש</t>
+          <t>הרב יהודה אריה מודנה – דיוקן של גאונות שנאבקה על עצמה</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2408,40 +2208,44 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1921–1944</t>
+          <t>1571–1648</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>בודפשט, הונגריה; נהלל; שדות ים; יוגוסלביה</t>
+          <t>ונציה; איטליה</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>ציונות, שליחות ושירה</t>
+          <t>מוסר והגות</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>צנחני היישוב, ציונות, תפילה, הליכה לקיסריה, אלי אלי, שליחות, השואה, גבורה, נשים</t>
+          <t>אוטוביוגרפיה, הימורים, התמכרות, פולמוס קבלה, יהודים–נוצרים, הומניזם, ספרות</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>משוררת, צנחנית וגיבורת היישוב שעלתה מהונגריה לארץ ישראל והצטרפה למשימת צניחה מעבר לקווי האויב באירופה. ביומניה ובשיריה חיברה בין זהות יהודית, תפילה, אחריות מוסרית ושליחות לאומית.</t>
+          <t>רבי יהודה אריה מודנה היה רב, דרשן ופולמוסן בגטו ונציה, בעל גאונות לשונית וכתיבה עשירה. לצד מפעל רוחני רחב הוא תיעד בכנות את התמכרותו להימורים ואת נפילותיו באוטוביוגרפיה "חיי יהודה". כתביו נעים בין הגנה על המסורת לבין ביקורת חריפה על הקבלה ושיח עם העולם הנוצרי.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>רוחניות אמיתית אינה מסתגרת מן המציאות אלא מחייבת פעולה; תפילה, אחריות לעם ונכונות למעשה יכולות להשתלב בשליחות מוסרית אחת.</t>
+          <t>יושר רוחני כמודל הנהגה: גאונות לצד חשיפה כנה של חולשה ומאבק פנימי.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>קטרינה סנש, גיורא סנש, צנחני היישוב, קיבוץ שדות ים</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>קהילת ונציה; פולמוס מול מקובלים; הומניזם נוצרי</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/7dCBE5OnROaK58y5cK5tiO?si=4Cr1F3_iTIu6UQbPYdZuyg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -2449,24 +2253,24 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>פועלה, הגותה ומשנתה הרוחנית-תורנית של חנה סנש- ניתוח היסטורי, ספרותי ותיאולוגי.docx</t>
+          <t>בין סמכות הלכתית, רציונליזם ומודרנה_ פועלו, יצירתו ומשנתו התורנית של רבי יהודה אריה ממודנה (הריא_ם).docx</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>פועלה, הגותה ומשנתה הרוחנית-תורנית של חנה סנש: ניתוח היסטורי, ספרותי ותיאולוגי</t>
+          <t>בין סמכות הלכתית, רציונליזם ומודרנה: פועלו, יצירתו ומשנתו התורנית של רבי יהודה אריה ממודנה (הריא"ם)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>563</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
+          <t>הרב יוסף יצחק שניאורסון (הריי"צ)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2476,44 +2280,28 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1886–1929</t>
+          <t>1880–1950</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>גרמניה</t>
+          <t>ארה"ב</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>פילוסופיה יהודית מודרנית</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>כוכב הגאולה, התגלות, דיאלוג, יהדות ונצרות, תרגום תנ"ך, ALS</t>
-        </is>
-      </c>
+          <t>חסידות, הנהגה</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>ב'כוכב הגאולה' מפרק את ה'כוליות' ומציע מבנה של אלוהים-אדם-עולם דרך בריאה/התגלות/גאולה. הקים Lehrhaus בפרנקפורט ותרגם תנ"ך עם בובר, תוך התמודדות עם ALS.</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>התגלות כדיבור ואהבה שמולידים אחריות; אמת נוצרת במפגש ולא במערכת מופשטת.</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>מרטין בובר; Lehrhaus; עמנואל לוינס (השפעה מאוחרת)</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7EpaIjYgIJVmSWDAsXDI7g?si=u6IC097XQ-KpBRfRRIGqcg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>האדמו"ר השישי של חב"ד. עמד בעוז מול השלטון הסובייטי, שוחרר ממאסר מוות, והעביר את מרכז חב"ד לאמריקה.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>מאושר</t>
@@ -2521,24 +2309,24 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג.docx</t>
+          <t>רבי יוסף יצחק שניאורסון.docx</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג</t>
+          <t>רבי יוסף יצחק שניאורסון</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>רבי משה חגיז – הקנאי הירושלמי שניסה להציל את היהדות מן הקריסה הפנימית</t>
+          <t>הרב יחזקאל לנדא – “הנודע ביהודה”</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2548,12 +2336,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1671–1750</t>
+          <t>1713–1793</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; איטליה; אמסטרדם; אירופה</t>
+          <t>פראג (בוהמיה)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2563,27 +2351,27 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>אחר שבתאות, פולמוס, סמכות חכמים, גבולות קבלה, השכלה, לקט הקמח</t>
+          <t>שו"ת, שבתאות, חסידות, השכלה, קבלה (זהירות), הנהגה</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>חגיז פעל לאחר טראומת השבתאות כקנאי-אחראי להצבת גבולות מול מה שראה כהתפוררות המסורת. משבר אישי הוביל אותו להתמסר לכתיבה ולפולמוס, ולעימותים שהדהדו בקהילות אירופה. ב"לקט הקמח" ביקש לשרטט סדר מחודש ולהחזיר סמכות הלכתית מרכזית, גם במחיר של קיטוב ומחלוקת.</t>
+          <t>גדול פוסקי פראג שניצב מול שבתאות, השכלה וחסידות. הכריע באומץ בסוגיות עקרוניות, הנהיג בקור רוח בזמן משברים, ושילב מאבק בכפירה עם אחריות ציבורית.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>קנאות כאחריות: שרטוט גבולות כדי למנוע קריסה רוחנית אחרי שבתאות – במחיר גבוה.</t>
+          <t>מנהיגות הלכתית אסטרטגית: לדעת מתי להילחם בגלוי ומתי לרסן כדי לשמור על אחדות הקהילה.</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>נחמיה חיון; החכם צבי; הרמח"ל; ר' יונתן אייבשיץ</t>
+          <t>מריה תרזה; יוזף השני; הערכה גם בחוגים חסידיים</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2kCpBIWS1B2NtObhJemSdG?si=CHbvRGp1RkW_Lj5w4HGnsQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/4EJ2FNYaB1FdSuKMRkfonR?si=123rhSTsT6Wga_7NA8Xp_A&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2593,600 +2381,568 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של רבי משה חגיז_ שומר חומות המסורת בעידן התמורות.docx</t>
+          <t>רבי יחזקאל לנדא, _הנודע ביהודה_.docx</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של רבי משה חגיז: שומר חומות המסורת בעידן התמורות</t>
+          <t>רבי יחזקאל לנדא, "הנודע ביהודה"</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>הרב אפרים מקלעת־חמאד</t>
+          <t>הרב יצחק נסים – הראשון לציון שניהל 'מדיניות חוץ' עצמאית</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>בערך 1050–1150</t>
+          <t>1895–1981</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>קלעת בן חמאד, צפון אפריקה</t>
+          <t>בגדד / ישראל</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>הלכה, נוסח ודקדוק</t>
+          <t>הלכה, הנהגה ציבורית</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>הרי"ף, דקדוק עברי, ביקורת נוסח, קירואן</t>
+          <t>ראשון לציון, רבנות ראשית, ממלכתיות, גיור, יחסי דת ומדינה</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>מן הדמויות העמוקות שבין תקופת הגאונים לראשוני ספרד ופרובנס, 'תלמיד חבר' של הרי"ף. הגהותיו נטמעו בספר ההלכות, והוא שילב רגישות פילולוגית ודקדוקית בתוך הפסיקה.</t>
+          <t>ראשון לציון והרב הראשי לישראל; הנהיג קו ממלכתי־עצמאי, פעל לקרב רחוקים וקבע עמדות ציבוריות תקיפות.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>החדרת דיוק לשוני וביקורת נוסח ככלים הלכתיים מהותיים, מתוך נאמנות למסורת ואומץ אינטלקטואלי.</t>
+          <t>רבנות ממלכתית גאה ועצמאית – שילוב הנהגה, פסיקה ואחריות לאומית.</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>הרי"ף; רבי שלמה אבן פרחון; הראב"ד; בעל המאור; הרמב"ן</t>
+          <t>חכמי בבל; הרבנות הראשית; הרב מרדכי אליהו (תלמיד/השפעה)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5teJp1U9ghLdy4CXNAusRN?si=uqTLoA-PT_yqmv9eyGRw6g&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=88</t>
+          <t>https://open.spotify.com/episode/6M7GqxrkmSgbLaowvUoIbM?si=YsGIvc_wSLu215jfLClMtg</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של רבי אפרים מקלעת חמאד_ מחקר היסטורי והלכתי מקיף.docx</t>
+          <t>מנהיגות, הלכה וממלכתיות_ פועלו ומשנתו התורנית של הראשון לציון הרב יצחק נסים.docx</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של רבי אפרים מקלעת חמאד: מחקר היסטורי והלכתי מקיף</t>
+          <t>מנהיגות, הלכה וממלכתיות: פועלו ומשנתו התורנית של הראשון לציון הרב יצחק נסים</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>565</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>הרמב"ן (רבי משה בן נחמן)</t>
+          <t>הרב מרדכי עטיה</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1194–1270</t>
+          <t>1883–1978</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ספרד, ארץ ישראל</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>פרשנות, הלכה, קבלה</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>ויכוח ברצלונה, פרשנות לתורה, תורת הסוד, עלייה לארץ</t>
-        </is>
-      </c>
+          <t>קבלה</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>פוסק, פרשן ומקובל ששילב את כל רבדי התורה, חידש את יישוב ירושלים ועמד באומץ מול הכנסייה.</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>שילוב פשט, דרש, סוד ופרשנות קבלית – ראיית הטבע כסדרה של ניסים נסתרים.</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>הרמב"ם, בעלי התוספות, הר"ן</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/3ZjAqfQEp21lw1GXKibFGq</t>
-        </is>
-      </c>
+          <t>מקובל וראש ישיבת המקובלים, מחכמי ארם צובא שקבעו משכנם בירושלים. קרא לגאולה מתוך תורת הסוד ומעשה.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>הרמב_ן_ ניתוח רב-ממדי של הגות, הלכה ומנהיגות במאה ה-13.docx</t>
+          <t>הרב מרדכי עטיה.docx</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ן: ניתוח רב-ממדי של הגות, הלכה ומנהיגות במאה ה-13</t>
+          <t>הרב מרדכי עטיה</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>566</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>חכמי פרובנס – בין נרבון, בית דוד והמיסטיקה הראשונה: המרכז היהודי ששבר את המפה הרוחנית של ימי הביניים</t>
+          <t>הרב משה צוריאל</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>המאות ה־11–13</t>
+          <t>1938–2023</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>פרובנס; נרבון; דרום צרפת</t>
+          <t>בני ברק</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>היסטוריה ותולדות</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>הלכה ותלמוד, מפגש ספרד–אשכנז, נשיאות נרבון, קבלה מוקדמת, חסידות אשכנז, מוסדות</t>
-        </is>
-      </c>
+          <t>מוסר, מחשבה, קבלה</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>פרובנס מתוארת כמרחב מפגש בין הלכה ספרדית שיטתית לדיאלקטיקה אשכנזית-צרפתית, וכמוקד מדיני-תורני סביב נרבון והמסורת הנשיאותית. מתוך המתח הזה נולדת קבלה מוקדמת בסינתזה עם חסידות אשכנז. הפרק מציג כיצד מרכז אזורי קטן שינה את המפה הרוחנית של ימי הביניים והכין קרקע להתפתחויות מאוחרות.</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>מפגש מסורות כמנוע יצירה: סינתזה בין ספרד–אשכנז שמולידה מרכז הלכתי ומיסטי חדש.</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>הראב"ד; הרז"ה; האחים הכהן; יצחק סגי נהור</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/28wg8VCd8QFBLQiEa8y15f?si=ai8T1gHuSUulzXa6z02hwA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>משגיח ישיבת 'שעלבים' ומחבר פורה. כינס וביאר את כתבי הראי"ה קוק, הגר"א והרמח"ל — גשר בין עולם המוסר לתורת ארץ ישראל.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>אור הגנוז במדבר_ משנתו הקבלית והנהגתו הרוחנית של המקובל רבי ברוך שפירא זצ_ל.docx</t>
+          <t>הרב משה צוריאל.docx</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>אור הגנוז במדבר: משנתו הקבלית והנהגתו הרוחנית של המקובל רבי ברוך שפירא זצ"ל</t>
+          <t>הרב משה צוריאל</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>מהפכת הרמב"ם, תגובת ספרד ומורשת הרמ"א – הקרב על נשמתה של התורה</t>
+          <t>הרב צבי הירש חיות (מהר"ץ חיות)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ימי הביניים–המאה ה־16</t>
+          <t>1805–1855</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ספרד; אשכנז; קרקוב</t>
+          <t>גליציה</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>מוסר והגות</t>
+          <t>תורה שבעל פה, הגנה על המסורת, מתודולוגיה</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>פילוסופיה, סדרי לימוד, הלכה, מטאפיזיקה, קבלה, עולם הישיבות, סמכות</t>
+          <t>מנחת קנאות, תורת נביאים, אמנציפציה, גשר מסורת-מחקר</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>דרמה אינטלקטואלית על מטרת לימוד התורה: הרמב"ם מציב את ההשגה המטאפיזית כפסגה, וחכמי ספרד מדגישים את מרכזיות הגמרא ולעיתים את הקבלה. הרמ"א מעצב מודל שבו לימוד הלכה ותלמוד הם עצמם התכלית ובכך מניח יסודות לעולם הישיבות. הפרק מצביע על השלכות לשאלת סמכות תורה שבעל-פה.</t>
+          <t>גדול תורה בגליציה שניסה לגשר בין מחקר זהיר לבין נאמנות מוחלטת לתורה שבעל פה, ובנה שפה של הגנה אינטלקטואלית על המסורת.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>הוויכוח על תכלית התורה: הלכה כתכלית מול פילוסופיה/קבלה כפסגה – ועיצוב עולם הישיבות.</t>
+          <t>גשר נאמן: פתיחות דעת המשרתת אמונה – לא מחליפה אותה.</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם; הרשב"א; הריטב"א; הרמ"א; רש"י ורשב"ם</t>
+          <t>חת"ם סופר; שלמה קלוגר; נחמן קרוכמל (רנ"ק)</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4NKKrtI7AcK5wwQ0ejB7h1?si=jKMxNYqPRq6LQQm_5UMAbw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/7qsdQhzQdtrX80wVbwkfmZ</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות, הלכה ומסורה_ פועלו ומשנתו התורנית של רבי מאיר הלוי אבולעפיה (הרמ_ה) בתקופת המעבר של יהדות ספרד.docx</t>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית_ משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר.docx</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות, הלכה ומסורה: פועלו ומשנתו התורנית של רבי מאיר הלוי אבולעפיה (הרמ"ה) בתקופת המעבר של יהדות ספרד</t>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית: משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>מימון בן יוסף (אב הרמב״ם)</t>
+          <t>הרב צבי הירש קלישר – ציונות דתית לפני הרצל</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1110 בקירוב–1165/1170</t>
+          <t>1795–1874</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>קורדובה, מרוקו, ארץ ישראל ומצרים</t>
+          <t>פרוסיה / ארץ ישראל (חזון)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה, מדע וחינוך</t>
+          <t>הגות ציונית-דתית והלכה</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>רב מימון הדיין, איגרת הנחמה, רמב״ם, אנוסים</t>
+          <t>גאולה בדרך הטבע, יישוב הארץ, חקלאות, קורבנות בלי בית, מדיניות</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>דיין ומנהיג שהיה החוליה המקשרת בין תור הזהב של ספרד לבין מהפכת הרמב״ם. הנהיג קהילות נרדפות, חיזק אנוסים ויצר בביתו הרמוניה בין תורה, מדע ושכל.</t>
+          <t>פוסק שמרן שניסח תוכנית מעשית לגאולה: עלייה, חקלאות ובניין הארץ “מעט מעט”. הציע מהלכים הלכתיים נועזים (כגון דיון בחידוש קורבנות) ופעל מול נדבנים ומעצמות.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>הנחת היסודות האנושיים, ההלכתיים והרעיוניים שמהם צמחה שיטת הרמב״ם.</t>
+          <t>גאולה קמעא קמעא: אחריות אנושית כמצווה – יוזמה לאומית ללא ניתוק מן ההלכה.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>הר״י מיגאש; הרי״ף; הרמב״ם; רבי אברהם בן הרמב״ם; משה הדרעי</t>
+          <t>מונטיפיורי; רוטשילד; נפוליאון השלישי; 'דרישת ציון'</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0N9JxxpJynDDTur8c5c0fd?si=H3uqUkfiSRSw3pYMwoKbnA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/7CWcx0r0X5jRyzuRCBPBDh?si=gf7x1W04SsWqd3iA4wjpMQ</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>משנתו התורנית, פועלו הציבורי ומורשתו של רב מימון הדיין_ חוליה מקשרת בין דורות.docx</t>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית_ משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר.docx</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>משנתו התורנית, פועלו הציבורי ומורשתו של רב מימון הדיין: חוליה מקשרת בין דורות</t>
+          <t>בין אקטיביזם משיחי לשמרנות הלכתית: משנתו התורנית ופועלו הציבורי של הרב צבי הירש קלישר</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>רבי משה הדרשן מנרבונה</t>
+          <t>הרב צבי יהודה הכהן קוק</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>המאה ה-11</t>
+          <t>1891–1982</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>נרבונה</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>מדרש</t>
+          <t>הגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>ספר יסוד, בראשית רבתי</t>
+          <t>מרכז הרב, אתחלתא דגאולה, התיישבות</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>החכם שעיצב את עולם המדרש באירופה והשפיע עמוקות על רש"י.</t>
+          <t>ממשיך דרכו של הראי"ה קוק ומנהיג דור התחייה של הציונות הדתית.</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>שימור ועיבוד אוצרות מדרש קדומים בתוך פרשנות אירופית.</t>
+          <t>חיבור בין מדינת ישראל, לימוד תורה וגאולה.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>רש"י; רבי נתן מרומי</t>
+          <t>הראי"ה קוק; הרב חנן פורת; הרב משה לוינגר</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1PpzvwnJnR9ssTIwkuP4Lj?si=6Muo4ngpS_yzlOrCWj4iKw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/33CjfygeixWek05uscU4qM?si=zHwL0eT7QtWwuw1PHxvNJg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של רבינו מנוח מנרבונה_ פרשנות, קודיפיקציה ומסורת פרובאנסאלית.docx</t>
+          <t>רב אברהם יצחק הכהן קוק.docx</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>פועלו ומשנתו התורנית של רבינו מנוח מנרבונה: פרשנות, קודיפיקציה ומסורת פרובאנסאלית</t>
+          <t>הם יצחק הכהן קוק: אנליזה מקיפה של מהפכת הקודש בתקופת התחייה</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>שמואל בן יצחק</t>
+          <t>הרב צדוק הכהן מלובלין – המיסטיקן האינטלקטואלי</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1190–1256</t>
+          <t>1823–1900</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ברצלונה, ספרד</t>
+          <t>ליטא / לובלין</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>הלכה ודיני ממונות</t>
+          <t>חסידות והגות</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>רבנו שמואל הסרדי, ספר התרומות, ממונות, משפט עברי</t>
+          <t>ספק כתנאי לתורה, תשובה, חטא וזכות, תורה שבעל פה, איזביצא</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי ספרד במאה ה־13 ואחד ממעצבי המשפט העברי. חיבורו 'ספר התרומות' סידר לראשונה באופן שיטתי תחום שלם של דיני ממונות.</t>
+          <t>עילוי ליטאי שנהפך לחסיד בעקבות מפגש עם ר׳ מרדכי יוסף מאיז׳ביצא. מציע תיאולוגיה שבה תורה שבעל‑פה היא התגלות מתמשכת דרך מאבק אנושי, וספק הוא תנאי לגילוי עמוק.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>הפיכת ההלכה המשפטית לשפה חיה, נגישה ושיטתית עבור דיין, סוחר וקהילה כלכלית ממשית.</t>
+          <t>הנפילה כחלק מהמהלך: חטא ותשובה נקראים לאחור כחלק מרצון ה׳; הסכנה האמיתית היא ייאוש.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ן; רבי נתן בן מאיר מטרינקטיי; הטור; שולחן ערוך</t>
+          <t>ר׳ מרדכי יוסף מאיז׳ביצא; הרב דסלר; הרב הוטנר</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5Cdc9RvxyriLFWPFMRfciK?si=P9JIX4Q4TCCtqmGdnswLcA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/6DLhfveOXBJupYoYqgceWx?si=zrPEwB1LQjua2OW_BkVXPw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>דמותו, מעמדו ומשנתו ההלכתית-מדעית של רבי יצחק חזקיה למפרונטי בעיני חכמי ישראל.docx</t>
+          <t>הארת התודעה וסוד הצמצום האנושי_ פועלו, ביוגרפיית העומק ומשנתו התורנית של רבי צדוק הכהן מלובלין.docx</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>דמותו, מעמדו ומשנתו ההלכתית-מדעית של רבי יצחק חזקיה למפרונטי בעיני חכמי ישראל</t>
+          <t>הארת התודעה וסוד הצמצום האנושי: פועלו, ביוגרפיית העומק ומשנתו התורנית של רבי צדוק הכהן מלובלין</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>המהר"י מינץ</t>
+          <t>הרב קלמן שם טוב גפן</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1405–1508</t>
+          <t>1856–1927</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>גרמניה ואיטליה / פדובה</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>הלכה והנהגה קהילתית</t>
+          <t>קבלה, פילוסופיה ומדע</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>פדובה, רנסנס, פסיקה אשכנזית, פורים</t>
+          <t>תורת הממדים</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>רב, פוסק וזקן הדור שהעביר את מרכז התורה האשכנזי אל איטליה של הרנסנס. הנהיג את יהדות פדובה ושילב נאמנות למסורת עם התמודדות הלכתית יצירתית.</t>
+          <t>הוגה שניסה ליצור סינתזה בין קבלה, מדע מודרני ופילוסופיה.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>עיצוב הנהגה הלכתית השומרת על סמכות המסורת בתוך מציאות רנסנסית פתוחה ומשתנה, תוך איזון בין תקיפות לגמישות.</t>
+          <t>המדע והתורה מתארים רבדים שונים של אותה מציאות.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>מהר"ם פאדובה; הרמ"א; אליהו דלמדיגו; דון יצחק אברבנאל</t>
+          <t>הראי״ה קוק, הרצי״ה קוק</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2UFLK856gB3r5MDYUiO2mV?si=GMJjiZMzQjK1asCeXsrPzg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/12f9H8UgJMaWzeIBegbaMu</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הלוי מינץ (מהר_י מינץ).docx</t>
+          <t>משנתו התורנית, הגותו הפילוסופית ופועלו המדעי של הרב שם טוב גפן_ ניתוח אנליטי מקיף של איש אשכולות בפרשת הדרכים של המודרנה.docx</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הלוי מינץ (מהר"י מינץ)</t>
+          <t>משנתו התורנית, הגותו הפילוסופית ופועלו המדעי של הרב שם טוב גפן: ניתוח אנליטי מקיף של איש אשכולות בפרשת הדרכים של המודרנה</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>אליאן עמדו לוי־ולנסי</t>
+          <t>הרב שלמה קרליבך</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3196,69 +2952,53 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1919–2006</t>
+          <t>1925–1994</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>צרפת</t>
+          <t>ארה"ב</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל, מקרא, פסיכואנליזה</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>אסכולת פריז, אברהם, הנני, פרשנות קיומית, נשים</t>
-        </is>
-      </c>
+          <t>נגינה, קירוב</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>הוגה עמוקה שחיברה בין מקרא, פילוסופיה ופסיכואנליזה. ראתה באברהם דמות קיומית של אחריות והיסטוריה.</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>הישות האברהמית – האדם כנוכחות מוסרית היוצרת היסטוריה דרך אמירה 'הנני'.</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>לוינס, מניטו, נהר</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7DJX0cnVGFtntXiLnNdbpj</t>
-        </is>
-      </c>
+          <t>'הרבי המרקד' — מחולל מהפכת הנגינה היהודית בדור התשובה. ניגוניו ופתיחת לבו קירבו רבבות ליהדות.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>אליענה אמדו לוי-ולנסי_ ניתוח רב-תחומי של דיאלוג, זהות וקיום יהודי.docx</t>
+          <t>הרב שלמה קרליבך – ניתוח מונוגרפי מעמיק.docx</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>אליענה אמדו לוי-ולנסי: ניתוח רב-תחומי של דיאלוג, זהות וקיום יהודי</t>
+          <t>הרב שלמה קרליבך – ניתוח מונוגרפי מעמיק</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>האדמו"ר מפיאסצ'נה (1889–1942) – קודש בתוך החורבן: תורה פסיכולוגית, אמונה ועמידה בגטו ורשה</t>
+          <t>הרב שמואל מוהליבר – מנהיג דתי ומבשר הציונות</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3268,69 +3008,69 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1889–1942</t>
+          <t>1824–1898</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>פולין; גטו ורשה</t>
+          <t>מזרח אירופה / ארץ ישראל (מפעל היישוב)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>חסידות; חינוך</t>
+          <t>מנהיגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>אמונה בשבר; פסיכולוגיה רוחנית; חינוך; גטו ורשה</t>
+          <t>חיבת ציון, אחדות דתיים-חילונים, היתר מכירה, התיישבות</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>דיוקן של הרבי מפיאסצ'נה כמחנך והוגה: עומק חסידי, הבנת נפש, ואומץ להמשיך ללמד ולכתוב בתוך גטו ורשה.</t>
+          <t>מנהיג חיבת ציון שהבין שהשיבה לארץ היא משימה מעשית. יצר גשר בין דתיים לחילונים, פעל עם רוטשילד להקמת מושבות, ותמך בהיתר מכירה בפולמוס השמיטה כדי להציל את ההתיישבות.</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>קדושה שמסרבת לברוח: עבודת ה' נבנית מתוך אמת פנימית גם כשהמציאות קורסת.</t>
+          <t>ברית ציבורית רחבה כצורך גאולי: אחדות בין כוחות שונים בעם כדי לבנות מציאות.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>חסידות פולין; כתבי דרשות מן השואה; תנועת המוסר</t>
+          <t>הרצל (כינויו בטקסט); הרב קוק (הספד); רוטשילד; מזכרת בתיה</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ</t>
+          <t>https://open.spotify.com/episode/5T2FtQnfoEkvsFnCYyFBcQ?si=B9g6mdr7TtqbzlQnC1gTMA</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>דו_ח מומחה_ פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ_נה.docx</t>
+          <t>הרב שמואל מוהליבר.docx</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>דו"ח מומחה: פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ'נה</t>
+          <t>הרב שמואל מוהליבר</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>הרבי מפיאסצ'נה</t>
+          <t>חנה סנש</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3340,69 +3080,65 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1889–1943</t>
+          <t>1921–1944</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>פולין</t>
+          <t>בודפשט, הונגריה; נהלל; שדות ים; יוגוסלביה</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>חסידות וחינוך</t>
+          <t>ציונות, שליחות ושירה</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>אש קודש, חובת התלמידים</t>
+          <t>צנחני היישוב, ציונות, תפילה, הליכה לקיסריה, אלי אלי, שליחות, השואה, גבורה, נשים</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>אדמו"ר שחשף את עומק הנשמה גם בתוך אימי השואה.</t>
+          <t>משוררת, צנחנית וגיבורת היישוב שעלתה מהונגריה לארץ ישראל והצטרפה למשימת צניחה מעבר לקווי האויב באירופה. ביומניה ובשיריה חיברה בין זהות יהודית, תפילה, אחריות מוסרית ושליחות לאומית.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>הפיכת המשבר וההסתר למקום של עבודת ה' פנימית.</t>
+          <t>רוחניות אמיתית אינה מסתגרת מן המציאות אלא מחייבת פעולה; תפילה, אחריות לעם ונכונות למעשה יכולות להשתלב בשליחות מוסרית אחת.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>גטו ורשה; בני מחשבה טובה</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>קטרינה סנש, גיורא סנש, צנחני היישוב, קיבוץ שדות ים</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>דו_ח מומחה_ פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ_נה.docx</t>
+          <t>פועלה, הגותה ומשנתה הרוחנית-תורנית של חנה סנש- ניתוח היסטורי, ספרותי ותיאולוגי.docx</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>דו"ח מומחה: פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ'נה</t>
+          <t>פועלה, הגותה ומשנתה הרוחנית-תורנית של חנה סנש: ניתוח היסטורי, ספרותי ותיאולוגי</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>הרבנית בת שבע אסתר קניבסקי</t>
+          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3412,65 +3148,69 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1932–2011</t>
+          <t>1886–1929</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; בני ברק</t>
+          <t>גרמניה</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>חסד, תפילה והנהגה רוחנית לנשים</t>
+          <t>פילוסופיה יהודית מודרנית</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>בית רשב״ם, חסד, תפילה, תהילים, עצה וברכה, צניעות, נשים</t>
+          <t>כוכב הגאולה, התגלות, דיאלוג, יהדות ונצרות, תרגום תנ"ך, ALS</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>בתו של הרב יוסף שלום אלישיב, נכדת רבי אריה לוין ורעיית הרב חיים קניבסקי. ביתה בבני ברק הפך לכתובת לאלפי נשים שביקשו עצה, תפילה וחיזוק, ולמוקד של צדקה, סיוע למשפחות וליווי חולים.</t>
+          <t>ב'כוכב הגאולה' מפרק את ה'כוליות' ומציע מבנה של אלוהים-אדם-עולם דרך בריאה/התגלות/גאולה. הקים Lehrhaus בפרנקפורט ותרגם תנ"ך עם בובר, תוך התמודדות עם ALS.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>השפעה רוחנית אינה תלויה בתפקיד רשמי: הקשבה אישית, חסד ואמונה פשוטה יכולות להפוך בית פרטי למרכז של תקווה ואהבת ישראל.</t>
+          <t>התגלות כדיבור ואהבה שמולידים אחריות; אמת נוצרת במפגש ולא במערכת מופשטת.</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>הרב יוסף שלום אלישיב (אביה), רבי אריה לוין (סבה), הרב חיים קניבסקי (בעלה), הרבנית לאה קולדצקי (בתה)</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>מרטין בובר; Lehrhaus; עמנואל לוינס (השפעה מאוחרת)</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/7EpaIjYgIJVmSWDAsXDI7g?si=u6IC097XQ-KpBRfRRIGqcg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>מורשת הרבנית קנייבסקי_ כוח התפילה, התהילים והפרשת החלה.docx</t>
+          <t>פרנץ רוזנצווייג.docx</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>מורשת הרבנית קנייבסקי: כוח התפילה, התהילים והפרשת החלה</t>
+          <t>פרנץ רוזנצווייג</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>שד"ל – הלוחם האחרון של היהדות הרגשית מול כיבוש השכל היווני</t>
+          <t>רבי משה חגיז – הקנאי הירושלמי שניסה להציל את היהדות מן הקריסה הפנימית</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3480,69 +3220,69 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1800–1865</t>
+          <t>1671–1750</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>פאדובה; איטליה</t>
+          <t>ירושלים; איטליה; אמסטרדם; אירופה</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>פרשנות מקרא ולשון</t>
+          <t>פסיקה והנהגה קהילתית</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>חכמת ישראל, פרשנות מקרא, פילולוגיה, רציונליזם, אמונה, חמלה, ביקורת יוון</t>
+          <t>אחר שבתאות, פולמוס, סמכות חכמים, גבולות קבלה, השכלה, לקט הקמח</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>שד"ל טען שהיהדות האותנטית היא דת של חמלה ואמונה ולא של שכל קר, ובנה מפעל מדעי (לשון, מקרא, ביקורת טקסט) כדי להגן על חיות המסורת. הוא נאבק בחוגי חכמת ישראל שנראו לו כמי שהופכים יהדות לארכיאולוגיה, ותקף את הכנסת "חכמת יוון" ליהדות. כאב חייו חיזק אצלו את עליונות האמונה והמעשה הטוב.</t>
+          <t>חגיז פעל לאחר טראומת השבתאות כקנאי-אחראי להצבת גבולות מול מה שראה כהתפוררות המסורת. משבר אישי הוביל אותו להתמסר לכתיבה ולפולמוס, ולעימותים שהדהדו בקהילות אירופה. ב"לקט הקמח" ביקש לשרטט סדר מחודש ולהחזיר סמכות הלכתית מרכזית, גם במחיר של קיטוב ומחלוקת.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>הגנה על יהדות של חמלה ואמונה מול רציונליזם קר – באמצעות מחקר מקרא ולשון.</t>
+          <t>קנאות כאחריות: שרטוט גבולות כדי למנוע קריסה רוחנית אחרי שבתאות – במחיר גבוה.</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>חכמת ישראל; רמב"ם; ראב"ע; שפינוזה</t>
+          <t>נחמיה חיון; החכם צבי; הרמח"ל; ר' יונתן אייבשיץ</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/03tAgaC9jfaMhMJ2rvW4uF?si=cgIj0F37SiKtDyDT85ZqKA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/2kCpBIWS1B2NtObhJemSdG?si=CHbvRGp1RkW_Lj5w4HGnsQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי_ עיצוב היהדות בעידן המשבר והשיקום(1).docx</t>
+          <t>פועלו ומשנתו התורנית של רבי משה חגיז_ שומר חומות המסורת בעידן התמורות.docx</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי: עיצוב היהדות בעידן המשבר והשיקום</t>
+          <t>פועלו ומשנתו התורנית של רבי משה חגיז: שומר חומות המסורת בעידן התמורות</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>590</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>שושלת אבוחצירא</t>
+          <t>רבי רפאל ברוך טולידאנו</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3552,116 +3292,84 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־19–20</t>
+          <t>1890–1971</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>מרוקו, ארץ ישראל</t>
+          <t>מקנס</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>קבלה, הנהגה, פיוט</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
-        </is>
-      </c>
+          <t>הלכה, פיוט</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
-        </is>
-      </c>
+          <t>ראב"ד מקנס ומחבר 'קיצור שולחן ערוך' לבני ספרד. פיוטו 'אשתחווה אפיים ארצה' מושר בכל תפוצות המזרח.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>סביר — לבדיקה</t>
+          <t>מאושר</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>רבי יעקב אבוחצירא_ האביר יעקב בראי הדורות.docx</t>
+          <t>רבי רפאל ברוך טולידאנו.docx</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>רבי יעקב אבוחצירא: האביר יעקב בראי הדורות</t>
+          <t>רבי רפאל ברוך טולידאנו</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>584</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
+          <t>רבי ישמעאל (בן אלישע)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>תנאים</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־19 (פרסום 1843)</t>
+          <t>60–135</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
+          <t>ארץ ישראל</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל (קבלה)</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
-        </is>
-      </c>
+          <t>מדרש הלכה</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE?si=N2J3HnklTRW2Gm-BmT4SFA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>אב עולם ובעל שלוש-עשרה המידות שהתורה נדרשת בהן. בר פלוגתא הגדול של רבי עקיבא בדרכי המדרש — 'דיברה תורה כלשון בני אדם'.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
           <t>סביר — לבדיקה</t>
@@ -3669,907 +3377,1043 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>אדולף פרנק בספרו _הקבלה_.docx</t>
+          <t>פועלו ומשנתו התורנית של התנא רבי ישמעאל_ ניתוח הרמנויטי, הלכתי וביוגרפי של אב עולם.docx</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>אדולף פרנק בספרו "הקבלה"</t>
+          <t>פועלו ומשנתו התורנית של התנא רבי ישמעאל: ניתוח הרמנויטי, הלכתי וביוגרפי של אב עולם</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>262</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>בת שבע</t>
+          <t>הרב אפרים מקלעת־חמאד</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>המלכים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>תקופת דוד ושלמה</t>
+          <t>בערך 1050–1150</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; ממלכת ישראל</t>
+          <t>קלעת בן חמאד, צפון אפריקה</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>מלכות, הנהגה וחכמה</t>
+          <t>הלכה, נוסח ודקדוק</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, שלמה המלך, נתן הנביא, אם המלך, אשת חיל, משלי, משפט צדק, נשים</t>
+          <t>הרי"ף, דקדוק עברי, ביקורת נוסח, קירואן</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>אשת דוד ואמו של שלמה, שבספר מלכים מתגלה כדמות מדינית נחושה: היא פועלת עם נתן הנביא להבטחת המלכת שלמה, ולאחר מכן זוכה למעמד ״אם המלך״. במסורת חז״ל היא מזוהה עם אמו של למואל המוכיחה את בנה על אחריות המלכות.</t>
+          <t>מן הדמויות העמוקות שבין תקופת הגאונים לראשוני ספרד ופרובנס, 'תלמיד חבר' של הרי"ף. הגהותיו נטמעו בספר ההלכות, והוא שילב רגישות פילולוגית ודקדוקית בתוך הפסיקה.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>הכתר אינו זכות בלבד אלא אחריות מוסרית; בת שבע מייצגת את הכוח להציב גבולות למלך ולדרוש ממנו צדק, משמעת עצמית ודאגה לחלשים.</t>
+          <t>החדרת דיוק לשוני וביקורת נוסח ככלים הלכתיים מהותיים, מתוך נאמנות למסורת ואומץ אינטלקטואלי.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, שלמה המלך, נתן הנביא, אדוניהו בן חגית</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>הרי"ף; רבי שלמה אבן פרחון; הראב"ד; בעל המאור; הרמב"ן</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5teJp1U9ghLdy4CXNAusRN?si=uqTLoA-PT_yqmv9eyGRw6g&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv&amp;t=88</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>נפסל — מסמך של אדם אחר</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבי אפרים מקלעת חמאד_ מחקר היסטורי והלכתי מקיף.docx</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>פועלו ומשנתו התורנית של רבי אפרים מקלעת חמאד: מחקר היסטורי והלכתי מקיף</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>צרויה</t>
+          <t>הרמב"ן (רבי משה בן נחמן)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>המלכים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>תקופת דוד המלך</t>
+          <t>1194–1270</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>בית לחם; ממלכת דוד</t>
+          <t>ספרד, ארץ ישראל</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>בית דוד, משפחה ומלוכה</t>
+          <t>פרשנות, הלכה, קבלה</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, יואב, אבישי, עשהאל, בני צרויה, הנהגה, גבורה, מלכות, נשים</t>
+          <t>ויכוח ברצלונה, פרשנות לתורה, תורת הסוד, עלייה לארץ</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>אחותו של דוד המלך ובתו של ישי, ששמה נשמר במקרא בעיקר דרך שלושת בניה - יואב, אבישי ועשהאל. הייחוס החוזר של הבנים דווקא לאמם הפך את צרויה לסמל משפחתי המזוהה עם כוח, גבורה ונאמנות לבית דוד.</t>
+          <t>פוסק, פרשן ומקובל ששילב את כל רבדי התורה, חידש את יישוב ירושלים ועמד באומץ מול הכנסייה.</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>המתח בין דוד לבין בני צרויה ממחיש את הצורך והסכנה שבחיבור בין חסד לכוח: המלכות זקוקה לעוצמה צבאית, אך גם לריסון מוסרי ולהנהגה רוחנית.</t>
+          <t>שילוב פשט, דרש, סוד ופרשנות קבלית – ראיית הטבע כסדרה של ניסים נסתרים.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>דוד המלך, ישי, יואב בן צרויה, אבישי בן צרויה, עשהאל בן צרויה</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
+          <t>הרמב"ם, בעלי התוספות, הר"ן</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3ZjAqfQEp21lw1GXKibFGq</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>הרמב_ן_ ניתוח רב-ממדי של הגות, הלכה ומנהיגות במאה ה-13.docx</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>הרמב"ן: ניתוח רב-ממדי של הגות, הלכה ומנהיגות במאה ה-13</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>בן סירא</t>
+          <t>חכמי פרובנס – בין נרבון, בית דוד והמיסטיקה הראשונה: המרכז היהודי ששבר את המפה הרוחנית של ימי הביניים</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>בית שני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>סביב 190 לפנה״ס</t>
+          <t>המאות ה־11–13</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ירושלים; מצרים (תרגום/תוספות הנכד)</t>
+          <t>פרובנס; נרבון; דרום צרפת</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>חכמה ומוסר</t>
+          <t>היסטוריה ותולדות</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>ספרות בית שני, מוסר ודרך ארץ, גבולות קאנון, השפעה חז"לית</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
+          <t>הלכה ותלמוד, מפגש ספרד–אשכנז, נשיאות נרבון, קבלה מוקדמת, חסידות אשכנז, מוסדות</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>פרובנס מתוארת כמרחב מפגש בין הלכה ספרדית שיטתית לדיאלקטיקה אשכנזית-צרפתית, וכמוקד מדיני-תורני סביב נרבון והמסורת הנשיאותית. מתוך המתח הזה נולדת קבלה מוקדמת בסינתזה עם חסידות אשכנז. הפרק מציג כיצד מרכז אזורי קטן שינה את המפה הרוחנית של ימי הביניים והכין קרקע להתפתחויות מאוחרות.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>מפגש מסורות כמנוע יצירה: סינתזה בין ספרד–אשכנז שמולידה מרכז הלכתי ומיסטי חדש.</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>הראב"ד; הרז"ה; האחים הכהן; יצחק סגי נהור</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3u5udRWI84FVJ3OsOBBbPF?si=ek7V_WzPS7OadSPOZSU-VA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/28wg8VCd8QFBLQiEa8y15f?si=ai8T1gHuSUulzXa6z02hwA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>נפסל — מסמך של אדם אחר</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>אור הגנוז במדבר_ משנתו הקבלית והנהגתו הרוחנית של המקובל רבי ברוך שפירא זצ_ל.docx</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>אור הגנוז במדבר: משנתו הקבלית והנהגתו הרוחנית של המקובל רבי ברוך שפירא זצ"ל</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>שמעון כיפא – מרטיר נוצרי או צדיק נסתר ששלחו חכמי ישראל?</t>
+          <t>מהפכת הרמב"ם, תגובת ספרד ומורשת הרמ"א – הקרב על נשמתה של התורה</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>בית שני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>המאות הראשונות לספירה</t>
+          <t>ימי הביניים–המאה ה־16</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ארץ ישראל; רומא; ראשית הנצרות</t>
+          <t>ספרד; אשכנז; קרקוב</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>מסורת ופולמוס</t>
+          <t>מוסר והגות</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>יהדות–נצרות, מסורות אזוטריות, זהות, פולמוס, ליטורגיה, ט' בטבת</t>
+          <t>פילוסופיה, סדרי לימוד, הלכה, מטאפיזיקה, קבלה, עולם הישיבות, סמכות</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>הפרק מציג את הפער בין המסורת הנוצרית על פטרוס לבין מסורות יהודיות המציירות את שמעון כיפא כשליח נסתר שנועד ליצור הפרדה בין יהדות לנצרות כדי למנוע שפיכות דמים והתבוללות. לפי הסיפור, הוא עיצב מנהגים ותיאולוגיה שמרחיקים מן היהדות ובמקביל למד תורה בסתר. מוצגים גם ייחוסים ליטורגיים ומסורות סביב צום ט' בטבת.</t>
+          <t>דרמה אינטלקטואלית על מטרת לימוד התורה: הרמב"ם מציב את ההשגה המטאפיזית כפסגה, וחכמי ספרד מדגישים את מרכזיות הגמרא ולעיתים את הקבלה. הרמ"א מעצב מודל שבו לימוד הלכה ותלמוד הם עצמם התכלית ובכך מניח יסודות לעולם הישיבות. הפרק מצביע על השלכות לשאלת סמכות תורה שבעל-פה.</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>מסורות כמנגנון זהות: סיפור 'שליח נסתר' שמפרש פילוג דתי כצעד הגנתי של הקהילה.</t>
+          <t>הוויכוח על תכלית התורה: הלכה כתכלית מול פילוסופיה/קבלה כפסגה – ועיצוב עולם הישיבות.</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>ספר חסידים; אוצר המדרשים; תולדות ישו</t>
+          <t>הרמב"ם; הרשב"א; הריטב"א; הרמ"א; רש"י ורשב"ם</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4tu43oeL4qVdXGKzX2025J?si=G3-56Xu3TxKoDiSCHX9gEA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/4NKKrtI7AcK5wwQ0ejB7h1?si=jKMxNYqPRq6LQQm_5UMAbw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה ומסורה_ פועלו ומשנתו התורנית של רבי מאיר הלוי אבולעפיה (הרמ_ה) בתקופת המעבר של יהדות ספרד.docx</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות, הלכה ומסורה: פועלו ומשנתו התורנית של רבי מאיר הלוי אבולעפיה (הרמ"ה) בתקופת המעבר של יהדות ספרד</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>292</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ילתא</t>
+          <t>מימון בן יוסף (אב הרמב״ם)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>אמוראים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־3–4 לספירה</t>
+          <t>1110 בקירוב–1165/1170</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>בבל</t>
+          <t>קורדובה, מרוקו, ארץ ישראל ומצרים</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה ומעמד נשים</t>
+          <t>הלכה, הנהגה, מדע וחינוך</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>רב נחמן, עולא, רבה בר בר חנה, היתר ואיסור, כוס של ברכה, 400 חביות יין, נשים</t>
+          <t>רב מימון הדיין, איגרת הנחמה, רמב״ם, אנוסים</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>בת למשפחת ראש הגולה ורעייתו של רב נחמן, מן הדמויות הנשיות הבולטות בתלמוד. היא מביעה רעיונות הלכתיים מקוריים, עומדת על דעתה מול חכמים, פונה לבירור הלכתי נוסף בעת הצורך ואף מייעצת לבעלה בענייני הנהגה.</t>
+          <t>דיין ומנהיג שהיה החוליה המקשרת בין תור הזהב של ספרד לבין מהפכת הרמב״ם. הנהיג קהילות נרדפות, חיזק אנוסים ויצר בביתו הרמוניה בין תורה, מדע ושכל.</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>עולם ההלכה כולל לא רק איסורים אלא גם מרחב של היתר, עונג וקדושה; ילתא מגלמת עצמאות אינטלקטואלית, מעמד ציבורי ונוכחות נשית פעילה בעולם האמוראי.</t>
+          <t>הנחת היסודות האנושיים, ההלכתיים והרעיוניים שמהם צמחה שיטת הרמב״ם.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>רב נחמן, עולא, רבה בר בר חנה, רב יצחק בריה דרב יהודה</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
+          <t>הר״י מיגאש; הרי״ף; הרמב״ם; רבי אברהם בן הרמב״ם; משה הדרעי</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0N9JxxpJynDDTur8c5c0fd?si=H3uqUkfiSRSw3pYMwoKbnA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>משנתו התורנית, פועלו הציבורי ומורשתו של רב מימון הדיין_ חוליה מקשרת בין דורות.docx</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>משנתו התורנית, פועלו הציבורי ומורשתו של רב מימון הדיין: חוליה מקשרת בין דורות</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>291</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>רבי חייא הגדול</t>
+          <t>שמואל בן יצחק</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>אמוראים</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־2–3 לספירה</t>
+          <t>1190–1256</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>בבל, טבריה</t>
+          <t>ברצלונה, ספרד</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>תורה שבעל פה, חינוך</t>
+          <t>הלכה ודיני ממונות</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>שכחת התורה, תוספתא, מסירות</t>
+          <t>רבנו שמואל הסרדי, ספר התרומות, ממונות, משפט עברי</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>הציל את התורה משכחה בפעולה מעשית כוללת. שילב עמל גשמי ורוחני כדי להעביר מסורת.</t>
+          <t>מגדולי חכמי ספרד במאה ה־13 ואחד ממעצבי המשפט העברי. חיבורו 'ספר התרומות' סידר לראשונה באופן שיטתי תחום שלם של דיני ממונות.</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>תורה נשמרת במעשה. אחריות אישית להעברה דורית.</t>
+          <t>הפיכת ההלכה המשפטית לשפה חיה, נגישה ושיטתית עבור דיין, סוחר וקהילה כלכלית ממשית.</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הנשיא, רבי אושעיה</t>
+          <t>הרמב״ן; רבי נתן בן מאיר מטרינקטיי; הטור; שולחן ערוך</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4MI4LUL2FI4WeVtEdPZS5F</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="3" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/5Cdc9RvxyriLFWPFMRfciK?si=P9JIX4Q4TCCtqmGdnswLcA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>דמותו, מעמדו ומשנתו ההלכתית-מדעית של רבי יצחק חזקיה למפרונטי בעיני חכמי ישראל.docx</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>דמותו, מעמדו ומשנתו ההלכתית-מדעית של רבי יצחק חזקיה למפרונטי בעיני חכמי ישראל</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>אברהם בר חייא</t>
+          <t>המהר"י מינץ</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>המאה ה-12</t>
+          <t>1405–1508</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ברצלונה</t>
+          <t>גרמניה ואיטליה / פדובה</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>מדע, פילוסופיה</t>
+          <t>הלכה והנהגה קהילתית</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>בר חייא, פילוסופיה, מדע יהודי, מתמטיקה</t>
+          <t>פדובה, רנסנס, פסיקה אשכנזית, פורים</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>היהודי הראשון שכתב מדע בעברית והשפיע על תרגום חכמת המזרח לאירופה.</t>
+          <t>רב, פוסק וזקן הדור שהעביר את מרכז התורה האשכנזי אל איטליה של הרנסנס. הנהיג את יהדות פדובה ושילב נאמנות למסורת עם התמודדות הלכתית יצירתית.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>שילוב בין תורה, מדע ופילוסופיה; תרגום חכמה כללית לעברית.</t>
+          <t>עיצוב הנהגה הלכתית השומרת על סמכות המסורת בתוך מציאות רנסנסית פתוחה ומשתנה, תוך איזון בין תקיפות לגמישות.</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>פיבונאצ'י, חכמי ספרד</t>
+          <t>מהר"ם פאדובה; הרמ"א; אליהו דלמדיגו; דון יצחק אברבנאל</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3FAGqYdzyMQbyPbon3KYoC</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="3" t="inlineStr"/>
-      <c r="N52" s="3" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/2UFLK856gB3r5MDYUiO2mV?si=GMJjiZMzQjK1asCeXsrPzg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>רבי יהודה הלוי מינץ (מהר_י מינץ).docx</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>רבי יהודה הלוי מינץ (מהר"י מינץ)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>הראב"ן</t>
+          <t>אליאן עמדו לוי־ולנסי</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1090–1170 בקירוב</t>
+          <t>1919–2006</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>מגנצא</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>הלכה והיסטוריה</t>
+          <t>מחשבת ישראל, מקרא, פסיכואנליזה</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>גזרות תתנ"ו</t>
+          <t>אסכולת פריז, אברהם, הנני, פרשנות קיומית, נשים</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>החכם שתיעד את החורבן ובנה מחדש את יהדות אשכנז.</t>
+          <t>הוגה עמוקה שחיברה בין מקרא, פילוסופיה ופסיכואנליזה. ראתה באברהם דמות קיומית של אחריות והיסטוריה.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>הפיכת זיכרון החורבן ליסוד של בנייה רוחנית.</t>
+          <t>הישות האברהמית – האדם כנוכחות מוסרית היוצרת היסטוריה דרך אמירה 'הנני'.</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>רבנו תם; הרשב"ם; הרא"ש</t>
+          <t>לוינס, מניטו, נהר</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5QGbbhxhb2hremjTS5I9E8?si=wQyrfYb9SgeVnHb998KX6w&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="3" t="inlineStr"/>
-      <c r="N53" s="3" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/7DJX0cnVGFtntXiLnNdbpj</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>אליענה אמדו לוי-ולנסי_ ניתוח רב-תחומי של דיאלוג, זהות וקיום יהודי.docx</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>אליענה אמדו לוי-ולנסי: ניתוח רב-תחומי של דיאלוג, זהות וקיום יהודי</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>הרד״ק</t>
+          <t>האדמו"ר מפיאסצ'נה (1889–1942) – קודש בתוך החורבן: תורה פסיכולוגית, אמונה ועמידה בגטו ורשה</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1160–1235</t>
+          <t>1889–1942</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>פרובאנס</t>
+          <t>פולין; גטו ורשה</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>מקרא ודקדוק</t>
+          <t>חסידות; חינוך</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>ספר השורשים, ספר המכלול</t>
+          <t>אמונה בשבר; פסיכולוגיה רוחנית; חינוך; גטו ורשה</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>מגדולי פרשני המקרא והמדקדקים, ממעצבי דרך הפשט בלימוד התנ״ך.</t>
+          <t>דיוקן של הרבי מפיאסצ'נה כמחנך והוגה: עומק חסידי, הבנת נפש, ואומץ להמשיך ללמד ולכתוב בתוך גטו ורשה.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>הבנת לשון הקודש כמפתח להבנת התורה.</t>
+          <t>קדושה שמסרבת לברוח: עבודת ה' נבנית מתוך אמת פנימית גם כשהמציאות קורסת.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>רבי יוסף קמחי, הרמב״ם</t>
+          <t>חסידות פולין; כתבי דרשות מן השואה; תנועת המוסר</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7t7Mwzw5zr9XQ4uPrDcKcz</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="3" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD?si=fGjrjZNLSu6BZj6EPEL5iQ</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>דו_ח מומחה_ פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ_נה.docx</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>דו"ח מומחה: פועלו ומשנתו התורנית של רבי קלונימוס קלמיש שפירא מפיאסצ'נה</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>הריצב״א</t>
+          <t>הרבנית בת שבע אסתר קניבסקי</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־12–13</t>
+          <t>1932–2011</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>צרפת</t>
+          <t>ירושלים; בני ברק</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, תוספות וסוד</t>
+          <t>חסד, תפילה והנהגה רוחנית לנשים</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>ר״י הבחור, רבנו תם, ר״י הזקן, מעשה מרכבה</t>
+          <t>בית רשב״ם, חסד, תפילה, תהילים, עצה וברכה, צניעות, נשים</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>מן הדמויות המרכזיות בדור שלאחר רבנו תם בעולם התוספות. שילב עצמאות למדנית ושימוש רחב בירושלמי עם מוניטין של איש חזיונות וסודות הבריאה.</t>
+          <t>בתו של הרב יוסף שלום אלישיב, נכדת רבי אריה לוין ורעיית הרב חיים קניבסקי. ביתה בבני ברק הפך לכתובת לאלפי נשים שביקשו עצה, תפילה וחיזוק, ולמוקד של צדקה, סיוע למשפחות וליווי חולים.</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>חיבור נדיר בין חריפות דיאלקטית תלמודית לבין עומק מיסטי, כגשר בין אשכנז, ספרד ועולמות הסוד.</t>
+          <t>השפעה רוחנית אינה תלויה בתפקיד רשמי: הקשבה אישית, חסד ואמונה פשוטה יכולות להפוך בית פרטי למרכז של תקווה ואהבת ישראל.</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>רבנו תם; ר״י הזקן; הרמב״ם; רבי יהודה בר יקר; רבי יחיאל מפאריס</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/0fIS5dc7OCTq1C6amM82LT?si=tqcgKwdFQPuRVDKuMbTmkQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>הרב יוסף שלום אלישיב (אביה), רבי אריה לוין (סבה), הרב חיים קניבסקי (בעלה), הרבנית לאה קולדצקי (בתה)</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>נפסל — מסמך של אדם אחר</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr"/>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>מורשת הרבנית קנייבסקי_ כוח התפילה, התהילים והפרשת החלה.docx</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>מורשת הרבנית קנייבסקי: כוח התפילה, התהילים והפרשת החלה</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>הרמ״ה</t>
+          <t>שד"ל – הלוחם האחרון של היהדות הרגשית מול כיבוש השכל היווני</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1170–1244</t>
+          <t>1800–1865</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ספרד</t>
+          <t>פאדובה; איטליה</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, מסורה והלכה</t>
+          <t>פרשנות מקרא ולשון</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>רבי מאיר הלוי אבולעפיה, יד רמה</t>
+          <t>חכמת ישראל, פרשנות מקרא, פילולוגיה, רציונליזם, אמונה, חמלה, ביקורת יוון</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי ספרד, פוסק, ראש ישיבה ובעל מסורת סייג לתורה.</t>
+          <t>שד"ל טען שהיהדות האותנטית היא דת של חמלה ואמונה ולא של שכל קר, ובנה מפעל מדעי (לשון, מקרא, ביקורת טקסט) כדי להגן על חיות המסורת. הוא נאבק בחוגי חכמת ישראל שנראו לו כמי שהופכים יהדות לארכיאולוגיה, ותקף את הכנסת "חכמת יוון" ליהדות. כאב חייו חיזק אצלו את עליונות האמונה והמעשה הטוב.</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>דיוק במסורת לצד הנהגה הלכתית עצמאית.</t>
+          <t>הגנה על יהדות של חמלה ואמונה מול רציונליזם קר – באמצעות מחקר מקרא ולשון.</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ם, הרמב״ן</t>
+          <t>חכמת ישראל; רמב"ם; ראב"ע; שפינוזה</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3DlGOty8LZ8KGhLiLcyqjs</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="3" t="inlineStr"/>
-      <c r="N56" s="3" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/03tAgaC9jfaMhMJ2rvW4uF?si=cgIj0F37SiKtDyDT85ZqKA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי_ עיצוב היהדות בעידן המשבר והשיקום(1).docx</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>פועלו, משנתו התורנית ומנהיגותו של רבן יוחנן בן זכאי: עיצוב היהדות בעידן המשבר והשיקום</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>מחזור ויטרי</t>
+          <t>שושלת אבוחצירא</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1105 בקירוב</t>
+          <t>המאה ה־19–20</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>צרפת</t>
+          <t>מרוקו, ארץ ישראל</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>ליטורגיה והלכה</t>
+          <t>קבלה, הנהגה, פיוט</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>מחזור ויטרי, רבנו שמחה מוויטרי</t>
+          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>אנציקלופדיה הלכתית וליטורגית מבית מדרשו של רש״י, המשמרת את נוסח צרפת ומסורות אשכנז הקדומות.</t>
+          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>חיבור בין תפילה, הלכה, אגדה וחיי קהילה.</t>
+          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>רש״י, בעלי התוספות</t>
+          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6xiWssuJyV4GypDbnlCpl0</t>
+          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>נפסל — מסמך של אדם אחר</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr"/>
-      <c r="N57" s="3" t="inlineStr"/>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>רבי יעקב אבוחצירא_ האביר יעקב בראי הדורות.docx</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>רבי יעקב אבוחצירא: האביר יעקב בראי הדורות</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ספר הכוזרי</t>
+          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>המאה ה־19 (פרסום 1843)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ספרד / אל־אנדלוס</t>
+          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>הגות ואמונה</t>
+          <t>מחשבת ישראל (קבלה)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הלוי, אמונה, סיני, ארץ ישראל</t>
+          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>אחד מחיבורי היסוד של המחשבה היהודית, שנכתב בידי רבי יהודה הלוי בערבית יהודית. מציג הגנה מקורית על היהדות דרך ההיסטוריה, ההתגלות הלאומית והקשר בין עם, מצוות וארץ.</t>
+          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>ביסוס האמונה היהודית על זיכרון היסטורי לאומי והתגלות ציבורית, ולא רק על הוכחה פילוסופית מופשטת.</t>
+          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>רבי יהודה הלוי; הרמב"ם; הרב קוק; ביאליק</t>
+          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0E55prQ6VaFsIXKSiCpDe3?si=XrQKU-Z0TgKEvgDDjH-MFQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE?si=N2J3HnklTRW2Gm-BmT4SFA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>נפסל — מסמך של אדם אחר</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="3" t="inlineStr"/>
+          <t>סביר — לבדיקה</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>אדולף פרנק בספרו _הקבלה_.docx</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>אדולף פרנק בספרו "הקבלה"</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>רבי אביגדור כ״ץ</t>
+          <t>הרב לורד יונתן זקס</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>המאה ה־13</t>
+          <t>1948–2020</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>איטליה, גרמניה ואוסטריה</t>
+          <t>אנגליה</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>הלכה והנהגה</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>חידושי תוספות</t>
-        </is>
-      </c>
+          <t>הגות, הנהגה</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>ממנהיגי יהדות אוסטריה ומחבר בין מסורות איטליה, אשכנז וצרפת.</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>בניית רצף מסורת באמצעות תלמידים וקהילות.</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>המהר״ם מרוטנבורג</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/0Gbt6DvaXHHA3NQUKn6gAe</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="3" t="inlineStr"/>
-      <c r="N59" s="3" t="inlineStr"/>
+          <t>רבה הראשי של בריטניה והוגה יהודי בעל השפעה עולמית. הציג את קול התורה בשפת הפילוסופיה והמוסר האוניברסלי.</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>לא ודאי</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>הרב לורד יונתן זקס.docx</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>nathan Sacks: A Comprehensive Analysis of Modern Jewish Thought and Global Ethics</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>רבי יוסף חיון (רי״ח)</t>
+          <t>יעקב אבינו</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>האבות</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>מאה 15</t>
+          <t>1652–1505 לפנה״ס</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ליסבון, פורטוגל</t>
+          <t>חברון</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>פרשנות מקרא/תיאולוגיה</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>תורה מן השמים, דיוק לשוני, ספר דברים, פרשנות סמנטית</t>
-        </is>
-      </c>
+          <t>תורה, אמת</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>מנהיג קהילת ליסבון ומורו של האברבנאל. פיתח פתרון לשאלת 'דברים מפי עצמו' ועיקרון שאין כפל עניין בתנ״ך.</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>משה ניסח נאומים, אך ה׳ הכתיב לו מילה במילה בעת כתיבת התורה; כל מילה במקרא ייחודית ואין 'נרדפות' סתמית.</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>דון יצחק אברבנאל; קנפנטון; המלבי״ם (הקדמה רעיונית)</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
-        </is>
-      </c>
+          <t>בחיר האבות ואבי שנים־עשר השבטים. 'איש תם יושב אוהלים' שירד למצרים והניח את יסוד בית ישראל.</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="3" t="inlineStr"/>
@@ -4577,51 +4421,43 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>571</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>רבי יצחק קנפנטון</t>
+          <t>יצחק אבינו</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>האבות</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1360–1463</t>
+          <t>1712–1532 לפנה״ס</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>קסטיליה; ספרד</t>
+          <t>חברון</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>למדנות תלמודית</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>דרכי התלמוד, גאון מקסטיליה</t>
-        </is>
-      </c>
+          <t>גבורה, תפילה</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
+          <t>השני שבאבות. נעקד על גבי המזבח בהר המוריה, וחפר מחדש את בארות אביו — ממשיך הדרך בארץ.</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/2xytN0uGuTq03wNYWvusDO?si=GjQi6caQRZGdjDrWc8cX7w</t>
-        </is>
-      </c>
+      <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="3" t="inlineStr"/>
@@ -4629,59 +4465,47 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>574</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>רבנו חננאל בן חושיאל</t>
+          <t>משה רבנו</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>יציאת מצרים</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>מאה 11</t>
+          <t>1391–1271 לפנה״ס</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>קירואן (צפון אפריקה)</t>
+          <t>מצרים</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>פירוש תלמוד/פסיקה</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
-        </is>
-      </c>
+          <t>תורה, נבואה, הנהגה</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
+          <t>אדון הנביאים ומקבל התורה בסיני. הוציא את ישראל ממצרים, קיבל את הלוחות ומסר תורה לכל ישראל — ראש שלשלת הקבלה.</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
-        </is>
-      </c>
+          <t>משה קיבל תורה מסיני ומסרה ליהושע (אבות א, א)</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="inlineStr"/>
@@ -4689,59 +4513,43 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
+          <t>שמואל הנביא</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>השופטים</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1100–1171</t>
+          <t>1120–1012 לפנה״ס</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>צרפת (אשכנז)</t>
+          <t>ארץ ישראל</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>תלמוד ושיטה למדנית</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>תוספות, שתי שקיעות, תפילין, תקנות, מסעות הצלב</t>
-        </is>
-      </c>
+          <t>נבואה, הנהגה</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>נכדו של רש״י שבנה את שיטת בעלי התוספות: לא מוותרים על סתירות – מחברים סוגיות וגשרים. במקביל היה מנהיג קהילה בתקופת מסעי הצלב ותקן תקנות חברתיות.</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>נאמנות קשוחה לנוסח הגמרא (“בספרים אל ימחק”) שמכריחה עומק, דיוק וחילוקים – ומייצרת לימוד יוצר.</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>בעלי התוספות; רש״י; מנהג זמן רבנו תם</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ?si=o5kksAmaQNiRkBHxN8CVpQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>אחרון השופטים וגדול הנביאים אחרי משה. הקים את המלוכה בישראל ומשח את שאול ואת דוד.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="3" t="inlineStr"/>
@@ -4749,167 +4557,163 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>המהרי״ק (רבי יוסף קולון)</t>
+          <t>בת שבע</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>המלכים</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1420–1480 בקירוב</t>
+          <t>תקופת דוד ושלמה</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>צרפת ואיטליה</t>
+          <t>ירושלים; ממלכת ישראל</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>הלכה ומנהג</t>
+          <t>מלכות, הנהגה וחכמה</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>שו״ת מהרי״ק</t>
+          <t>דוד המלך, שלמה המלך, נתן הנביא, אם המלך, אשת חיל, משלי, משפט צדק, נשים</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>מגדולי הפוסקים שהעניקו למנהג הקהילתי מעמד מרכזי בפסיקה.</t>
+          <t>אשת דוד ואמו של שלמה, שבספר מלכים מתגלה כדמות מדינית נחושה: היא פועלת עם נתן הנביא להבטחת המלכת שלמה, ולאחר מכן זוכה למעמד ״אם המלך״. במסורת חז״ל היא מזוהה עם אמו של למואל המוכיחה את בנה על אחריות המלכות.</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>המנהג הוא חלק מהתורה החיה של עם ישראל.</t>
+          <t>הכתר אינו זכות בלבד אלא אחריות מוסרית; בת שבע מייצגת את הכוח להציב גבולות למלך ולדרוש ממנו צדק, משמעת עצמית ודאגה לחלשים.</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>הרמ״א, תרומת הדשן</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5V8efc6gWfwrgHLR6E1AQZ</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+          <t>דוד המלך, שלמה המלך, נתן הנביא, אדוניהו בן חגית</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>572</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
+          <t>ישעיהו הנביא</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>המלכים</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1858–1936</t>
+          <t>765–695 לפנה״ס</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>רוגצ'וב/דווינסק</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
-        </is>
-      </c>
+          <t>נבואה</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
+          <t>מגדולי נביאי הכתב. נבואות החורבן והנחמה שלו — 'נחמו נחמו עמי' — מלוות את ישראל בכל הדורות.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>הרב יעקב ששפורטש</t>
+          <t>צרויה</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>המלכים</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1610–1698</t>
+          <t>תקופת דוד המלך</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>צפון אפריקה, אירופה המערבית (אמסטרדם, לונדון, המבורג, ליבורנו)</t>
+          <t>בית לחם; ממלכת דוד</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>פולמוס/הנהגה</t>
+          <t>בית דוד, משפחה ומלוכה</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/09JfLsbxRNjLhC969SxOPd?si=zTKhNkZ7T8qiI1akCdsAvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>דוד המלך, יואב, אבישי, עשהאל, בני צרויה, הנהגה, גבורה, מלכות, נשים</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>אחותו של דוד המלך ובתו של ישי, ששמה נשמר במקרא בעיקר דרך שלושת בניה - יואב, אבישי ועשהאל. הייחוס החוזר של הבנים דווקא לאמם הפך את צרויה לסמל משפחתי המזוהה עם כוח, גבורה ונאמנות לבית דוד.</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>המתח בין דוד לבין בני צרויה ממחיש את הצורך והסכנה שבחיבור בין חסד לכוח: המלכות זקוקה לעוצמה צבאית, אך גם לריסון מוסרי ולהנהגה רוחנית.</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>דוד המלך, ישי, יואב בן צרויה, אבישי בן צרויה, עשהאל בן צרויה</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="3" t="inlineStr"/>
@@ -4917,59 +4721,43 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>595</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>רבי דוד פארדו</t>
+          <t>שלמה המלך</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>המלכים</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1719–1792</t>
+          <t>1010–931 לפנה״ס</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ונציה, הבלקן, ירושלים</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>תלמוד, משנה ותוספתא</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>חסדי דוד, תוספתא</t>
-        </is>
-      </c>
+          <t>חכמה, מלכות</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>מגדולי פרשני התוספתא, שהחזיר את לימודה למרכז בית המדרש באמצעות פירושו 'חסדי דוד'.</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>דיוק טקסטואלי לצד מחויבות עמוקה למסורת.</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>פרופ' שאול ליברמן</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/0gNG3pg6tSS0rP12co2dsU</t>
-        </is>
-      </c>
+          <t>החכם מכל אדם ובונה בית המקדש הראשון. חיבר את משלי, קהלת ושיר השירים.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="3" t="inlineStr"/>
@@ -4977,119 +4765,99 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>רבי משה דוד ואלי (הרמ״ד ואלי)</t>
+          <t>בן סירא</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>בית שני</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1697–1777</t>
+          <t>סביב 190 לפנה״ס</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>פדובה, איטליה</t>
+          <t>ירושלים; מצרים (תרגום/תוספות הנכד)</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>קבלה/פרשנות מקרא</t>
+          <t>חכמה ומוסר</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>פשוטו מכוון אל סודו, רמח״ל, כתבים גנוזים</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>רופא מוסמך וחבר קרוב של הרמח״ל. פיתח שיטת פרשנות: הפשט עצמו רומז לסוד בכל שינוי דקדוקי/לשוני.</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>מיפוי לשון המקרא למבנה הספירות; דחיית חכמות חיצוניות כתחליף; מפעל פירושים עצום שנחשף רק בדורות האחרונים.</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>הרמח״ל; חוג פדובה; הדפסת כתבים בדורנו</t>
-        </is>
-      </c>
+          <t>ספרות בית שני, מוסר ודרך ארץ, גבולות קאנון, השפעה חז"לית</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6Sc3CiYpTfV68Ke8SueReD</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/3u5udRWI84FVJ3OsOBBbPF?si=ek7V_WzPS7OadSPOZSU-VA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>רבי רפאל עמנואל חי ריקי</t>
+          <t>יהודית</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>בית שני</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>1687–1743</t>
+          <t>170–100 לפנה״ס</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>איטליה וירושלים</t>
+          <t>ארץ ישראל</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>קבלה ופרשנות</t>
+          <t>גבורה</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>משנת חסידים, יושר לבב, קבלת האר"י</t>
+          <t>נשים</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>מקובל, פייטן ופרשן משנה, מן הדמויות הבולטות בקבלת איטליה.</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>שילוב קבלת האר"י עם הוראה שיטתית וספרות הלכתית-קבלית.</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>האר"י; הרש"ש; האור החיים</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/3Foy6VcyWU352VPpw1z1cp?si=jaoMkKODSduL9jAf58zdww</t>
-        </is>
-      </c>
+          <t>גיבורת הספר החיצוני הקרוי על שמה, שמסרה נפשה להצלת עמה. דמותה נקשרה במסורת לנס חנוכה.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="3" t="inlineStr"/>
@@ -5097,57 +4865,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>רבי שבתאי הכהן (הש"ך)</t>
+          <t>שמעון כיפא – מרטיר נוצרי או צדיק נסתר ששלחו חכמי ישראל?</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>בית שני</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1622–1663</t>
+          <t>המאות הראשונות לספירה</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>פולין</t>
+          <t>ארץ ישראל; רומא; ראשית הנצרות</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>הלכה, חושן משפט, ביקורת מקורות</t>
+          <t>מסורת ופולמוס</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>שפתי כהן, יורה דעה, תקפו כהן, מחלוקת</t>
+          <t>יהדות–נצרות, מסורות אזוטריות, זהות, פולמוס, ליטורגיה, ט' בטבת</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>פוסק גאון שדרש פתיחה מחודשת של ההלכה, עימת את המקובל, חידש בעיון, וספריו הפכו יסוד ללימוד ולפסיקה עד היום.</t>
+          <t>הפרק מציג את הפער בין המסורת הנוצרית על פטרוס לבין מסורות יהודיות המציירות את שמעון כיפא כשליח נסתר שנועד ליצור הפרדה בין יהדות לנצרות כדי למנוע שפיכות דמים והתבוללות. לפי הסיפור, הוא עיצב מנהגים ותיאולוגיה שמרחיקים מן היהדות ובמקביל למד תורה בסתר. מוצגים גם ייחוסים ליטורגיים ומסורות סביב צום ט' בטבת.</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>הלכה כעיון פתוח ולא כקובץ סגור; עקרונות חדשניים בדיני ממונות וספקות.</t>
+          <t>מסורות כמנגנון זהות: סיפור 'שליח נסתר' שמפרש פילוג דתי כצעד הגנתי של הקהילה.</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>הט"ז, מגיני שלמה, מגלה עמוקות</t>
+          <t>ספר חסידים; אוצר המדרשים; תולדות ישו</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0zeTxQVV4ZhQFYYST2sO12</t>
+          <t>https://open.spotify.com/episode/4tu43oeL4qVdXGKzX2025J?si=G3-56Xu3TxKoDiSCHX9gEA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr"/>
@@ -5157,59 +4925,43 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>578</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>האדר״ת (רבי אליהו דוד רבינוביץ'-תאומים)</t>
+          <t>רבי טרפון</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>תנאים</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>1843–1905</t>
+          <t>46–117</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ליטא וירושלים</t>
+          <t>יבנה</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>הלכה, מוסר והנהגה ציבורית</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>סדר אליהו, נפש דוד</t>
-        </is>
-      </c>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>רבה של פוניבז', מיר וירושלים, ומחותנו של הראי״ה קוק.</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>גדלות בתורה מחייבת אחריות ציבורית ודוגמה אישית.</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>הראי״ה קוק, רבי שמואל סלנט</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7zHC1A3dQMNYpbYXahsYQd</t>
-        </is>
-      </c>
+          <t>מגדולי תנאי יבנה, כהן שזכה לשרת במקדש. בר פלוגתא ואוהבו של רבי עקיבא; 'היום קצר והמלאכה מרובה'.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="3" t="inlineStr"/>
@@ -5217,59 +4969,55 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>הלל צייטלין (1871–1942) – פילוסוף יהודי בין ניטשה לחסידות, שנרצח בשואה</t>
+          <t>ילתא</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אמוראים</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1871–1942</t>
+          <t>המאה ה־3–4 לספירה</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>פולין; מזרח אירופה</t>
+          <t>בבל</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>מחשבה</t>
+          <t>הלכה, הנהגה ומעמד נשים</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>מודרנה יהודית; אקזיסטנציאליזם; חסידות; משבר אמונה</t>
+          <t>רב נחמן, עולא, רבה בר בר חנה, היתר ואיסור, כוס של ברכה, 400 חביות יין, נשים</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>הלל צייטלין: פילוסוף יהודי בין ניטשה לחסידות, מבקר תרבות שחוזר לעומק רוחני; נרצח בשואה.</t>
+          <t>בת למשפחת ראש הגולה ורעייתו של רב נחמן, מן הדמויות הנשיות הבולטות בתלמוד. היא מביעה רעיונות הלכתיים מקוריים, עומדת על דעתה מול חכמים, פונה לבירור הלכתי נוסף בעת הצורך ואף מייעצת לבעלה בענייני הנהגה.</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>החיפוש עצמו הוא עבודת ה': להפוך ספק ומודרניות למנוע של תשובה וחידוש רוחני.</t>
+          <t>עולם ההלכה כולל לא רק איסורים אלא גם מרחב של היתר, עונג וקדושה; ילתא מגלמת עצמאות אינטלקטואלית, מעמד ציבורי ונוכחות נשית פעילה בעולם האמוראי.</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>ניטשה; בובר; ברנר; חסידות חב"ד; ספרות יהודית מודרנית</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>https://spotifycreators-web.app.link/e/VKh6sMX4yQb</t>
-        </is>
-      </c>
+          <t>רב נחמן, עולא, רבה בר בר חנה, רב יצחק בריה דרב יהודה</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="3" t="inlineStr"/>
@@ -5277,59 +5025,43 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>576</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודא ליאון אשכנזי (מניטו)</t>
+          <t>רב הונא</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אמוראים</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1922–1996</t>
+          <t>216–296</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>אלג'יריה → צרפת → ישראל</t>
+          <t>סורא</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל, קבלה, זהות לאומית</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>אסכולת פריז, לוינס, שושני, עברי/יהודי, צמצום כמוסר, תחייה</t>
-        </is>
-      </c>
+          <t>הלכה</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>הוגה וקבליסט שחיבר בין מסורת צפון אפריקה, שיח אינטלקטואלי צרפתי ותורת ארץ ישראל; ניסח תורת זהויות והעמיד שפה חדשה של תחייה.</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>זהות 'עברי' כשלב תודעתי-לאומי שמאחד קודש וחול, משפחה ועם, מוסר והיסטוריה.</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>עמנואל לוינס; אנדרה נהר; יעקב גורדין; מר שושני; הרב צבי יהודה קוק; הרב אורי שרקי</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/6vCbxdldNDpdncGxSjvAyD</t>
-        </is>
-      </c>
+          <t>עמוד התווך של הדור השני לאמוראי בבל וראש ישיבת סורא ארבעים שנה. הלכה כמותו בממונות ברוב מחלוקותיו.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="3" t="inlineStr"/>
@@ -5337,57 +5069,57 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף משאש</t>
+          <t>רבי חייא הגדול</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>אמוראים</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1892–1974</t>
+          <t>המאה ה־2–3 לספירה</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>מקנס (מרוקו) → חיפה</t>
+          <t>בבל, טבריה</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>הלכה, היסטוריה, הנהגה</t>
+          <t>תורה שבעל פה, חינוך</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>פסיקה ריאלית, רציונליזם, אחדות ישראל, יהדות המגרב, אתחלתא דגאולה</t>
+          <t>שכחת התורה, תוספתא, מסירות</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>איש אשכולות שראה במציאות כלי להבנת ההלכה, פסק באומץ מתוך חמלה ורוח הזמן, וחיזק את אחדות ישראל בין גולה לתקומה.</t>
+          <t>הציל את התורה משכחה בפעולה מעשית כוללת. שילב עמל גשמי ורוחני כדי להעביר מסורת.</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>הלכה נצחית שפוגשת זמן: ריאליזם הלכתי כמפתח לשמירת המסורת בחברה משתנה.</t>
+          <t>תורה נשמרת במעשה. אחריות אישית להעברה דורית.</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>קהילות המגרב; רבנות חיפה; שיח ציוני-דתי</t>
+          <t>רבי יהודה הנשיא, רבי אושעיה</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2bY5WI2sxqsa1csNcbHXoG</t>
+          <t>https://open.spotify.com/episode/4MI4LUL2FI4WeVtEdPZS5F</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr"/>
@@ -5397,59 +5129,43 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>הרב מאיר זייני</t>
+          <t>רבי אבון הגדול</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>גאונים</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1921–2012</t>
+          <t>900–960</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>אלג׳יריה → פריז → ירושלים</t>
+          <t>מגנצא</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות קהילה/ציונות/מסורת צפון אפריקה</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>יהדות אלג׳יריה, עוז חיים, תורה וגבורה, עלייה בגיל 85</t>
-        </is>
-      </c>
+          <t>תורה, פיוט</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>רב קהילות באלג׳יריה, רב צבאי, ובצרפת החיה בית כנסת והנחיל זהות ליוורנואית-ציונית. עלה לישראל בגיל 85.</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>מנהיגות 'גדול גיבור' המחברת תורה ומעשה; גאולה מתוך מפגש תפילה-עשייה ושימור ניגון מסורת.</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>מגורשי ספרד; הרב שרקי (תיאור תלמידים)</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/0hEDzOsuXWV4gBqUTv3KqW</t>
-        </is>
-      </c>
+          <t>מאבות הקהילה הרבנית הקדומה ברינוס. ממניחי היסוד לתרבות התורה של אשכנז הקדומה, דורות לפני רבנו גרשום.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="3" t="inlineStr"/>
@@ -5457,55 +5173,59 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>הרב רפאל יהודה מנחם לוי – רבי יהודה מרגוזה</t>
+          <t>אברהם בר חייא</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1783–1879</t>
+          <t>המאה ה-12</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>סרייבו; ירושלים; קושטא; יפו</t>
+          <t>ברצלונה</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>רבנות, התיישבות וחקלאות</t>
+          <t>מדע, פילוסופיה</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>יפו, הפרדס היהודי הראשון, מקוה ישראל, פתח תקווה, ועד העיר, עבודת האדמה</t>
+          <t>בר חייא, פילוסופיה, מדע יהודי, מתמטיקה</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>רבה הראשון של יפו החדשה, שאיחד קהילות, קלט עולים והקים מוסדות ציבור. נטע ב־1842 את הפרדס היהודי הראשון בעת החדשה, תמך במקוה ישראל ועודד עבודה, חקלאות והתיישבות בארץ.</t>
+          <t>היהודי הראשון שכתב מדע בעברית והשפיע על תרגום חכמת המזרח לאירופה.</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>תורה ועבודת האדמה אינן סותרות זו את זו; בניין הארץ, עצמאות כלכלית ויוזמה ציבורית הם חלק מתהליך הגאולה.</t>
+          <t>שילוב בין תורה, מדע ופילוסופיה; תרגום חכמה כללית לעברית.</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>הרב יהודה ביבאס, משה מונטיפיורי, קרל נטר, מייסדי פתח תקווה</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>פיבונאצ'י, חכמי ספרד</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3FAGqYdzyMQbyPbon3KYoC</t>
+        </is>
+      </c>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="3" t="inlineStr"/>
@@ -5513,105 +5233,121 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>חכם ציון חביב ברכה</t>
+          <t>הריצב״א</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
+          <t>המאה ה־12–13</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ירושלים (נחלאות)</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
+          <t>תלמוד, תוספות וסוד</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
+          <t>ר״י הבחור, רבנו תם, ר״י הזקן, מעשה מרכבה</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>מן הדמויות המרכזיות בדור שלאחר רבנו תם בעולם התוספות. שילב עצמאות למדנית ושימוש רחב בירושלמי עם מוניטין של איש חזיונות וסודות הבריאה.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>חיבור נדיר בין חריפות דיאלקטית תלמודית לבין עומק מיסטי, כגשר בין אשכנז, ספרד ועולמות הסוד.</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>רבנו תם; ר״י הזקן; הרמב״ם; רבי יהודה בר יקר; רבי יחיאל מפאריס</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/0fIS5dc7OCTq1C6amM82LT?si=tqcgKwdFQPuRVDKuMbTmkQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
       <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>טובה סנהדראי-גולדרייך</t>
+          <t>מחזור ויטרי</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1906–1993</t>
+          <t>1105 בקירוב</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>גליציה; ארץ ישראל</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות ציונית־דתית</t>
+          <t>ליטורגיה והלכה</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, המפד"ל, כנסת, שירות לאומי, נשים</t>
+          <t>מחזור ויטרי, רבנו שמחה מוויטרי</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>חברת הכנסת הדתית הראשונה, ממנהיגות תנועת "אמונה" ומקימת "רשימת הפועלת והאישה הדתית" ב־1949. כיהנה ארבע קדנציות בכנסת מטעם המפד"ל וקידמה חקיקה חברתית ורווחתית.</t>
+          <t>אנציקלופדיה הלכתית וליטורגית מבית מדרשו של רש״י, המשמרת את נוסח צרפת ומסורות אשכנז הקדומות.</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>שילוב מחויבות הלכתית עם אחריות ציבורית ופרלמנטרית — הרחבת השתתפות נשים דתיות בבניין המדינה מבלי לוותר על עקרונות.</t>
+          <t>חיבור בין תפילה, הלכה, אגדה וחיי קהילה.</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, המפד"ל</t>
+          <t>רש״י, בעלי התוספות</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0RuE8l4DbgcRxBQWjGBUv3?si=rW9fZeAOTueEFDMOKUR5mQ</t>
+          <t>https://open.spotify.com/episode/6xiWssuJyV4GypDbnlCpl0</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -5625,115 +5361,123 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>רבי מאיר שמחה הכהן מדווינסק</t>
+          <t>ספר הכוזרי</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>1843–1926</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>דווינסק (לטביה/ליטא)</t>
+          <t>ספרד / אל־אנדלוס</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>הלכה/פרשנות תורה/מחשבה ציונית</t>
+          <t>הגות ואמונה</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>אור שמח, משך חכמה, גלות וזהות, שבועות</t>
+          <t>רבי יהודה הלוי, אמונה, סיני, ארץ ישראל</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>מחבר 'אור שמח' ו'משך חכמה'. גשר בין שכל לאמונה ובין גלות לתחייה; ניתוח חריף של היסטוריה יהודית וקדושה.</t>
+          <t>אחד מחיבורי היסוד של המחשבה היהודית, שנכתב בידי רבי יהודה הלוי בערבית יהודית. מציג הגנה מקורית על היהדות דרך ההיסטוריה, ההתגלות הלאומית והקשר בין עם, מצוות וארץ.</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>הגלות כמנגנון זהות; קדושה אינה בחומר אלא ברצון ה׳; ציונות וגאולה בדרך הטבע (בלפור/סן-רמו).</t>
+          <t>ביסוס האמונה היהודית על זיכרון היסטורי לאומי והתגלות ציבורית, ולא רק על הוכחה פילוסופית מופשטת.</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ם; הרב קוק; עידן התחייה</t>
+          <t>רבי יהודה הלוי; הרמב"ם; הרב קוק; ביאליק</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5M242GRqncgReaYVplhjBU</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr"/>
+          <t>https://open.spotify.com/episode/0E55prQ6VaFsIXKSiCpDe3?si=XrQKU-Z0TgKEvgDDjH-MFQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
       <c r="M79" s="3" t="inlineStr"/>
       <c r="N79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>רבי שמשון רפאל הירש</t>
+          <t>רבי יוסף חיון (רי״ח)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1808–1888</t>
+          <t>מאה 15</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>המבורג; פרנקפורט, גרמניה</t>
+          <t>ליסבון, פורטוגל</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>הגות, חינוך ויחסי תורה ומודרנה</t>
+          <t>פרשנות מקרא/תיאולוגיה</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>תורה עם דרך ארץ, אורתודוקסיה, השכלה כללית, חינוך, איגרות צפון, חורב, פולמוס הפרישה</t>
+          <t>תורה מן השמים, דיוק לשוני, ספר דברים, פרשנות סמנטית</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>רב, פרשן והוגה יהודי מגרמניה שניסח את שיטת ״תורה עם דרך ארץ״. הנהיג בפרנקפורט מערכת חינוך ששילבה לימודי קודש עם לימודים כלליים, ונאבק ברפורמה תוך הדגשת מחויבות מלאה להלכה גם בתוך התרבות המודרנית.</t>
+          <t>מנהיג קהילת ליסבון ומורו של האברבנאל. פיתח פתרון לשאלת 'דברים מפי עצמו' ועיקרון שאין כפל עניין בתנ״ך.</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>אפשר להיות מעורב במדע, בתרבות ובחברה המודרנית מבלי שהתורה תאבד את מרכזיותה; הפתיחות לעולם דורשת זהות תורנית ברורה וגבולות הלכתיים מוצקים.</t>
+          <t>משה ניסח נאומים, אך ה׳ הכתיב לו מילה במילה בעת כתיבת התורה; כל מילה במקרא ייחודית ואין 'נרדפות' סתמית.</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>רבי יצחק דב במברגר, קהילת פרנקפורט, התנועה הרפורמית, האורתודוקסיה הגרמנית</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
+          <t>דון יצחק אברבנאל; קנפנטון; המלבי״ם (הקדמה רעיונית)</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
+        </is>
+      </c>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="inlineStr"/>
@@ -5741,57 +5485,49 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>רס״ן רועי קליין</t>
+          <t>רבי יצחק קנפנטון</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>1975–2006</t>
+          <t>1360–1463</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>קסטיליה; ספרד</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות וציונות דתית</t>
+          <t>למדנות תלמודית</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>מלחמת לבנון השנייה</t>
+          <t>דרכי התלמוד, גאון מקסטיליה</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>קצין צה״ל שעוטר בעיטור העוז לאחר שנפל תוך הצלת חייליו בקרב בבינת ג'בייל.</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>גבורה צומחת מחיים של אחריות, אמונה ומסירות.</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>צה״ל, הציונות הדתית</t>
-        </is>
-      </c>
+          <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
+          <t>https://open.spotify.com/episode/2xytN0uGuTq03wNYWvusDO?si=GjQi6caQRZGdjDrWc8cX7w</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
@@ -5801,59 +5537,43 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>רס״ן רועי קליין הי״ד</t>
+          <t>רבי משה מקוצי (הסמ"ג)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1975–2006</t>
+          <t>1200–1260</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>צרפת</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>מוסר, מנהיגות</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>גבורה, צה״ל, אמונה</t>
-        </is>
-      </c>
+          <t>הלכה, דרשנות</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>קצין צה"ל שמסר נפשו להצלת חייליו והפך לסמל של גבורה הנובעת מחיים של ערכים.</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>גבורה כרצף חיים – לא רגע חד־פעמי</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>צה״ל; חינוך דתי</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
-        </is>
-      </c>
+          <t>מבעלי התוספות ומחבר 'ספר מצוות גדול' — הקודקס ההלכתי הגדול של יהדות צרפת. סבב בקהילות ספרד ואשכנז כמוכיח ומעורר.</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="inlineStr"/>
@@ -5861,57 +5581,57 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ר׳ אריה־לייב גינצבורג – “שאגת אריה”</t>
+          <t>רבנו חננאל בן חושיאל</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>בערך 1695–1785</t>
+          <t>מאה 11</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>מזרח אירופה / מץ (צרפת)</t>
+          <t>קירואן (צפון אפריקה)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>פסיקה ועיון תלמודי</t>
+          <t>פירוש תלמוד/פסיקה</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>אורח חיים, חריפות, פשט, עצמאות, ביקורת מקרא (תורת הבחינות)</t>
+          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>גאון תלמודי ופוסק עצמאי שחי בעוני ונדודים, התנגש בממסד ולא פחד לחלוק. ספרו 'שאגת אריה' נעשה אבן יסוד בפסיקת אורח חיים וחיבוריו נלמדים בעומק.</t>
+          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>אמת הלכתית ללא פשרות: דיוק במקורות הראשונים ועצמאות פסיקה – גם במחיר של בדידות ציבורית.</t>
+          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>השפעה מאוחרת על הרב מרדכי ברויאר (תורת הבחינות); הערכה בחב״ד</t>
+          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4tSyrs2SrcNd1WsVBoHZuh?si=fQD3_QT6TqqaEDMyoYR9bw</t>
+          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
@@ -5921,65 +5641,1377 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>שלמה מונק</t>
+          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>ראשונים</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1803–1867</t>
+          <t>1100–1171</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>גרמניה וצרפת</t>
+          <t>צרפת (אשכנז)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>מדעי היהדות ופילוסופיה</t>
+          <t>תלמוד ושיטה למדנית</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>מורה נבוכים, אבן גבירול</t>
+          <t>תוספות, שתי שקיעות, תפילין, תקנות, מסעות הצלב</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>מזרחן וחוקר יהדות שהחזיר את אבן גבירול להיסטוריה של הפילוסופיה וערך את מורה נבוכים מן המקור הערבי.</t>
+          <t>נכדו של רש״י שבנה את שיטת בעלי התוספות: לא מוותרים על סתירות – מחברים סוגיות וגשרים. במקביל היה מנהיג קהילה בתקופת מסעי הצלב ותקן תקנות חברתיות.</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>שילוב בין מחקר מדעי לנאמנות למסורת.</t>
+          <t>נאמנות קשוחה לנוסח הגמרא (“בספרים אל ימחק”) שמכריחה עומק, דיוק וחילוקים – ומייצרת לימוד יוצר.</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם, אבן גבירול</t>
+          <t>בעלי התוספות; רש״י; מנהג זמן רבנו תם</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0fBwsgpkyNbo7MJnjhEgeH</t>
+          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ?si=o5kksAmaQNiRkBHxN8CVpQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="3" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>רש"י (רבי שלמה יצחקי)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>1040–1105</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>טרואה</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא, פרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>גדול פרשני ישראל. פירושו לתורה ולתלמוד — בהיר, תמציתי וצמוד לפשט — פתח את שערי הלימוד לכל הדורות, ובלעדיו אין דף גמרא נלמד.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>פשוטו של מקרא — פירוש שכל תלמיד יכול להיכנס בו</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>המהרי״ק (רבי יוסף קולון)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>1420–1480 בקירוב</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>צרפת ואיטליה</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>הלכה ומנהג</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>שו״ת מהרי״ק</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים שהעניקו למנהג הקהילתי מעמד מרכזי בפסיקה.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>המנהג הוא חלק מהתורה החיה של עם ישראל.</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>הרמ״א, תרומת הדשן</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5V8efc6gWfwrgHLR6E1AQZ</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>1858–1936</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>רוגצ'וב/דווינסק</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>הרב יעקב ששפורטש</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>1610–1698</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>צפון אפריקה, אירופה המערבית (אמסטרדם, לונדון, המבורג, ליבורנו)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>פולמוס/הנהגה</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/09JfLsbxRNjLhC969SxOPd?si=zTKhNkZ7T8qiI1akCdsAvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>יוסל מרוסהיים</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>1476–1554</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>שתדלנות, הנהגה</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>השתדלן הגדול של יהדות אשכנז מול הקיסר קרל החמישי. 'ספר המקנה' שלו — עדות אישית להנהגה בדור של גזרות ורפורמציה.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>רבי דוד פארדו</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>1719–1792</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ונציה, הבלקן, ירושלים</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>תלמוד, משנה ותוספתא</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>חסדי דוד, תוספתא</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי פרשני התוספתא, שהחזיר את לימודה למרכז בית המדרש באמצעות פירושו 'חסדי דוד'.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>דיוק טקסטואלי לצד מחויבות עמוקה למסורת.</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>פרופ' שאול ליברמן</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0gNG3pg6tSS0rP12co2dsU</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>רבי משה דוד ואלי (הרמ״ד ואלי)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>1697–1777</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>פדובה, איטליה</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>קבלה/פרשנות מקרא</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>פשוטו מכוון אל סודו, רמח״ל, כתבים גנוזים</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>רופא מוסמך וחבר קרוב של הרמח״ל. פיתח שיטת פרשנות: הפשט עצמו רומז לסוד בכל שינוי דקדוקי/לשוני.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>מיפוי לשון המקרא למבנה הספירות; דחיית חכמות חיצוניות כתחליף; מפעל פירושים עצום שנחשף רק בדורות האחרונים.</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>הרמח״ל; חוג פדובה; הדפסת כתבים בדורנו</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/6Sc3CiYpTfV68Ke8SueReD</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>רבי נתן מברסלב (מנמירוב)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>1780–1844</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>אוקראינה</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>חסידות</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>תלמידו הגדול וסופרו של רבי נחמן מברסלב. העלה על הכתב את תורותיו, ייסד את מסורת ההתבודדות והתפילה — 'ליקוטי תפילות'.</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>רבי רפאל עמנואל חי ריקי</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>1687–1743</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>איטליה וירושלים</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>קבלה ופרשנות</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>משנת חסידים, יושר לבב, קבלת האר"י</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>מקובל, פייטן ופרשן משנה, מן הדמויות הבולטות בקבלת איטליה.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>שילוב קבלת האר"י עם הוראה שיטתית וספרות הלכתית-קבלית.</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>האר"י; הרש"ש; האור החיים</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3Foy6VcyWU352VPpw1z1cp?si=jaoMkKODSduL9jAf58zdww</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>רבי שבתאי הכהן (הש"ך)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>1622–1663</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>פולין</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>הלכה, חושן משפט, ביקורת מקורות</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>שפתי כהן, יורה דעה, תקפו כהן, מחלוקת</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>פוסק גאון שדרש פתיחה מחודשת של ההלכה, עימת את המקובל, חידש בעיון, וספריו הפכו יסוד ללימוד ולפסיקה עד היום.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>הלכה כעיון פתוח ולא כקובץ סגור; עקרונות חדשניים בדיני ממונות וספקות.</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>הט"ז, מגיני שלמה, מגלה עמוקות</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0zeTxQVV4ZhQFYYST2sO12</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>האדר״ת (רבי אליהו דוד רבינוביץ'-תאומים)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>1843–1905</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>ליטא וירושלים</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>הלכה, מוסר והנהגה ציבורית</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>סדר אליהו, נפש דוד</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>רבה של פוניבז', מיר וירושלים, ומחותנו של הראי״ה קוק.</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>גדלות בתורה מחייבת אחריות ציבורית ודוגמה אישית.</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>הראי״ה קוק, רבי שמואל סלנט</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/7zHC1A3dQMNYpbYXahsYQd</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>הלל צייטלין (1871–1942) – פילוסוף יהודי בין ניטשה לחסידות, שנרצח בשואה</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>1871–1942</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>פולין; מזרח אירופה</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>מחשבה</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>מודרנה יהודית; אקזיסטנציאליזם; חסידות; משבר אמונה</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>הלל צייטלין: פילוסוף יהודי בין ניטשה לחסידות, מבקר תרבות שחוזר לעומק רוחני; נרצח בשואה.</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>החיפוש עצמו הוא עבודת ה': להפוך ספק ומודרניות למנוע של תשובה וחידוש רוחני.</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>ניטשה; בובר; ברנר; חסידות חב"ד; ספרות יהודית מודרנית</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>https://spotifycreators-web.app.link/e/VKh6sMX4yQb</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="3" t="inlineStr"/>
+      <c r="N96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>הרב יהודא ליאון אשכנזי (מניטו)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>1922–1996</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>אלג'יריה → צרפת → ישראל</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>מחשבת ישראל, קבלה, זהות לאומית</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>אסכולת פריז, לוינס, שושני, עברי/יהודי, צמצום כמוסר, תחייה</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>הוגה וקבליסט שחיבר בין מסורת צפון אפריקה, שיח אינטלקטואלי צרפתי ותורת ארץ ישראל; ניסח תורת זהויות והעמיד שפה חדשה של תחייה.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>זהות 'עברי' כשלב תודעתי-לאומי שמאחד קודש וחול, משפחה ועם, מוסר והיסטוריה.</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>עמנואל לוינס; אנדרה נהר; יעקב גורדין; מר שושני; הרב צבי יהודה קוק; הרב אורי שרקי</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/6vCbxdldNDpdncGxSjvAyD</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
+      <c r="N97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>הרב יוסף משאש</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>1892–1974</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>מקנס (מרוקו) → חיפה</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>הלכה, היסטוריה, הנהגה</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>פסיקה ריאלית, רציונליזם, אחדות ישראל, יהדות המגרב, אתחלתא דגאולה</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>איש אשכולות שראה במציאות כלי להבנת ההלכה, פסק באומץ מתוך חמלה ורוח הזמן, וחיזק את אחדות ישראל בין גולה לתקומה.</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>הלכה נצחית שפוגשת זמן: ריאליזם הלכתי כמפתח לשמירת המסורת בחברה משתנה.</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>קהילות המגרב; רבנות חיפה; שיח ציוני-דתי</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/2bY5WI2sxqsa1csNcbHXoG</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="3" t="inlineStr"/>
+      <c r="N98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>הרב מאיר זייני</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>1921–2012</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>אלג׳יריה → פריז → ירושלים</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>מנהיגות קהילה/ציונות/מסורת צפון אפריקה</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>יהדות אלג׳יריה, עוז חיים, תורה וגבורה, עלייה בגיל 85</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>רב קהילות באלג׳יריה, רב צבאי, ובצרפת החיה בית כנסת והנחיל זהות ליוורנואית-ציונית. עלה לישראל בגיל 85.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות 'גדול גיבור' המחברת תורה ומעשה; גאולה מתוך מפגש תפילה-עשייה ושימור ניגון מסורת.</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>מגורשי ספרד; הרב שרקי (תיאור תלמידים)</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0hEDzOsuXWV4gBqUTv3KqW</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>הרב רפאל יהודה מנחם לוי – רבי יהודה מרגוזה</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>1783–1879</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>סרייבו; ירושלים; קושטא; יפו</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>רבנות, התיישבות וחקלאות</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>יפו, הפרדס היהודי הראשון, מקוה ישראל, פתח תקווה, ועד העיר, עבודת האדמה</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>רבה הראשון של יפו החדשה, שאיחד קהילות, קלט עולים והקים מוסדות ציבור. נטע ב־1842 את הפרדס היהודי הראשון בעת החדשה, תמך במקוה ישראל ועודד עבודה, חקלאות והתיישבות בארץ.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>תורה ועבודת האדמה אינן סותרות זו את זו; בניין הארץ, עצמאות כלכלית ויוזמה ציבורית הם חלק מתהליך הגאולה.</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>הרב יהודה ביבאס, משה מונטיפיורי, קרל נטר, מייסדי פתח תקווה</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="3" t="inlineStr"/>
+      <c r="N100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>חכם ציון חביב ברכה</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>ירושלים (נחלאות)</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>קבלה</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr"/>
+      <c r="N101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>טובה סנהדראי-גולדרייך</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>1906–1993</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>גליציה; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>מנהיגות ציונית־דתית</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>תנועת אמונה, המפד"ל, כנסת, שירות לאומי, נשים</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>חברת הכנסת הדתית הראשונה, ממנהיגות תנועת "אמונה" ומקימת "רשימת הפועלת והאישה הדתית" ב־1949. כיהנה ארבע קדנציות בכנסת מטעם המפד"ל וקידמה חקיקה חברתית ורווחתית.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>שילוב מחויבות הלכתית עם אחריות ציבורית ופרלמנטרית — הרחבת השתתפות נשים דתיות בבניין המדינה מבלי לוותר על עקרונות.</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>תנועת אמונה, המפד"ל</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0RuE8l4DbgcRxBQWjGBUv3?si=rW9fZeAOTueEFDMOKUR5mQ</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>נפסל — מסמך של אדם אחר</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr"/>
+      <c r="N102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>רבי מאיר שמחה הכהן מדווינסק</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>1843–1926</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>דווינסק (לטביה/ליטא)</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>הלכה/פרשנות תורה/מחשבה ציונית</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>אור שמח, משך חכמה, גלות וזהות, שבועות</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>מחבר 'אור שמח' ו'משך חכמה'. גשר בין שכל לאמונה ובין גלות לתחייה; ניתוח חריף של היסטוריה יהודית וקדושה.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>הגלות כמנגנון זהות; קדושה אינה בחומר אלא ברצון ה׳; ציונות וגאולה בדרך הטבע (בלפור/סן-רמו).</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>הרמב״ם; הרב קוק; עידן התחייה</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5M242GRqncgReaYVplhjBU</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr"/>
+      <c r="N103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>רבי שמשון רפאל הירש</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>1808–1888</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>המבורג; פרנקפורט, גרמניה</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>הגות, חינוך ויחסי תורה ומודרנה</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>תורה עם דרך ארץ, אורתודוקסיה, השכלה כללית, חינוך, איגרות צפון, חורב, פולמוס הפרישה</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>רב, פרשן והוגה יהודי מגרמניה שניסח את שיטת ״תורה עם דרך ארץ״. הנהיג בפרנקפורט מערכת חינוך ששילבה לימודי קודש עם לימודים כלליים, ונאבק ברפורמה תוך הדגשת מחויבות מלאה להלכה גם בתוך התרבות המודרנית.</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>אפשר להיות מעורב במדע, בתרבות ובחברה המודרנית מבלי שהתורה תאבד את מרכזיותה; הפתיחות לעולם דורשת זהות תורנית ברורה וגבולות הלכתיים מוצקים.</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>רבי יצחק דב במברגר, קהילת פרנקפורט, התנועה הרפורמית, האורתודוקסיה הגרמנית</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="3" t="inlineStr"/>
+      <c r="N104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>רס״ן רועי קליין הי״ד</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>1975–2006</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>ישראל</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>מוסר, מנהיגות</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>גבורה, צה״ל, אמונה</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>קצין צה"ל שמסר נפשו להצלת חייליו והפך לסמל של גבורה הנובעת מחיים של ערכים.</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>גבורה כרצף חיים – לא רגע חד־פעמי</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>צה״ל; חינוך דתי</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="3" t="inlineStr"/>
+      <c r="N105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ר׳ אריה־לייב גינצבורג – “שאגת אריה”</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>בערך 1695–1785</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>מזרח אירופה / מץ (צרפת)</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>פסיקה ועיון תלמודי</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>אורח חיים, חריפות, פשט, עצמאות, ביקורת מקרא (תורת הבחינות)</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>גאון תלמודי ופוסק עצמאי שחי בעוני ונדודים, התנגש בממסד ולא פחד לחלוק. ספרו 'שאגת אריה' נעשה אבן יסוד בפסיקת אורח חיים וחיבוריו נלמדים בעומק.</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>אמת הלכתית ללא פשרות: דיוק במקורות הראשונים ועצמאות פסיקה – גם במחיר של בדידות ציבורית.</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>השפעה מאוחרת על הרב מרדכי ברויאר (תורת הבחינות); הערכה בחב״ד</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/4tSyrs2SrcNd1WsVBoHZuh?si=fQD3_QT6TqqaEDMyoYR9bw</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="3" t="inlineStr"/>
+      <c r="N106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>שלמה מונק</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>1803–1867</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>גרמניה וצרפת</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>מדעי היהדות ופילוסופיה</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>מורה נבוכים, אבן גבירול</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>מזרחן וחוקר יהדות שהחזיר את אבן גבירול להיסטוריה של הפילוסופיה וערך את מורה נבוכים מן המקור הערבי.</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>שילוב בין מחקר מדעי לנאמנות למסורת.</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>הרמב"ם, אבן גבירול</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0fBwsgpkyNbo7MJnjhEgeH</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
+      <c r="N107" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N84"/>
+  <autoFilter ref="A1:N107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/חכמים_ללא_מחקר.xlsx
+++ b/data/חכמים_ללא_מחקר.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חכמים ללא מחקר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1739,12 +1739,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>רבי יצחק בר אלעזר הלוי</t>
+          <t>רבי יצחק קנפנטון</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1754,54 +1754,46 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1000–1070 בקירוב</t>
+          <t>1360–1463</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>אשכנז</t>
+          <t>קסטיליה; ספרד</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>הלכה ופרשנות</t>
+          <t>למדנות תלמודית</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>סגן לויה</t>
+          <t>דרכי התלמוד, גאון מקסטיליה</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>ראש ישיבת וורמייזא ומגדולי רבותיו של רש"י, בעל השפעה מכרעת על יהדות אשכנז.</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>הנהגה תורנית המשלבת סמכות, ענווה ודיוק הלכתי.</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>רש"י, רבנו גרשום</t>
-        </is>
-      </c>
+          <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4mph8tbv9qfvaXuaEBr9Ci</t>
+          <t>https://open.spotify.com/episode/2xytN0uGuTq03wNYWvusDO?si=GjQi6caQRZGdjDrWc8cX7w</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>רבי יצחק קנפנטון</t>
+          <t>רבי ישראל אלנקוה</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1811,46 +1803,54 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1360–1463</t>
+          <t>מאה 14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>קסטיליה; ספרד</t>
+          <t>טולדו (ספרד)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>למדנות תלמודית</t>
+          <t>מוסר/אגדה</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>דרכי התלמוד, גאון מקסטיליה</t>
+          <t>מנורת המאור, פרעות קנ״א, כינוס מדרשים</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
+          <t>מחבר 'מנורת המאור' מתוך כאב הדור והפיזור הרוחני. אסף מדרשים, אגדה וזוהר למסילת מוסר חיה ונגישה.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>מוסר כ'מנגינה חיה': צדקה כתיקון והצלה; תפילה כעמידה של דלות; הבניית חיים דרך סיפורים ומשלים.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>הרא״ש; יהדות ספרד לאחר 1391</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2xytN0uGuTq03wNYWvusDO?si=GjQi6caQRZGdjDrWc8cX7w</t>
+          <t>https://open.spotify.com/episode/7ong9XinXN1Na6aWhTzXME</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>רבי ישראל אלנקוה</t>
+          <t>רבנו חננאל בן חושיאל</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1860,54 +1860,54 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>מאה 14</t>
+          <t>מאה 11</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>טולדו (ספרד)</t>
+          <t>קירואן (צפון אפריקה)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>מוסר/אגדה</t>
+          <t>פירוש תלמוד/פסיקה</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>מנורת המאור, פרעות קנ״א, כינוס מדרשים</t>
+          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>מחבר 'מנורת המאור' מתוך כאב הדור והפיזור הרוחני. אסף מדרשים, אגדה וזוהר למסילת מוסר חיה ונגישה.</t>
+          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>מוסר כ'מנגינה חיה': צדקה כתיקון והצלה; תפילה כעמידה של דלות; הבניית חיים דרך סיפורים ומשלים.</t>
+          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>הרא״ש; יהדות ספרד לאחר 1391</t>
+          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7ong9XinXN1Na6aWhTzXME</t>
+          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>רבי שלמה בן אברהם</t>
+          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1917,54 +1917,54 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1235–1310 בקירוב</t>
+          <t>1100–1171</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ברצלונה, ספרד</t>
+          <t>צרפת (אשכנז)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה קהילתית ופולמוס אמוני</t>
+          <t>תלמוד ושיטה למדנית</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>רשב״א, תורת הבית, שו״ת, ברצלונה, פולמוס הפילוסופיה</t>
+          <t>תוספות, שתי שקיעות, תפילין, תקנות, מסעות הצלב</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>מגדולי הפוסקים והמנהיגים בתולדות התורה. עמד בראש קהילת ברצלונה, הנהיג ציבור, עיצב דיני קהילה וכתב אלפי תשובות שהשפיעו על כל עולם ההלכה.</t>
+          <t>נכדו של רש״י שבנה את שיטת בעלי התוספות: לא מוותרים על סתירות – מחברים סוגיות וגשרים. במקביל היה מנהיג קהילה בתקופת מסעי הצלב ותקן תקנות חברתיות.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>יצירת מרכז הלכתי מאוזן המחבר עומק תלמודי, אחריות ציבורית, גבולות אמונה והנהגה מעשית.</t>
+          <t>נאמנות קשוחה לנוסח הגמרא (“בספרים אל ימחק”) שמכריחה עומק, דיוק וחילוקים – ומייצרת לימוד יוצר.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ן; רבנו יונה; רבי יצחק מנרבונה; הריטב״א; רבנו בחיי; רבי יוסף קארו; אברהם אבולעפיה</t>
+          <t>בעלי התוספות; רש״י; מנהג זמן רבנו תם</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3fFSccuIPUhBryOySLd1mz?si=vVleiPsHQNK-DYsKMhH7LQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ?si=o5kksAmaQNiRkBHxN8CVpQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>594</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>רבנו חננאל בן חושיאל</t>
+          <t>רש"י (רבי שלמה יצחקי)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1974,213 +1974,185 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>מאה 11</t>
+          <t>1040–1105</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>קירואן (צפון אפריקה)</t>
+          <t>טרואה</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>פירוש תלמוד/פסיקה</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
-        </is>
-      </c>
+          <t>פרשנות המקרא, פרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
+          <t>גדול פרשני ישראל. פירושו לתורה ולתלמוד — בהיר, תמציתי וצמוד לפשט — פתח את שערי הלימוד לכל הדורות, ובלעדיו אין דף גמרא נלמד.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
-        </is>
-      </c>
+          <t>פשוטו של מקרא — פירוש שכל תלמיד יכול להיכנס בו</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
+          <t>הבעל שם טוב (רבי ישראל בעש"ט)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1100–1171</t>
+          <t>1698–1760</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>צרפת (אשכנז)</t>
+          <t>אוקראינה</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>תלמוד ושיטה למדנית</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>תוספות, שתי שקיעות, תפילין, תקנות, מסעות הצלב</t>
-        </is>
-      </c>
+          <t>חסידות, קבלה</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>נכדו של רש״י שבנה את שיטת בעלי התוספות: לא מוותרים על סתירות – מחברים סוגיות וגשרים. במקביל היה מנהיג קהילה בתקופת מסעי הצלב ותקן תקנות חברתיות.</t>
+          <t>מייסד תנועת החסידות. לימד שאין מקום פנוי ממנו, העמיד את הדבקות, השמחה ואהבת כל יהודי במרכז העבודה — ושינה את פני יהדות מזרח אירופה.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>נאמנות קשוחה לנוסח הגמרא (“בספרים אל ימחק”) שמכריחה עומק, דיוק וחילוקים – ומייצרת לימוד יוצר.</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>בעלי התוספות; רש״י; מנהג זמן רבנו תם</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ?si=o5kksAmaQNiRkBHxN8CVpQ&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>לית אתר פנוי מיניה — עבודת ה' בדבקות ובשמחה</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>רש"י (רבי שלמה יצחקי)</t>
+          <t>הרב אברהם יצחקי (זרע אברהם)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1040–1105</t>
+          <t>1661–1729</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>טרואה</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>פרשנות המקרא, פרשנות התלמוד</t>
+          <t>הלכה, הנהגה</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>גדול פרשני ישראל. פירושו לתורה ולתלמוד — בהיר, תמציתי וצמוד לפשט — פתח את שערי הלימוד לכל הדורות, ובלעדיו אין דף גמרא נלמד.</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>פשוטו של מקרא — פירוש שכל תלמיד יכול להיכנס בו</t>
-        </is>
-      </c>
+          <t>הראשון לציון ומחבר שו"ת 'זרע אברהם'. ממנהיגי ירושלים במאבק בשבתאות ובביצור מעמדה התורני של העיר.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>שמואל בן יצחק</t>
+          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ראשונים</t>
+          <t>אחרונים</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1190–1256</t>
+          <t>1858–1936</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ברצלונה, ספרד</t>
+          <t>רוגצ'וב/דווינסק</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>הלכה ודיני ממונות</t>
+          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>רבנו שמואל הסרדי, ספר התרומות, ממונות, משפט עברי</t>
+          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>מגדולי חכמי ספרד במאה ה־13 ואחד ממעצבי המשפט העברי. חיבורו 'ספר התרומות' סידר לראשונה באופן שיטתי תחום שלם של דיני ממונות.</t>
+          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>הפיכת ההלכה המשפטית לשפה חיה, נגישה ושיטתית עבור דיין, סוחר וקהילה כלכלית ממשית.</t>
+          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ן; רבי נתן בן מאיר מטרינקטיי; הטור; שולחן ערוך</t>
+          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5Cdc9RvxyriLFWPFMRfciK?si=P9JIX4Q4TCCtqmGdnswLcA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>הבעל שם טוב (רבי ישראל בעש"ט)</t>
+          <t>הרב יעקב ששפורטש</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2190,42 +2162,42 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1698–1760</t>
+          <t>1610–1698</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>אוקראינה</t>
+          <t>צפון אפריקה, אירופה המערבית (אמסטרדם, לונדון, המבורג, ליבורנו)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>חסידות, קבלה</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>מייסד תנועת החסידות. לימד שאין מקום פנוי ממנו, העמיד את הדבקות, השמחה ואהבת כל יהודי במרכז העבודה — ושינה את פני יהדות מזרח אירופה.</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>לית אתר פנוי מיניה — עבודת ה' בדבקות ובשמחה</t>
-        </is>
-      </c>
+          <t>פולמוס/הנהגה</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/09JfLsbxRNjLhC969SxOPd?si=zTKhNkZ7T8qiI1akCdsAvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>הרב אברהם יצחקי (זרע אברהם)</t>
+          <t>רבי יוסף שלמה דלמדיגו – יש״ר מקנדיה</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2235,38 +2207,50 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1661–1729</t>
+          <t>1591–1655</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>קנדיה, כרתים; פדובה; המבורג; אמסטרדם; פראג</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>הלכה, הנהגה</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
+          <t>רפואה, אסטרונומיה והגות</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>גלילאו, קופרניקוס, הליוצנטריות, מתמטיקה, רפואה, קבלה, תורה ומדע</t>
+        </is>
+      </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>הראשון לציון ומחבר שו"ת 'זרע אברהם'. ממנהיגי ירושלים במאבק בשבתאות ובביצור מעמדה התורני של העיר.</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
+          <t>רב, רופא, מתמטיקאי ואסטרונום שלמד אצל גלילאו באוניברסיטת פדובה. קיבל את המודל ההליוצנטרי ושילב ידע מדעי עם עיון תורני, תוך התמודדות מורכבת עם הקבלה וספר הזוהר.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>ידע מדעי חדש אינו חייב לאיים על המסורת; אפשר להשתמש בו כדי להעמיק בהבנת הבריאה, ההלכה וחכמת התורה.</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>גלילאו גליליי, קופרניקוס, בעל תוספות יום טוב, רבי יעקב עמדין, החיד״א, הראי״ה קוק, הרב יוסף קאפח</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
+          <t>רבי משה דוד ואלי (הרמ״ד ואלי)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2276,54 +2260,54 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1858–1936</t>
+          <t>1697–1777</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>רוגצ'וב/דווינסק</t>
+          <t>פדובה, איטליה</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
+          <t>קבלה/פרשנות מקרא</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
+          <t>פשוטו מכוון אל סודו, רמח״ל, כתבים גנוזים</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
+          <t>רופא מוסמך וחבר קרוב של הרמח״ל. פיתח שיטת פרשנות: הפשט עצמו רומז לסוד בכל שינוי דקדוקי/לשוני.</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
+          <t>מיפוי לשון המקרא למבנה הספירות; דחיית חכמות חיצוניות כתחליף; מפעל פירושים עצום שנחשף רק בדורות האחרונים.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
+          <t>הרמח״ל; חוג פדובה; הדפסת כתבים בדורנו</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
+          <t>https://open.spotify.com/episode/6Sc3CiYpTfV68Ke8SueReD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>הרב יעקב ששפורטש</t>
+          <t>רבי רפאל עמנואל חי ריקי</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2333,135 +2317,151 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1610–1698</t>
+          <t>1687–1743</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>צפון אפריקה, אירופה המערבית (אמסטרדם, לונדון, המבורג, ליבורנו)</t>
+          <t>איטליה וירושלים</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>פולמוס/הנהגה</t>
+          <t>קבלה ופרשנות</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+          <t>משנת חסידים, יושר לבב, קבלת האר"י</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>מקובל, פייטן ופרשן משנה, מן הדמויות הבולטות בקבלת איטליה.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>שילוב קבלת האר"י עם הוראה שיטתית וספרות הלכתית-קבלית.</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>האר"י; הרש"ש; האור החיים</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/09JfLsbxRNjLhC969SxOPd?si=zTKhNkZ7T8qiI1akCdsAvg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/3Foy6VcyWU352VPpw1z1cp?si=jaoMkKODSduL9jAf58zdww</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>רבי יוסף שלמה דלמדיגו – יש״ר מקנדיה</t>
+          <t>הלל צייטלין (1871–1942) – פילוסוף יהודי בין ניטשה לחסידות, שנרצח בשואה</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1591–1655</t>
+          <t>1871–1942</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>קנדיה, כרתים; פדובה; המבורג; אמסטרדם; פראג</t>
+          <t>פולין; מזרח אירופה</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>רפואה, אסטרונומיה והגות</t>
+          <t>מחשבה</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>גלילאו, קופרניקוס, הליוצנטריות, מתמטיקה, רפואה, קבלה, תורה ומדע</t>
+          <t>מודרנה יהודית; אקזיסטנציאליזם; חסידות; משבר אמונה</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>רב, רופא, מתמטיקאי ואסטרונום שלמד אצל גלילאו באוניברסיטת פדובה. קיבל את המודל ההליוצנטרי ושילב ידע מדעי עם עיון תורני, תוך התמודדות מורכבת עם הקבלה וספר הזוהר.</t>
+          <t>הלל צייטלין: פילוסוף יהודי בין ניטשה לחסידות, מבקר תרבות שחוזר לעומק רוחני; נרצח בשואה.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>ידע מדעי חדש אינו חייב לאיים על המסורת; אפשר להשתמש בו כדי להעמיק בהבנת הבריאה, ההלכה וחכמת התורה.</t>
+          <t>החיפוש עצמו הוא עבודת ה': להפוך ספק ומודרניות למנוע של תשובה וחידוש רוחני.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>גלילאו גליליי, קופרניקוס, בעל תוספות יום טוב, רבי יעקב עמדין, החיד״א, הראי״ה קוק, הרב יוסף קאפח</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>ניטשה; בובר; ברנר; חסידות חב"ד; ספרות יהודית מודרנית</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>https://spotifycreators-web.app.link/e/VKh6sMX4yQb</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>525</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>רבי יעקב אבן חביב (עין יעקב)</t>
+          <t>הרב אריה קפלן</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>אמצע המאה ה-15 – 1516</t>
+          <t>1934–1983</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>זמורה שבקסטיליה, ספרד; פורטוגל; סלוניקי</t>
+          <t>ברונקס, ניו יורק; ירושלים; ארצות הברית</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>אגדה, הלכה ומנהיגות קהילת המגורשים</t>
+          <t>קבלה, מדע והנגשת יהדות</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>עין יעקב, גירוש ספרד, אגדות התלמוד, סלוניקי, אנוסים</t>
+          <t>פיזיקה גרעינית, קבלה, מדיטציה יהודית, גיל היקום, The Living Torah, תורה ומדע, קירוב</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>ראש ישיבה נערץ בקסטיליה שגורש מספרד בשנת 1492, נמלט מפורטוגל אחרי גזירת ההמרה של 1497 והנהיג את קהילת המגורשים בסלוניקי. חיבר את "עין יעקב", כינוס אגדות התלמוד עם פירוש, ופירוש ל"ארבעה טורים" שעמד לפני רבי יוסף קארו בכתיבת "בית יוסף". נפטר בסלוניקי בשנת 1516, ובנו המהרלב״ח השלים את מפעלו.</t>
+          <t>רב, פיזיקאי, מתרגם וחוקר קבלה שפעל בארצות הברית והנגיש יהדות לקהל מודרני. עסק ביחסי תורה ומדע, בגיל היקום ובשחזור מסורות מדיטטיביות יהודיות מתוך ספרי הקבלה והחסידות, וכתב את The Living Torah.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>שיקום האמונה אחרי החורבן דרך אגדות חז״ל: האגדה כמסד רוחני ומקור תקווה לדור מגורשים שאיבד את עולמו הפיזי.</t>
+          <t>יהודי מודרני אינו צריך לבחור בין אינטלקט לאמונה; אפשר להשתמש בשפה מדעית ופסיכולוגית כדי להעמיק במקורות ולתרגם מסורת עתיקה לעולם מושגים בן זמננו.</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>רבי לוי אבן חביב (המהרלב״ח); רבי יצחק אבוהב; רבי יוסף קארו</t>
+          <t>ישיבת תורה ודעת, ישיבת מיר, רבי יצחק דמן עכו, רבי נחמן מברסלב, מקובלי ספרד והחסידות</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -2469,126 +2469,122 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>רבי משה דוד ואלי (הרמ״ד ואלי)</t>
+          <t>הרב יהודא ליאון אשכנזי (מניטו)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1697–1777</t>
+          <t>1922–1996</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>פדובה, איטליה</t>
+          <t>אלג'יריה → צרפת → ישראל</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>קבלה/פרשנות מקרא</t>
+          <t>מחשבת ישראל, קבלה, זהות לאומית</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>פשוטו מכוון אל סודו, רמח״ל, כתבים גנוזים</t>
+          <t>אסכולת פריז, לוינס, שושני, עברי/יהודי, צמצום כמוסר, תחייה</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>רופא מוסמך וחבר קרוב של הרמח״ל. פיתח שיטת פרשנות: הפשט עצמו רומז לסוד בכל שינוי דקדוקי/לשוני.</t>
+          <t>הוגה וקבליסט שחיבר בין מסורת צפון אפריקה, שיח אינטלקטואלי צרפתי ותורת ארץ ישראל; ניסח תורת זהויות והעמיד שפה חדשה של תחייה.</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>מיפוי לשון המקרא למבנה הספירות; דחיית חכמות חיצוניות כתחליף; מפעל פירושים עצום שנחשף רק בדורות האחרונים.</t>
+          <t>זהות 'עברי' כשלב תודעתי-לאומי שמאחד קודש וחול, משפחה ועם, מוסר והיסטוריה.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>הרמח״ל; חוג פדובה; הדפסת כתבים בדורנו</t>
+          <t>עמנואל לוינס; אנדרה נהר; יעקב גורדין; מר שושני; הרב צבי יהודה קוק; הרב אורי שרקי</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6Sc3CiYpTfV68Ke8SueReD</t>
+          <t>https://open.spotify.com/episode/6vCbxdldNDpdncGxSjvAyD</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>רבי רפאל עמנואל חי ריקי</t>
+          <t>הרב יהודה ליב דון יחיא</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>אחרונים</t>
+          <t>מודרני</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1687–1743</t>
+          <t>1869–1941</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>איטליה וירושלים</t>
+          <t>בלארוס; וולוז׳ין; שקלוב; צ׳רניגוב; תל אביב</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>קבלה ופרשנות</t>
+          <t>הלכה, חסידות וציונות דתית</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>משנת חסידים, יושר לבב, קבלת האר"י</t>
+          <t>וולוז׳ין, רבי חיים מבריסק, חב״ד-קאפוסט, המזרחי, חיבת ציון, בכורי יהודה, ציונות דתית</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>מקובל, פייטן ופרשן משנה, מן הדמויות הבולטות בקבלת איטליה.</t>
+          <t>רב, למדן והוגה ששילב בעולמו את הלמדנות הבריסקאית, מסורת חסידית ואת חזון הציונות הדתית. היה מתלמידי רבי חיים סולובייצ׳יק, השתתף בייסוד תנועת המזרחי וראה ביישוב הארץ ובבניין מוסדות לאומיים ביטוי מעשי של אמונה.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>שילוב קבלת האר"י עם הוראה שיטתית וספרות הלכתית-קבלית.</t>
+          <t>אמונה איננה המתנה פסיבית אלא כוח המחייב פעולה: כשם שהאדם בונה סוכה כדי ליצור מקום לקדושה, כך בניין הארץ והתחייה הלאומית יכולים להיות מעשה דתי המוציא את כוחות העם מן הכוח אל הפועל.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>האר"י; הרש"ש; האור החיים</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/3Foy6VcyWU352VPpw1z1cp?si=jaoMkKODSduL9jAf58zdww</t>
-        </is>
-      </c>
+          <t>רבי חיים סולובייצ׳יק, רבי אליעזר דון יחיא, חיים נחמן ביאליק, הראי״ה קוק, תנועת המזרחי</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>הלל צייטלין (1871–1942) – פילוסוף יהודי בין ניטשה לחסידות, שנרצח בשואה</t>
+          <t>הרב יוסף משאש</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2598,54 +2594,54 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1871–1942</t>
+          <t>1892–1974</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>פולין; מזרח אירופה</t>
+          <t>מקנס (מרוקו) → חיפה</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>מחשבה</t>
+          <t>הלכה, היסטוריה, הנהגה</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>מודרנה יהודית; אקזיסטנציאליזם; חסידות; משבר אמונה</t>
+          <t>פסיקה ריאלית, רציונליזם, אחדות ישראל, יהדות המגרב, אתחלתא דגאולה</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>הלל צייטלין: פילוסוף יהודי בין ניטשה לחסידות, מבקר תרבות שחוזר לעומק רוחני; נרצח בשואה.</t>
+          <t>איש אשכולות שראה במציאות כלי להבנת ההלכה, פסק באומץ מתוך חמלה ורוח הזמן, וחיזק את אחדות ישראל בין גולה לתקומה.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>החיפוש עצמו הוא עבודת ה': להפוך ספק ומודרניות למנוע של תשובה וחידוש רוחני.</t>
+          <t>הלכה נצחית שפוגשת זמן: ריאליזם הלכתי כמפתח לשמירת המסורת בחברה משתנה.</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>ניטשה; בובר; ברנר; חסידות חב"ד; ספרות יהודית מודרנית</t>
+          <t>קהילות המגרב; רבנות חיפה; שיח ציוני-דתי</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>https://spotifycreators-web.app.link/e/VKh6sMX4yQb</t>
+          <t>https://open.spotify.com/episode/2bY5WI2sxqsa1csNcbHXoG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>הרב אריה קפלן</t>
+          <t>הרב מאיר זייני</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2655,50 +2651,54 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1934–1983</t>
+          <t>1921–2012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ברונקס, ניו יורק; ירושלים; ארצות הברית</t>
+          <t>אלג׳יריה → פריז → ירושלים</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>קבלה, מדע והנגשת יהדות</t>
+          <t>מנהיגות קהילה/ציונות/מסורת צפון אפריקה</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>פיזיקה גרעינית, קבלה, מדיטציה יהודית, גיל היקום, The Living Torah, תורה ומדע, קירוב</t>
+          <t>יהדות אלג׳יריה, עוז חיים, תורה וגבורה, עלייה בגיל 85</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>רב, פיזיקאי, מתרגם וחוקר קבלה שפעל בארצות הברית והנגיש יהדות לקהל מודרני. עסק ביחסי תורה ומדע, בגיל היקום ובשחזור מסורות מדיטטיביות יהודיות מתוך ספרי הקבלה והחסידות, וכתב את The Living Torah.</t>
+          <t>רב קהילות באלג׳יריה, רב צבאי, ובצרפת החיה בית כנסת והנחיל זהות ליוורנואית-ציונית. עלה לישראל בגיל 85.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>יהודי מודרני אינו צריך לבחור בין אינטלקט לאמונה; אפשר להשתמש בשפה מדעית ופסיכולוגית כדי להעמיק במקורות ולתרגם מסורת עתיקה לעולם מושגים בן זמננו.</t>
+          <t>מנהיגות 'גדול גיבור' המחברת תורה ומעשה; גאולה מתוך מפגש תפילה-עשייה ושימור ניגון מסורת.</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>ישיבת תורה ודעת, ישיבת מיר, רבי יצחק דמן עכו, רבי נחמן מברסלב, מקובלי ספרד והחסידות</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t>מגורשי ספרד; הרב שרקי (תיאור תלמידים)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0hEDzOsuXWV4gBqUTv3KqW</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודא ליאון אשכנזי (מניטו)</t>
+          <t>הרב צבי הירש חיות (מהר"ץ חיות)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2708,54 +2708,54 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1922–1996</t>
+          <t>1805–1855</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>אלג'יריה → צרפת → ישראל</t>
+          <t>גליציה</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>מחשבת ישראל, קבלה, זהות לאומית</t>
+          <t>תורה שבעל פה, הגנה על המסורת, מתודולוגיה</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>אסכולת פריז, לוינס, שושני, עברי/יהודי, צמצום כמוסר, תחייה</t>
+          <t>מנחת קנאות, תורת נביאים, אמנציפציה, גשר מסורת-מחקר</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>הוגה וקבליסט שחיבר בין מסורת צפון אפריקה, שיח אינטלקטואלי צרפתי ותורת ארץ ישראל; ניסח תורת זהויות והעמיד שפה חדשה של תחייה.</t>
+          <t>גדול תורה בגליציה שניסה לגשר בין מחקר זהיר לבין נאמנות מוחלטת לתורה שבעל פה, ובנה שפה של הגנה אינטלקטואלית על המסורת.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>זהות 'עברי' כשלב תודעתי-לאומי שמאחד קודש וחול, משפחה ועם, מוסר והיסטוריה.</t>
+          <t>גשר נאמן: פתיחות דעת המשרתת אמונה – לא מחליפה אותה.</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>עמנואל לוינס; אנדרה נהר; יעקב גורדין; מר שושני; הרב צבי יהודה קוק; הרב אורי שרקי</t>
+          <t>חת"ם סופר; שלמה קלוגר; נחמן קרוכמל (רנ"ק)</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/6vCbxdldNDpdncGxSjvAyD</t>
+          <t>https://open.spotify.com/episode/7qsdQhzQdtrX80wVbwkfmZ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>הרב יהודה ליב דון יחיא</t>
+          <t>הרב צבי יהודה הכהן קוק</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2765,50 +2765,54 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1869–1941</t>
+          <t>1891–1982</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>בלארוס; וולוז׳ין; שקלוב; צ׳רניגוב; תל אביב</t>
+          <t>ירושלים</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>הלכה, חסידות וציונות דתית</t>
+          <t>הגות ציונית-דתית</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>וולוז׳ין, רבי חיים מבריסק, חב״ד-קאפוסט, המזרחי, חיבת ציון, בכורי יהודה, ציונות דתית</t>
+          <t>מרכז הרב, אתחלתא דגאולה, התיישבות</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>רב, למדן והוגה ששילב בעולמו את הלמדנות הבריסקאית, מסורת חסידית ואת חזון הציונות הדתית. היה מתלמידי רבי חיים סולובייצ׳יק, השתתף בייסוד תנועת המזרחי וראה ביישוב הארץ ובבניין מוסדות לאומיים ביטוי מעשי של אמונה.</t>
+          <t>ממשיך דרכו של הראי"ה קוק ומנהיג דור התחייה של הציונות הדתית.</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>אמונה איננה המתנה פסיבית אלא כוח המחייב פעולה: כשם שהאדם בונה סוכה כדי ליצור מקום לקדושה, כך בניין הארץ והתחייה הלאומית יכולים להיות מעשה דתי המוציא את כוחות העם מן הכוח אל הפועל.</t>
+          <t>חיבור בין מדינת ישראל, לימוד תורה וגאולה.</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>רבי חיים סולובייצ׳יק, רבי אליעזר דון יחיא, חיים נחמן ביאליק, הראי״ה קוק, תנועת המזרחי</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>הראי"ה קוק; הרב חנן פורת; הרב משה לוינגר</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/33CjfygeixWek05uscU4qM?si=zHwL0eT7QtWwuw1PHxvNJg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף חיים מבגדאד – “בן איש חי” (לא מה שחשבתם)</t>
+          <t>הרב רפאל יהודה מנחם לוי – רבי יהודה מרגוזה</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2818,54 +2822,50 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1835–1909</t>
+          <t>1783–1879</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>בגדאד</t>
+          <t>סרייבו; ירושלים; קושטא; יפו</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>הלכה, קבלה והגות חברתית</t>
+          <t>רבנות, התיישבות וחקלאות</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>ביקורת חברתית, מעמדות, טנזימאט, פסיקה, פיוט, קבלה</t>
+          <t>יפו, הפרדס היהודי הראשון, מקוה ישראל, פתח תקווה, ועד העיר, עבודת האדמה</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>דמות רב-פנים: מגדולי פוסקי המזרח וגם הוגה חברתי. לאחר משבר אישי וכלכלי פיתח שפה שמחברת תורה למציאות של יחסי כוח, ומעניקה לעניים ידע מוסרי ייחודי.</t>
+          <t>רבה הראשון של יפו החדשה, שאיחד קהילות, קלט עולים והקים מוסדות ציבור. נטע ב־1842 את הפרדס היהודי הראשון בעת החדשה, תמך במקוה ישראל ועודד עבודה, חקלאות והתיישבות בארץ.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>תורה כפרשנות חברתית: הפסיקה והדרשה חושפות עוולות ומחייבות אחריות מוסרית – בלי לוותר על עומק הלכתי וקבלי.</t>
+          <t>תורה ועבודת האדמה אינן סותרות זו את זו; בניין הארץ, עצמאות כלכלית ויוזמה ציבורית הם חלק מתהליך הגאולה.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>רפורמות הטנזימאט; דיון מודרני על שוויון וזהות; מסורת יהדות בבל</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5mA6IjVV5SbxfT0OfQ22Ad?si=-IWNH499SoGWQ6XF5UUQbg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>הרב יהודה ביבאס, משה מונטיפיורי, קרל נטר, מייסדי פתח תקווה</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>הרב יוסף משאש</t>
+          <t>הרבנית ברכה קאפח</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2875,54 +2875,54 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1892–1974</t>
+          <t>1922–2013</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>מקנס (מרוקו) → חיפה</t>
+          <t>צנעא, תימן; ירושלים</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>הלכה, היסטוריה, הנהגה</t>
+          <t>חסד ועשייה קהילתית</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>פסיקה ריאלית, רציונליזם, אחדות ישראל, יהדות המגרב, אתחלתא דגאולה</t>
+          <t>סגולת נעמי, יהדות תימן, פרס ישראל, חסד, נשים</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>איש אשכולות שראה במציאות כלי להבנת ההלכה, פסק באומץ מתוך חמלה ורוח הזמן, וחיזק את אחדות ישראל בין גולה לתקומה.</t>
+          <t>אשת חסד ומנהיגת קהילה, ייסדה את עמותת "סגולת נעמי" לסיוע לאלפי משפחות בירושלים. בעלה, הרב יוסף קאפח, הקדיש עצמו להדרת כתבי הרמב"ם, בעוד היא בנתה תשתית כלכלית וחברתית למשפחה ולקהילה.</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>הלכה נצחית שפוגשת זמן: ריאליזם הלכתי כמפתח לשמירת המסורת בחברה משתנה.</t>
+          <t>חסד כמערכת מאורגנת ומכובדת ולא כמעשה חד־פעמי — שילוב לב רחב עם סדר וניהול קפדני כדי לשמור על כבוד המקבלים.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>קהילות המגרב; רבנות חיפה; שיח ציוני-דתי</t>
+          <t>הרב יוסף קאפח (בעלה)</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2bY5WI2sxqsa1csNcbHXoG</t>
+          <t>https://open.spotify.com/episode/78MX2sAT6M6hAi0qCuuhb7?si=-05qETOVSCGChK_7lpJwmA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>הרב מאיר זייני</t>
+          <t>הרבנית ד"ר ברוריה דייוויד</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2932,54 +2932,54 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1921–2012</t>
+          <t>1938–2023</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>אלג׳יריה → פריז → ירושלים</t>
+          <t>ניו יורק; ירושלים</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות קהילה/ציונות/מסורת צפון אפריקה</t>
+          <t>חינוך נשים ולמדנות</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>יהדות אלג׳יריה, עוז חיים, תורה וגבורה, עלייה בגיל 85</t>
+          <t>מכון שרה שנירר (BJJ), הרב יצחק הוטנר, פחד יצחק, למדנות נשית, נשים</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>רב קהילות באלג׳יריה, רב צבאי, ובצרפת החיה בית כנסת והנחיל זהות ליוורנואית-ציונית. עלה לישראל בגיל 85.</t>
+          <t>בתו של הרב יצחק הוטנר, בעלת דוקטורט מאוניברסיטת קולומביה, ייסדה ומיכוונת את מכון שרה שנירר בירושלים כמוסד עילית ללמדנות נשים חרדיות, ועמדה בראש עריכת ספרי אביה לאחר פטירתו.</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>מנהיגות 'גדול גיבור' המחברת תורה ומעשה; גאולה מתוך מפגש תפילה-עשייה ושימור ניגון מסורת.</t>
+          <t>העצמת הלמדנות הנשית ברמה אינטלקטואלית גבוהה מבלי לערער על גבולות המבנה המסורתי של עולם התורה.</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>מגורשי ספרד; הרב שרקי (תיאור תלמידים)</t>
+          <t>הרב יצחק הוטנר (אביה), הרב יונתן דייוויד (בעלה), פרופ' סאלו בארון</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0hEDzOsuXWV4gBqUTv3KqW</t>
+          <t>https://open.spotify.com/episode/6hBYh8i79O4pCQKeB10QNN?si=IuDV3verTYivgK2SuPnG9w</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי הירש חיות (מהר"ץ חיות)</t>
+          <t>הרבנית ויכנא קפלן</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2989,54 +2989,54 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1805–1855</t>
+          <t>1913–1986</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>גליציה</t>
+          <t>סלונים; קרקוב; ניו יורק</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>תורה שבעל פה, הגנה על המסורת, מתודולוגיה</t>
+          <t>חינוך</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>מנחת קנאות, תורת נביאים, אמנציפציה, גשר מסורת-מחקר</t>
+          <t>בית יעקב אמריקה, וויליאמסבורג, תנועת המוסר, רבי אלחנן וסרמן, נשים</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>גדול תורה בגליציה שניסה לגשר בין מחקר זהיר לבין נאמנות מוחלטת לתורה שבעל פה, ובנה שפה של הגנה אינטלקטואלית על המסורת.</t>
+          <t>תלמידתה המובהקת של שרה שנירר, ייסדה ב־1937 את רשת "בית יעקב" בארצות הברית, החל מכיתה קטנה בביתה שבוויליאמסבורג ועד למוסד חינוכי רחב היקף עם פנימייה, תיכון וסמינר להכשרת מורות.</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>גשר נאמן: פתיחות דעת המשרתת אמונה – לא מחליפה אותה.</t>
+          <t>התאמת מודל "בית יעקב" האירופי למציאות האמריקאית, תוך שילוב דרישות רוחניות גבוהות עם יחס אישי ורגישות חינוכית.</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>חת"ם סופר; שלמה קלוגר; נחמן קרוכמל (רנ"ק)</t>
+          <t>שרה שנירר, רבי ישראל יעקב לובצ'נסקי, רבי אלחנן וסרמן</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7qsdQhzQdtrX80wVbwkfmZ</t>
+          <t>https://open.spotify.com/episode/7gEH0FmW9xyX4je0Jk40A7?si=9VHkgmhURN2trmReuSg2hg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>הרב צבי יהודה הכהן קוק</t>
+          <t>הרבנית שרה הרצוג</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3046,54 +3046,54 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1891–1982</t>
+          <t>1896–1979</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>לטביה; סקוטלנד; אירלנד; ירושלים</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>הגות ציונית-דתית</t>
+          <t>מנהיגות ציבורית וחסד</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>מרכז הרב, אתחלתא דגאולה, התיישבות</t>
+          <t>תנועת אמונה, בית החולים הרצוג, הרב יצחק אייזיק הרצוג, שירות לאומי, נשים</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>ממשיך דרכו של הראי"ה קוק ומנהיג דור התחייה של הציונות הדתית.</t>
+          <t>רעייתו של הרב הראשי יצחק אייזיק הרצוג, הובילה מפעל חברתי רחב: הקמת תנועת "אמונה" ב־1959, פיתוח בית החולים הרצוג, ועידוד השכלה ותעסוקה לנשים דתיות.</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>חיבור בין מדינת ישראל, לימוד תורה וגאולה.</t>
+          <t>שילוב נאמנות הלכתית עם מעורבות ציבורית פעילה — האישה תורמת לבניין החברה והאומה ולא רק לבית.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>הראי"ה קוק; הרב חנן פורת; הרב משה לוינגר</t>
+          <t>הרב יצחק אייזיק הלוי הרצוג (בעלה), חיים הרצוג (בנה), יצחק הרצוג (נכדה)</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/33CjfygeixWek05uscU4qM?si=zHwL0eT7QtWwuw1PHxvNJg&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+          <t>https://open.spotify.com/episode/5cRN0ef6AcQepyWCQ1IKwv?si=fgo8Tk4GSBORkdMUO9tVuw</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>הרב רפאל יהודה מנחם לוי – רבי יהודה מרגוזה</t>
+          <t>חכם ציון חביב ברכה</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3103,50 +3103,42 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1783–1879</t>
+          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>סרייבו; ירושלים; קושטא; יפו</t>
+          <t>ירושלים (נחלאות)</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>רבנות, התיישבות וחקלאות</t>
+          <t>קבלה</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>יפו, הפרדס היהודי הראשון, מקוה ישראל, פתח תקווה, ועד העיר, עבודת האדמה</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>רבה הראשון של יפו החדשה, שאיחד קהילות, קלט עולים והקים מוסדות ציבור. נטע ב־1842 את הפרדס היהודי הראשון בעת החדשה, תמך במקוה ישראל ועודד עבודה, חקלאות והתיישבות בארץ.</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>תורה ועבודת האדמה אינן סותרות זו את זו; בניין הארץ, עצמאות כלכלית ויוזמה ציבורית הם חלק מתהליך הגאולה.</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>הרב יהודה ביבאס, משה מונטיפיורי, קרל נטר, מייסדי פתח תקווה</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
+          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>הרבנית ברכה קאפח</t>
+          <t>טובה סנהדראי-גולדרייך</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3156,54 +3148,54 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1922–2013</t>
+          <t>1906–1993</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>צנעא, תימן; ירושלים</t>
+          <t>גליציה; ארץ ישראל</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>חסד ועשייה קהילתית</t>
+          <t>מנהיגות ציונית־דתית</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>סגולת נעמי, יהדות תימן, פרס ישראל, חסד, נשים</t>
+          <t>תנועת אמונה, המפד"ל, כנסת, שירות לאומי, נשים</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>אשת חסד ומנהיגת קהילה, ייסדה את עמותת "סגולת נעמי" לסיוע לאלפי משפחות בירושלים. בעלה, הרב יוסף קאפח, הקדיש עצמו להדרת כתבי הרמב"ם, בעוד היא בנתה תשתית כלכלית וחברתית למשפחה ולקהילה.</t>
+          <t>חברת הכנסת הדתית הראשונה, ממנהיגות תנועת "אמונה" ומקימת "רשימת הפועלת והאישה הדתית" ב־1949. כיהנה ארבע קדנציות בכנסת מטעם המפד"ל וקידמה חקיקה חברתית ורווחתית.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>חסד כמערכת מאורגנת ומכובדת ולא כמעשה חד־פעמי — שילוב לב רחב עם סדר וניהול קפדני כדי לשמור על כבוד המקבלים.</t>
+          <t>שילוב מחויבות הלכתית עם אחריות ציבורית ופרלמנטרית — הרחבת השתתפות נשים דתיות בבניין המדינה מבלי לוותר על עקרונות.</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>הרב יוסף קאפח (בעלה)</t>
+          <t>תנועת אמונה, המפד"ל</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/78MX2sAT6M6hAi0qCuuhb7?si=-05qETOVSCGChK_7lpJwmA</t>
+          <t>https://open.spotify.com/episode/0RuE8l4DbgcRxBQWjGBUv3?si=rW9fZeAOTueEFDMOKUR5mQ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>הרבנית ד"ר ברוריה דייוויד</t>
+          <t>רבי גדליה נדל</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3213,54 +3205,50 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1938–2023</t>
+          <t>1923–2004</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>ניו יורק; ירושלים</t>
+          <t>ליטא; בני ברק, ארץ ישראל</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>חינוך נשים ולמדנות</t>
+          <t>הלכה, מחשבת ישראל ותורה ומדע</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>מכון שרה שנירר (BJJ), הרב יצחק הוטנר, פחד יצחק, למדנות נשית, נשים</t>
+          <t>החזון איש, אבולוציה, גיל העולם, טעמי המצוות, רמב״ם, עצמאות כלכלית, אמת</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>בתו של הרב יצחק הוטנר, בעלת דוקטורט מאוניברסיטת קולומביה, ייסדה ומיכוונת את מכון שרה שנירר בירושלים כמוסד עילית ללמדנות נשים חרדיות, ועמדה בראש עריכת ספרי אביה לאחר פטירתו.</t>
+          <t>מתלמידיו הקרובים של החזון איש ופוסק בשיכון חזון איש, שנודע בדרך לימוד עצמאית ובחתירה להבנת רעיון המצווה. לצד קנאותו ההלכתית והציבורית סבר שאין סתירה הכרחית בין תורת האבולוציה לבין התורה וראה במדע כלי לבירור האמת.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>העצמת הלמדנות הנשית ברמה אינטלקטואלית גבוהה מבלי לערער על גבולות המבנה המסורתי של עולם התורה.</t>
+          <t>אמונה אינה צריכה לחשוש מן האמת; אפשר לשלב נאמנות עמוקה לתורה עם יושר אינטלקטואלי, עיון בטבע והבנת העיקרון הרוחני והמוסרי שמאחורי ההלכה.</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>הרב יצחק הוטנר (אביה), הרב יונתן דייוויד (בעלה), פרופ' סאלו בארון</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/6hBYh8i79O4pCQKeB10QNN?si=IuDV3verTYivgK2SuPnG9w</t>
-        </is>
-      </c>
+          <t>החזון איש, רבי יצחק זאב סולובייצ׳יק מבריסק, רבי שמשון אהרן פולנסקי, הרמב״ם</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>הרבנית ויכנא קפלן</t>
+          <t>רבי מאיר הגדול מפרמישלאן</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3270,54 +3258,50 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1913–1986</t>
+          <t>1703–1773</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>סלונים; קרקוב; ניו יורק</t>
+          <t>פרמישלאן, גליציה</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>חינוך</t>
+          <t>חסידות, קבלה וחינוך</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>בית יעקב אמריקה, וויליאמסבורג, תנועת המוסר, רבי אלחנן וסרמן, נשים</t>
+          <t>הבעל שם טוב, ראשית החסידות, פרנקיסטים, מלמד תינוקות, יאיר אור</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>תלמידתה המובהקת של שרה שנירר, ייסדה ב־1937 את רשת "בית יעקב" בארצות הברית, החל מכיתה קטנה בביתה שבוויליאמסבורג ועד למוסד חינוכי רחב היקף עם פנימייה, תיכון וסמינר להכשרת מורות.</t>
+          <t>מתלמידיו הקרובים של הבעל שם טוב וממנהיגי הדור הראשון של החסידות. היה מקובל עמוק ולוחם נגד הפרנקיסטים, אך בחר בענווה ללמד ילדים קטנים ולראות באותיות האל״ף־בי״ת שער לסודות התורה.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>התאמת מודל "בית יעקב" האירופי למציאות האמריקאית, תוך שילוב דרישות רוחניות גבוהות עם יחס אישי ורגישות חינוכית.</t>
+          <t>גדלות רוחנית נבחנת בענווה ובנכונות לעסוק ביסודות הפשוטים; אותיות של ילד יכולות לשאת את אותם סודות המצויים בעולמות הקבלה.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>שרה שנירר, רבי ישראל יעקב לובצ'נסקי, רבי אלחנן וסרמן</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7gEH0FmW9xyX4je0Jk40A7?si=9VHkgmhURN2trmReuSg2hg</t>
-        </is>
-      </c>
+          <t>הבעל שם טוב, רבי שבתי מרשקוב, שושלות נדבורנה, קרעטשניף וקאלוש</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>הרבנית שרה הרצוג</t>
+          <t>רבי מאיר שמחה הכהן מדווינסק</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3327,54 +3311,54 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1896–1979</t>
+          <t>1843–1926</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>לטביה; סקוטלנד; אירלנד; ירושלים</t>
+          <t>דווינסק (לטביה/ליטא)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות ציבורית וחסד</t>
+          <t>הלכה/פרשנות תורה/מחשבה ציונית</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, בית החולים הרצוג, הרב יצחק אייזיק הרצוג, שירות לאומי, נשים</t>
+          <t>אור שמח, משך חכמה, גלות וזהות, שבועות</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>רעייתו של הרב הראשי יצחק אייזיק הרצוג, הובילה מפעל חברתי רחב: הקמת תנועת "אמונה" ב־1959, פיתוח בית החולים הרצוג, ועידוד השכלה ותעסוקה לנשים דתיות.</t>
+          <t>מחבר 'אור שמח' ו'משך חכמה'. גשר בין שכל לאמונה ובין גלות לתחייה; ניתוח חריף של היסטוריה יהודית וקדושה.</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>שילוב נאמנות הלכתית עם מעורבות ציבורית פעילה — האישה תורמת לבניין החברה והאומה ולא רק לבית.</t>
+          <t>הגלות כמנגנון זהות; קדושה אינה בחומר אלא ברצון ה׳; ציונות וגאולה בדרך הטבע (בלפור/סן-רמו).</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>הרב יצחק אייזיק הלוי הרצוג (בעלה), חיים הרצוג (בנה), יצחק הרצוג (נכדה)</t>
+          <t>הרמב״ם; הרב קוק; עידן התחייה</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5cRN0ef6AcQepyWCQ1IKwv?si=fgo8Tk4GSBORkdMUO9tVuw</t>
+          <t>https://open.spotify.com/episode/5M242GRqncgReaYVplhjBU</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>חכם ציון חביב ברכה</t>
+          <t>רבי שמשון רפאל הירש</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3384,42 +3368,50 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
+          <t>1808–1888</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ירושלים (נחלאות)</t>
+          <t>המבורג; פרנקפורט, גרמניה</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>קבלה</t>
+          <t>הגות, חינוך ויחסי תורה ומודרנה</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
+          <t>תורה עם דרך ארץ, אורתודוקסיה, השכלה כללית, חינוך, איגרות צפון, חורב, פולמוס הפרישה</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>רב, פרשן והוגה יהודי מגרמניה שניסח את שיטת ״תורה עם דרך ארץ״. הנהיג בפרנקפורט מערכת חינוך ששילבה לימודי קודש עם לימודים כלליים, ונאבק ברפורמה תוך הדגשת מחויבות מלאה להלכה גם בתוך התרבות המודרנית.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>אפשר להיות מעורב במדע, בתרבות ובחברה המודרנית מבלי שהתורה תאבד את מרכזיותה; הפתיחות לעולם דורשת זהות תורנית ברורה וגבולות הלכתיים מוצקים.</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>רבי יצחק דב במברגר, קהילת פרנקפורט, התנועה הרפורמית, האורתודוקסיה הגרמנית</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>טובה סנהדראי-גולדרייך</t>
+          <t>רס״ן רועי קליין הי״ד</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3429,54 +3421,54 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1906–1993</t>
+          <t>1975–2006</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>גליציה; ארץ ישראל</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>מנהיגות ציונית־דתית</t>
+          <t>מוסר, מנהיגות</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, המפד"ל, כנסת, שירות לאומי, נשים</t>
+          <t>גבורה, צה״ל, אמונה</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>חברת הכנסת הדתית הראשונה, ממנהיגות תנועת "אמונה" ומקימת "רשימת הפועלת והאישה הדתית" ב־1949. כיהנה ארבע קדנציות בכנסת מטעם המפד"ל וקידמה חקיקה חברתית ורווחתית.</t>
+          <t>קצין צה"ל שמסר נפשו להצלת חייליו והפך לסמל של גבורה הנובעת מחיים של ערכים.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>שילוב מחויבות הלכתית עם אחריות ציבורית ופרלמנטרית — הרחבת השתתפות נשים דתיות בבניין המדינה מבלי לוותר על עקרונות.</t>
+          <t>גבורה כרצף חיים – לא רגע חד־פעמי</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>תנועת אמונה, המפד"ל</t>
+          <t>צה״ל; חינוך דתי</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/0RuE8l4DbgcRxBQWjGBUv3?si=rW9fZeAOTueEFDMOKUR5mQ</t>
+          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>רבי גדליה נדל</t>
+          <t>שושלת אבוחצירא</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3486,50 +3478,54 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1923–2004</t>
+          <t>המאה ה־19–20</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ליטא; בני ברק, ארץ ישראל</t>
+          <t>מרוקו, ארץ ישראל</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>הלכה, מחשבת ישראל ותורה ומדע</t>
+          <t>קבלה, הנהגה, פיוט</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>החזון איש, אבולוציה, גיל העולם, טעמי המצוות, רמב״ם, עצמאות כלכלית, אמת</t>
+          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>מתלמידיו הקרובים של החזון איש ופוסק בשיכון חזון איש, שנודע בדרך לימוד עצמאית ובחתירה להבנת רעיון המצווה. לצד קנאותו ההלכתית והציבורית סבר שאין סתירה הכרחית בין תורת האבולוציה לבין התורה וראה במדע כלי לבירור האמת.</t>
+          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>אמונה אינה צריכה לחשוש מן האמת; אפשר לשלב נאמנות עמוקה לתורה עם יושר אינטלקטואלי, עיון בטבע והבנת העיקרון הרוחני והמוסרי שמאחורי ההלכה.</t>
+          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>החזון איש, רבי יצחק זאב סולובייצ׳יק מבריסק, רבי שמשון אהרן פולנסקי, הרמב״ם</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>רבי מאיר הגדול מפרמישלאן</t>
+          <t>שלמה מונק</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3539,50 +3535,54 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1703–1773</t>
+          <t>1803–1867</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>פרמישלאן, גליציה</t>
+          <t>גרמניה וצרפת</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>חסידות, קבלה וחינוך</t>
+          <t>מדעי היהדות ופילוסופיה</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>הבעל שם טוב, ראשית החסידות, פרנקיסטים, מלמד תינוקות, יאיר אור</t>
+          <t>מורה נבוכים, אבן גבירול</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>מתלמידיו הקרובים של הבעל שם טוב וממנהיגי הדור הראשון של החסידות. היה מקובל עמוק ולוחם נגד הפרנקיסטים, אך בחר בענווה ללמד ילדים קטנים ולראות באותיות האל״ף־בי״ת שער לסודות התורה.</t>
+          <t>מזרחן וחוקר יהדות שהחזיר את אבן גבירול להיסטוריה של הפילוסופיה וערך את מורה נבוכים מן המקור הערבי.</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>גדלות רוחנית נבחנת בענווה ובנכונות לעסוק ביסודות הפשוטים; אותיות של ילד יכולות לשאת את אותם סודות המצויים בעולמות הקבלה.</t>
+          <t>שילוב בין מחקר מדעי לנאמנות למסורת.</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>הבעל שם טוב, רבי שבתי מרשקוב, שושלות נדבורנה, קרעטשניף וקאלוש</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+          <t>הרמב"ם, אבן גבירול</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0fBwsgpkyNbo7MJnjhEgeH</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>רבי מאיר שמחה הכהן מדווינסק</t>
+          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3592,328 +3592,47 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1843–1926</t>
+          <t>המאה ה־19 (פרסום 1843)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>דווינסק (לטביה/ליטא)</t>
+          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>הלכה/פרשנות תורה/מחשבה ציונית</t>
+          <t>מחשבת ישראל (קבלה)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>אור שמח, משך חכמה, גלות וזהות, שבועות</t>
+          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>מחבר 'אור שמח' ו'משך חכמה'. גשר בין שכל לאמונה ובין גלות לתחייה; ניתוח חריף של היסטוריה יהודית וקדושה.</t>
+          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>הגלות כמנגנון זהות; קדושה אינה בחומר אלא ברצון ה׳; ציונות וגאולה בדרך הטבע (בלפור/סן-רמו).</t>
+          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>הרמב״ם; הרב קוק; עידן התחייה</t>
+          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5M242GRqncgReaYVplhjBU</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>רבי שמשון רפאל הירש</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>1808–1888</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>המבורג; פרנקפורט, גרמניה</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>הגות, חינוך ויחסי תורה ומודרנה</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>תורה עם דרך ארץ, אורתודוקסיה, השכלה כללית, חינוך, איגרות צפון, חורב, פולמוס הפרישה</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>רב, פרשן והוגה יהודי מגרמניה שניסח את שיטת ״תורה עם דרך ארץ״. הנהיג בפרנקפורט מערכת חינוך ששילבה לימודי קודש עם לימודים כלליים, ונאבק ברפורמה תוך הדגשת מחויבות מלאה להלכה גם בתוך התרבות המודרנית.</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>אפשר להיות מעורב במדע, בתרבות ובחברה המודרנית מבלי שהתורה תאבד את מרכזיותה; הפתיחות לעולם דורשת זהות תורנית ברורה וגבולות הלכתיים מוצקים.</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>רבי יצחק דב במברגר, קהילת פרנקפורט, התנועה הרפורמית, האורתודוקסיה הגרמנית</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>רס״ן רועי קליין הי״ד</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>1975–2006</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>ישראל</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>מוסר, מנהיגות</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>גבורה, צה״ל, אמונה</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>קצין צה"ל שמסר נפשו להצלת חייליו והפך לסמל של גבורה הנובעת מחיים של ערכים.</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>גבורה כרצף חיים – לא רגע חד־פעמי</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>צה״ל; חינוך דתי</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/6oOKCpQo5tEf5hcdghAQIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>שושלת אבוחצירא</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>המאה ה־19–20</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>מרוקו, ארץ ישראל</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>קבלה, הנהגה, פיוט</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>שלמה מונק</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>1803–1867</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>גרמניה וצרפת</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>מדעי היהדות ופילוסופיה</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>מורה נבוכים, אבן גבירול</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>מזרחן וחוקר יהדות שהחזיר את אבן גבירול להיסטוריה של הפילוסופיה וערך את מורה נבוכים מן המקור הערבי.</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>שילוב בין מחקר מדעי לנאמנות למסורת.</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>הרמב"ם, אבן גבירול</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/0fBwsgpkyNbo7MJnjhEgeH</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>המאה ה־19 (פרסום 1843)</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>מחשבת ישראל (קבלה)</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
           <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE?si=N2J3HnklTRW2Gm-BmT4SFA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K65"/>
+  <autoFilter ref="A1:K60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>